--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$345</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="776">
   <si>
     <t>id</t>
   </si>
@@ -2401,6 +2401,15 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/79dd474cb6bb</t>
+  </si>
+  <si>
+    <t>东京恐怖故事崇山乐园</t>
+  </si>
+  <si>
+    <t>崇山乐园,东京恐怖故事崇山乐园</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c675e7514d1a</t>
   </si>
 </sst>
 </file>
@@ -3076,7 +3085,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3132,10 +3141,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3457,7 +3462,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E346"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="20.9166666666667" customWidth="1"/>
@@ -8066,13 +8071,13 @@
       <c r="A313">
         <v>312</v>
       </c>
-      <c r="B313" s="22" t="s">
+      <c r="B313" s="13" t="s">
         <v>703</v>
       </c>
       <c r="D313" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E313" s="22" t="s">
+      <c r="E313" s="13" t="s">
         <v>704</v>
       </c>
     </row>
@@ -8100,7 +8105,7 @@
       <c r="D315" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E315" s="22" t="s">
+      <c r="E315" s="13" t="s">
         <v>708</v>
       </c>
     </row>
@@ -8114,7 +8119,7 @@
       <c r="D316" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E316" s="22" t="s">
+      <c r="E316" s="13" t="s">
         <v>710</v>
       </c>
     </row>
@@ -8122,14 +8127,14 @@
       <c r="A317">
         <v>316</v>
       </c>
-      <c r="B317" s="23" t="s">
+      <c r="B317" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="C317" s="23"/>
-      <c r="D317" s="23" t="s">
+      <c r="C317" s="8"/>
+      <c r="D317" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E317" s="23" t="s">
+      <c r="E317" s="8" t="s">
         <v>713</v>
       </c>
     </row>
@@ -8137,14 +8142,14 @@
       <c r="A318">
         <v>317</v>
       </c>
-      <c r="B318" s="23" t="s">
+      <c r="B318" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="C318" s="23"/>
-      <c r="D318" s="23" t="s">
+      <c r="C318" s="8"/>
+      <c r="D318" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E318" s="23" t="s">
+      <c r="E318" s="8" t="s">
         <v>715</v>
       </c>
     </row>
@@ -8152,14 +8157,14 @@
       <c r="A319">
         <v>318</v>
       </c>
-      <c r="B319" s="23" t="s">
+      <c r="B319" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="C319" s="23"/>
-      <c r="D319" s="23" t="s">
+      <c r="C319" s="8"/>
+      <c r="D319" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E319" s="23" t="s">
+      <c r="E319" s="8" t="s">
         <v>717</v>
       </c>
     </row>
@@ -8167,14 +8172,14 @@
       <c r="A320">
         <v>319</v>
       </c>
-      <c r="B320" s="23" t="s">
+      <c r="B320" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C320" s="23"/>
-      <c r="D320" s="23" t="s">
+      <c r="C320" s="8"/>
+      <c r="D320" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E320" s="23" t="s">
+      <c r="E320" s="8" t="s">
         <v>719</v>
       </c>
     </row>
@@ -8182,14 +8187,14 @@
       <c r="A321">
         <v>320</v>
       </c>
-      <c r="B321" s="23" t="s">
+      <c r="B321" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="C321" s="23"/>
-      <c r="D321" s="23" t="s">
+      <c r="C321" s="8"/>
+      <c r="D321" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E321" s="23" t="s">
+      <c r="E321" s="8" t="s">
         <v>721</v>
       </c>
     </row>
@@ -8197,14 +8202,14 @@
       <c r="A322">
         <v>321</v>
       </c>
-      <c r="B322" s="23" t="s">
+      <c r="B322" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="C322" s="23"/>
-      <c r="D322" s="23" t="s">
+      <c r="C322" s="8"/>
+      <c r="D322" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E322" s="23" t="s">
+      <c r="E322" s="8" t="s">
         <v>723</v>
       </c>
     </row>
@@ -8212,14 +8217,14 @@
       <c r="A323">
         <v>322</v>
       </c>
-      <c r="B323" s="23" t="s">
+      <c r="B323" s="8" t="s">
         <v>724</v>
       </c>
-      <c r="C323" s="23"/>
-      <c r="D323" s="23" t="s">
+      <c r="C323" s="8"/>
+      <c r="D323" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E323" s="23" t="s">
+      <c r="E323" s="8" t="s">
         <v>725</v>
       </c>
     </row>
@@ -8227,14 +8232,14 @@
       <c r="A324">
         <v>323</v>
       </c>
-      <c r="B324" s="23" t="s">
+      <c r="B324" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="C324" s="23"/>
-      <c r="D324" s="23" t="s">
+      <c r="C324" s="8"/>
+      <c r="D324" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E324" s="23" t="s">
+      <c r="E324" s="8" t="s">
         <v>727</v>
       </c>
     </row>
@@ -8242,14 +8247,14 @@
       <c r="A325">
         <v>324</v>
       </c>
-      <c r="B325" s="23" t="s">
+      <c r="B325" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="C325" s="23"/>
-      <c r="D325" s="23" t="s">
+      <c r="C325" s="8"/>
+      <c r="D325" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E325" s="23" t="s">
+      <c r="E325" s="8" t="s">
         <v>729</v>
       </c>
     </row>
@@ -8257,14 +8262,14 @@
       <c r="A326">
         <v>325</v>
       </c>
-      <c r="B326" s="23" t="s">
+      <c r="B326" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="C326" s="23"/>
-      <c r="D326" s="23" t="s">
+      <c r="C326" s="8"/>
+      <c r="D326" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E326" s="23" t="s">
+      <c r="E326" s="8" t="s">
         <v>731</v>
       </c>
     </row>
@@ -8272,14 +8277,14 @@
       <c r="A327">
         <v>326</v>
       </c>
-      <c r="B327" s="23" t="s">
+      <c r="B327" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="C327" s="23"/>
-      <c r="D327" s="23" t="s">
+      <c r="C327" s="8"/>
+      <c r="D327" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E327" s="23" t="s">
+      <c r="E327" s="8" t="s">
         <v>733</v>
       </c>
     </row>
@@ -8287,14 +8292,14 @@
       <c r="A328">
         <v>327</v>
       </c>
-      <c r="B328" s="23" t="s">
+      <c r="B328" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="C328" s="23"/>
-      <c r="D328" s="23" t="s">
+      <c r="C328" s="8"/>
+      <c r="D328" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E328" s="23" t="s">
+      <c r="E328" s="8" t="s">
         <v>735</v>
       </c>
     </row>
@@ -8302,14 +8307,14 @@
       <c r="A329">
         <v>328</v>
       </c>
-      <c r="B329" s="23" t="s">
+      <c r="B329" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="C329" s="23"/>
-      <c r="D329" s="23" t="s">
+      <c r="C329" s="8"/>
+      <c r="D329" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E329" s="23" t="s">
+      <c r="E329" s="8" t="s">
         <v>737</v>
       </c>
     </row>
@@ -8317,14 +8322,14 @@
       <c r="A330">
         <v>329</v>
       </c>
-      <c r="B330" s="23" t="s">
+      <c r="B330" s="8" t="s">
         <v>738</v>
       </c>
-      <c r="C330" s="23"/>
-      <c r="D330" s="23" t="s">
+      <c r="C330" s="8"/>
+      <c r="D330" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E330" s="23" t="s">
+      <c r="E330" s="8" t="s">
         <v>739</v>
       </c>
     </row>
@@ -8332,14 +8337,14 @@
       <c r="A331">
         <v>330</v>
       </c>
-      <c r="B331" s="23" t="s">
+      <c r="B331" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="C331" s="23"/>
-      <c r="D331" s="23" t="s">
+      <c r="C331" s="8"/>
+      <c r="D331" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E331" s="23" t="s">
+      <c r="E331" s="8" t="s">
         <v>741</v>
       </c>
     </row>
@@ -8347,14 +8352,14 @@
       <c r="A332">
         <v>331</v>
       </c>
-      <c r="B332" s="23" t="s">
+      <c r="B332" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="C332" s="23"/>
-      <c r="D332" s="23" t="s">
+      <c r="C332" s="8"/>
+      <c r="D332" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E332" s="23" t="s">
+      <c r="E332" s="8" t="s">
         <v>743</v>
       </c>
     </row>
@@ -8362,14 +8367,14 @@
       <c r="A333">
         <v>332</v>
       </c>
-      <c r="B333" s="23" t="s">
+      <c r="B333" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="C333" s="23"/>
-      <c r="D333" s="23" t="s">
+      <c r="C333" s="8"/>
+      <c r="D333" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E333" s="23" t="s">
+      <c r="E333" s="8" t="s">
         <v>745</v>
       </c>
     </row>
@@ -8377,14 +8382,14 @@
       <c r="A334">
         <v>333</v>
       </c>
-      <c r="B334" s="23" t="s">
+      <c r="B334" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="C334" s="23"/>
-      <c r="D334" s="23" t="s">
+      <c r="C334" s="8"/>
+      <c r="D334" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E334" s="23" t="s">
+      <c r="E334" s="8" t="s">
         <v>747</v>
       </c>
     </row>
@@ -8392,14 +8397,14 @@
       <c r="A335">
         <v>334</v>
       </c>
-      <c r="B335" s="23" t="s">
+      <c r="B335" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="C335" s="23"/>
-      <c r="D335" s="23" t="s">
+      <c r="C335" s="8"/>
+      <c r="D335" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E335" s="23" t="s">
+      <c r="E335" s="8" t="s">
         <v>749</v>
       </c>
     </row>
@@ -8407,14 +8412,14 @@
       <c r="A336">
         <v>335</v>
       </c>
-      <c r="B336" s="23" t="s">
+      <c r="B336" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="C336" s="23"/>
-      <c r="D336" s="23" t="s">
+      <c r="C336" s="8"/>
+      <c r="D336" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E336" s="23" t="s">
+      <c r="E336" s="8" t="s">
         <v>751</v>
       </c>
     </row>
@@ -8422,14 +8427,14 @@
       <c r="A337">
         <v>336</v>
       </c>
-      <c r="B337" s="23" t="s">
+      <c r="B337" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="C337" s="23"/>
-      <c r="D337" s="23" t="s">
+      <c r="C337" s="8"/>
+      <c r="D337" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E337" s="23" t="s">
+      <c r="E337" s="8" t="s">
         <v>753</v>
       </c>
     </row>
@@ -8437,14 +8442,14 @@
       <c r="A338">
         <v>337</v>
       </c>
-      <c r="B338" s="23" t="s">
+      <c r="B338" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="C338" s="23"/>
-      <c r="D338" s="23" t="s">
+      <c r="C338" s="8"/>
+      <c r="D338" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E338" s="23" t="s">
+      <c r="E338" s="8" t="s">
         <v>755</v>
       </c>
     </row>
@@ -8452,14 +8457,14 @@
       <c r="A339">
         <v>338</v>
       </c>
-      <c r="B339" s="23" t="s">
+      <c r="B339" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="C339" s="23"/>
-      <c r="D339" s="23" t="s">
+      <c r="C339" s="8"/>
+      <c r="D339" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E339" s="23" t="s">
+      <c r="E339" s="8" t="s">
         <v>757</v>
       </c>
     </row>
@@ -8467,14 +8472,14 @@
       <c r="A340">
         <v>339</v>
       </c>
-      <c r="B340" s="23" t="s">
+      <c r="B340" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="C340" s="23"/>
-      <c r="D340" s="23" t="s">
+      <c r="C340" s="8"/>
+      <c r="D340" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E340" s="23" t="s">
+      <c r="E340" s="8" t="s">
         <v>759</v>
       </c>
     </row>
@@ -8482,14 +8487,14 @@
       <c r="A341">
         <v>340</v>
       </c>
-      <c r="B341" s="23" t="s">
+      <c r="B341" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="C341" s="23"/>
-      <c r="D341" s="23" t="s">
+      <c r="C341" s="8"/>
+      <c r="D341" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E341" s="23" t="s">
+      <c r="E341" s="8" t="s">
         <v>761</v>
       </c>
     </row>
@@ -8497,14 +8502,14 @@
       <c r="A342">
         <v>341</v>
       </c>
-      <c r="B342" s="23" t="s">
+      <c r="B342" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="C342" s="23"/>
-      <c r="D342" s="23" t="s">
+      <c r="C342" s="8"/>
+      <c r="D342" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E342" s="23" t="s">
+      <c r="E342" s="8" t="s">
         <v>763</v>
       </c>
     </row>
@@ -8512,14 +8517,14 @@
       <c r="A343">
         <v>342</v>
       </c>
-      <c r="B343" s="23" t="s">
+      <c r="B343" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="C343" s="23"/>
-      <c r="D343" s="23" t="s">
+      <c r="C343" s="8"/>
+      <c r="D343" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="E343" s="23" t="s">
+      <c r="E343" s="8" t="s">
         <v>765</v>
       </c>
     </row>
@@ -8530,7 +8535,7 @@
       <c r="B344" t="s">
         <v>766</v>
       </c>
-      <c r="C344" s="24" t="s">
+      <c r="C344" s="16" t="s">
         <v>767</v>
       </c>
       <c r="D344" t="s">
@@ -8554,8 +8559,25 @@
         <v>772</v>
       </c>
     </row>
+    <row r="346" ht="15" spans="1:5">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346" s="17" t="s">
+        <v>773</v>
+      </c>
+      <c r="C346" t="s">
+        <v>774</v>
+      </c>
+      <c r="D346" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E346" s="22" t="s">
+        <v>775</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E312" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E345" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="987">
   <si>
     <t>id</t>
   </si>
@@ -2410,6 +2410,639 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/c675e7514d1a</t>
+  </si>
+  <si>
+    <t>《十六年无穷日》作者：夏日勿苇</t>
+  </si>
+  <si>
+    <t>小说</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f8867443f692</t>
+  </si>
+  <si>
+    <t>《被曾经的金丝雀反向圈养了》作者：墨泊洲</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f140a8d03b3f</t>
+  </si>
+  <si>
+    <t>《被竹马的表兄觊觎后》作者：抱帚忘雪</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4bc68383e4a7</t>
+  </si>
+  <si>
+    <t>《穿进狗血文后和男主的命运交换了[快穿gb]》作者：姜沉漾</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0a181c0e6fba</t>
+  </si>
+  <si>
+    <t>《从签到开始修仙成圣》作者：缇卡</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4d78409bb045</t>
+  </si>
+  <si>
+    <t>《掺水酒不会梦到黑皮巧克力》作者：岫夕</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/3d3d6f38c059</t>
+  </si>
+  <si>
+    <t>《大美人甜蜜再婚生活[七零]》作者：春池星</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/cfeecb7ee244</t>
+  </si>
+  <si>
+    <t>《大魔头他养大了死对头》作者：墨弦青</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ff364bbd6ae7</t>
+  </si>
+  <si>
+    <t>《都市怪谈拆迁办（第一诡异拆迁办）》作者：撕枕犹眠</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e3af1f65fcfd</t>
+  </si>
+  <si>
+    <t>《当我错刷你的校园卡之后》作者：周在川</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/482b8161a979</t>
+  </si>
+  <si>
+    <t>《奋斗的金丝雀》</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/63d40d123952</t>
+  </si>
+  <si>
+    <t>《古言短篇4：囡囡》作者：袖侧</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/a782cbd8996f</t>
+  </si>
+  <si>
+    <t>《怀了主母兄长的孩子后》作者：不落言笙</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/64613639cd9a</t>
+  </si>
+  <si>
+    <t>《捡到一只小狐狸O！[全息]》作者：沉缄</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1956a451801e</t>
+  </si>
+  <si>
+    <t>《将军太傲娇》作者：苏有仪</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/2bfe95745f87</t>
+  </si>
+  <si>
+    <t>《假千金身份曝光后被迫万人迷了》作者：待我温酒</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/36b6271022b6</t>
+  </si>
+  <si>
+    <t>《九十三个红绿灯》作者：樾杉木</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/6686c7ffa0ee</t>
+  </si>
+  <si>
+    <t>《锦书散落星河》宋锦书 顾瑾珩</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0e85973b25e5</t>
+  </si>
+  <si>
+    <t>《救赎文但与黑化男主互演》作者：酒酿汤圆W</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f58655bfbce1</t>
+  </si>
+  <si>
+    <t>《巨星只想卖鞋和贴贴[娱乐圈]》作者：支野</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/08454139a9ee</t>
+  </si>
+  <si>
+    <t>《开局一朵向日葵》作者：文梦呓</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e07a7a754007</t>
+  </si>
+  <si>
+    <t>《没错，我是大反派[轮回末世]》作者：焚轮吹梦</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/2fa4be453ecd</t>
+  </si>
+  <si>
+    <t>《满级富婆，潇洒九零》作者：金面佛</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e4b2d3f18610</t>
+  </si>
+  <si>
+    <t>《末日领主种番薯日志[基建]》作者：甜饼喂猪</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/6b5c613e600f</t>
+  </si>
+  <si>
+    <t>《毛绒绒带我进厂》作者：春和景明一号</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0cdea0127956</t>
+  </si>
+  <si>
+    <t>《明月不曾奔我而来》林舒苒 傅庭深</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0981cf7326b7</t>
+  </si>
+  <si>
+    <t>《妈，救命!》作者：红刺北</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ce546aec935d</t>
+  </si>
+  <si>
+    <t>《年代大佬的报恩小娇妻[八零]》作者：金湘语</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d9439264c38f</t>
+  </si>
+  <si>
+    <t>《南风若知我意》谢瑶 裴瑾南</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4c9283f0e472</t>
+  </si>
+  <si>
+    <t>《犬系陷阱》作者：韩肆夏</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1f8464d03eb1</t>
+  </si>
+  <si>
+    <t>《清云鉴》作者：烬天翼</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/64c41e2c8c8f</t>
+  </si>
+  <si>
+    <t>《全宇宙都在觊觎我的基因》作者：鹿衔灯</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/099bc0290e64</t>
+  </si>
+  <si>
+    <t>《如懿传进忠同人之穿越时空奔向你》作者：进忠公公的迷妹</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/62efb3dfcc54</t>
+  </si>
+  <si>
+    <t>《少阁主今天也没有死》作者：嵊灵</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/6a758e390481</t>
+  </si>
+  <si>
+    <t>《世界更新中》作者：烛萤舟</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/43b85a883caa</t>
+  </si>
+  <si>
+    <t>《随老公进城的乡下小媳妇重生了》</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/820eacb3194b</t>
+  </si>
+  <si>
+    <t>《守陵娘子山食纪》作者：绿豆红汤</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/fa49fc0c0f95</t>
+  </si>
+  <si>
+    <t>《谁说分手后不能暗恋前任》作者：陶格</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0ef3713d4a3c</t>
+  </si>
+  <si>
+    <t>《首席她又吐血了[星际机甲]》作者：仿生八爪鱼</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/a26f853b0682</t>
+  </si>
+  <si>
+    <t>《师祖为何还不飞升》作者：海盐芝士卷</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d69a0acd3e96</t>
+  </si>
+  <si>
+    <t>《丧葬直播后暴富了》作者：达不溜蓝</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1368e1ea0cab</t>
+  </si>
+  <si>
+    <t>《退!我老公尾巴在响!》作者：椰椰不打烊</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0f0e14b02765</t>
+  </si>
+  <si>
+    <t>《她有惑人美貌2[快穿]》作者：玥滢</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/670d5495b1f4</t>
+  </si>
+  <si>
+    <t>《为你打开时间的门[网络版]》作者：皎皎</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/2efb921bae6b</t>
+  </si>
+  <si>
+    <t>《亡妻的第八年》作者：浅困</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/3c6297954de3</t>
+  </si>
+  <si>
+    <t>《我听见海棠花落》江晚吟 周砚白</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1d1b9ad7d03a</t>
+  </si>
+  <si>
+    <t>《小巷烟火[八零]》作者：秋凌</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ccf8fc90be25</t>
+  </si>
+  <si>
+    <t>《御兽：从天灾降临开始》作者：金彩</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e90ebe569558</t>
+  </si>
+  <si>
+    <t>《纯白恶魔》作者：priest</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/022714ae032d</t>
+  </si>
+  <si>
+    <t>《春风沉醉的夜晚》作者：鲤鲤鲤</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/97d3517f3181</t>
+  </si>
+  <si>
+    <t>《穿进真假少爷文，我成恋综背景板》</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/a851f0d05c25</t>
+  </si>
+  <si>
+    <t>《纯情金主和他的金丝雀大哥》作者：布布里</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ff8cea42c6be</t>
+  </si>
+  <si>
+    <t>《顶级恋爱脑，但装的》作者：祝辞酒</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/3a739975c3f7</t>
+  </si>
+  <si>
+    <t>《当他分手后》作者：雾苏台</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/224914d3532f</t>
+  </si>
+  <si>
+    <t>《烦人上司竟是我的家奴？！》作者：勤恳牛马</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0841d607b49a</t>
+  </si>
+  <si>
+    <t>《分手》作者：冷山就木</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/a43b0ac43ac7</t>
+  </si>
+  <si>
+    <t>《寡夫郎有喜了》作者：猛嚼酸菜鱼</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/84f97a540914</t>
+  </si>
+  <si>
+    <t>《顾总，夫人他又去相亲啦！》作者：楚君山</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/762657b4b30a</t>
+  </si>
+  <si>
+    <t>《荒岛求生后揣了宿敌的崽》作者：日月一明</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c9a0823e7eab</t>
+  </si>
+  <si>
+    <t>《和死对头的异界冒险[基建]》作者：木兰竹</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/40585eff661f</t>
+  </si>
+  <si>
+    <t>《禁欲系顶流被强取豪夺后》作者：付萌萌</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/933c97a68084</t>
+  </si>
+  <si>
+    <t>《快穿硬核管家，专治霸总癫公》</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/15b08ea06645</t>
+  </si>
+  <si>
+    <t>《凌晨三点熬夜会被随机拉进怪谈故事会》作者：石头羊</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/62243c60a6a9</t>
+  </si>
+  <si>
+    <t>《荔枝煮茶》作者：静沚</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/edf623756613</t>
+  </si>
+  <si>
+    <t>《摩擦生热》作者：一院</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/5101cd34980b</t>
+  </si>
+  <si>
+    <t>《梦里看见昨天》作者：不执灯</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1c2a11368396</t>
+  </si>
+  <si>
+    <t>《男团选秀里的祭天皇族》作者：颓废大带鱼</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f763483fe001</t>
+  </si>
+  <si>
+    <t>《破产霸总：兵王司机别太会宠</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/9b5a7cc1def6</t>
+  </si>
+  <si>
+    <t>《漂亮宝贝不养了？》作者：杳杳一言</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ec1324328ded</t>
+  </si>
+  <si>
+    <t>《什刹海是海吗》作者：晏灼宁</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/a7b409de2c77</t>
+  </si>
+  <si>
+    <t>《死对头误食吐真剂后》作者：查理小羊</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/fe07af9cd0de</t>
+  </si>
+  <si>
+    <t>《丧尸也可以打网球》作者：左木茶茶君</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/dc4c5e85b752</t>
+  </si>
+  <si>
+    <t>《死亡万花筒》 作者：西子绪【补福利番】</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/895a7f71a9b6</t>
+  </si>
+  <si>
+    <t>《伤心绿苹果》作者：下一天雨</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/cc4a46d54c2c</t>
+  </si>
+  <si>
+    <t>《同僚们都有病啊！》作者：甜来哉</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/dbb1998382b5</t>
+  </si>
+  <si>
+    <t>《我靠天道系统带领宗门致富》</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/4ce5b4487a56</t>
+  </si>
+  <si>
+    <t>《为了多活几年我闪婚了》作者：言六册</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/555709453c4a</t>
+  </si>
+  <si>
+    <t>《误撩高岭之花后他黑化了》作者：深海鲤</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/675d96b714f9</t>
+  </si>
+  <si>
+    <t>《万人嫌军校o，但钓系美人！》作者：一枕孤舟</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/7d304028184e</t>
+  </si>
+  <si>
+    <t>《易感期的顶A黏上舔狗beta了》作者：月下莲客</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/85b74c7d27d9</t>
+  </si>
+  <si>
+    <t>《诱惑》作者：冥月鬼姬／鬼姬·溟</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/eb8104eb1785</t>
+  </si>
+  <si>
+    <t>《作精假少爷失忆后攻略养兄》作者：脉脉春风</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/7b6c6e87bc4a</t>
+  </si>
+  <si>
+    <t>《竹马每天都在钓我》作者：橙三月</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/37c3261ca8ac</t>
+  </si>
+  <si>
+    <t>《直男的自我攻略》作者：落回</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/7e4bceb98040</t>
+  </si>
+  <si>
+    <t>《真实遗愿清单》作者：卡比丘</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/53d1bb667dfa</t>
+  </si>
+  <si>
+    <t>《重生之豁然》作者：缘何故</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/5da1fc0f0d5a</t>
+  </si>
+  <si>
+    <t>《重生之至尊仙侣》作者：冰糖莲子羹</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d859100214e2</t>
+  </si>
+  <si>
+    <t>《重新救赎偏执反派后（快穿）》作者：糖晚</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ea5bce8e8a94</t>
+  </si>
+  <si>
+    <t>《穿成绝嗣皇帝早死的崽》作者：闻鹊语</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/f20fae829a05</t>
+  </si>
+  <si>
+    <t>《九殿下究竟何时登基》作者：骨漏呱闻</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/612e51dd4b9e</t>
+  </si>
+  <si>
+    <t>《快穿：大佬又穿成恶毒女配啦！》作者：暮十七</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/efb48ceeee98</t>
+  </si>
+  <si>
+    <t>《末世降临：我的随身空间无限大！》作者：卿阿卿</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1c3cdaf6d56e</t>
+  </si>
+  <si>
+    <t>《末世小店：我带系统搞经营》作者：榴莲肠粉</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0b64680b1485</t>
+  </si>
+  <si>
+    <t>《骑自行车逛遍各位面》作者：蒜冰激凌香</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d9f0fb0e7d3a</t>
+  </si>
+  <si>
+    <t>《傻女归来》作者：小寒将至</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1aa3c8677929</t>
+  </si>
+  <si>
+    <t>《逃荒，我全家都是重生的》作者：墨墨是墨爷</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/194d0b3064f7</t>
+  </si>
+  <si>
+    <t>《心声泄露后：满朝文武爱上吃瓜》作者：甜玉米汁</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c4b2d592a21c</t>
+  </si>
+  <si>
+    <t>《直播：摇出霍去病做代打》作者：酒神葡萄绿</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1d7fb390a435</t>
+  </si>
+  <si>
+    <t>《败给格格＆别吵，前任的大佬小叔在宠了》景格 厉牧时 作者：灯下不黑黑</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/48d88efb4a8e</t>
+  </si>
+  <si>
+    <t>《别人修仙我捡漏，卷王们破防了》凤青禾 作者：一人派对</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ac430a3f3cb6</t>
+  </si>
+  <si>
+    <t>《白月光回京，夜夜被太子爷亲红温》贺雨棠 周宴泽 作者：野火不熄</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/21ed9b227073</t>
+  </si>
+  <si>
+    <t>《春望山楹》云菅 周婆子 作者：庄大刀</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c148f9eb8dae</t>
+  </si>
+  <si>
+    <t>《热恋从新婚开始＆婚既钟情》林序秋 周望津 作者：暴躁小红</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/30aceb039b93</t>
+  </si>
+  <si>
+    <t>《越夜越熟＆玩玩而已，他怎么上瘾了》诗悦 秦昭 作者：玛格绿特</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/142fee39cf5f</t>
+  </si>
+  <si>
+    <t>《真千金她断亲修道＆玄学大佬断亲后，和酆都大帝锁了》酆烬 沈月魄 作者：脾气暴躁的吼吼</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0c78700a9b55</t>
   </si>
 </sst>
 </file>
@@ -3085,7 +3718,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3143,6 +3776,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3462,10 +4097,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E346"/>
+  <dimension ref="A1:E451"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="20.9166666666667" customWidth="1"/>
+    <col min="2" max="2" width="60.75" customWidth="1"/>
     <col min="3" max="4" width="20.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="33.0833333333333" style="1" customWidth="1"/>
   </cols>
@@ -8574,6 +9209,1581 @@
       </c>
       <c r="E346" s="22" t="s">
         <v>775</v>
+      </c>
+    </row>
+    <row r="347" ht="15" spans="1:5">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="C347" s="23"/>
+      <c r="D347" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E347" s="23" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="348" ht="15" spans="1:5">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348" s="23" t="s">
+        <v>779</v>
+      </c>
+      <c r="C348" s="23"/>
+      <c r="D348" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E348" s="23" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="349" ht="15" spans="1:5">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349" s="23" t="s">
+        <v>781</v>
+      </c>
+      <c r="C349" s="23"/>
+      <c r="D349" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E349" s="23" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="350" ht="15" spans="1:5">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350" s="23" t="s">
+        <v>783</v>
+      </c>
+      <c r="C350" s="23"/>
+      <c r="D350" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E350" s="23" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="351" ht="15" spans="1:5">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351" s="23" t="s">
+        <v>785</v>
+      </c>
+      <c r="C351" s="23"/>
+      <c r="D351" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E351" s="23" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="352" ht="15" spans="1:5">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352" s="23" t="s">
+        <v>787</v>
+      </c>
+      <c r="C352" s="23"/>
+      <c r="D352" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E352" s="23" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="353" ht="15" spans="1:5">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" s="23" t="s">
+        <v>789</v>
+      </c>
+      <c r="C353" s="23"/>
+      <c r="D353" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E353" s="23" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="354" ht="15" spans="1:5">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354" s="23" t="s">
+        <v>791</v>
+      </c>
+      <c r="C354" s="23"/>
+      <c r="D354" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E354" s="23" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="355" ht="15" spans="1:5">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355" s="23" t="s">
+        <v>793</v>
+      </c>
+      <c r="C355" s="23"/>
+      <c r="D355" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E355" s="23" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="356" ht="15" spans="1:5">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356" s="23" t="s">
+        <v>795</v>
+      </c>
+      <c r="C356" s="23"/>
+      <c r="D356" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E356" s="23" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="357" ht="15" spans="1:5">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357" s="23" t="s">
+        <v>797</v>
+      </c>
+      <c r="C357" s="23"/>
+      <c r="D357" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E357" s="23" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="358" ht="15" spans="1:5">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358" s="23" t="s">
+        <v>799</v>
+      </c>
+      <c r="C358" s="23"/>
+      <c r="D358" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E358" s="23" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="359" ht="15" spans="1:5">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="C359" s="23"/>
+      <c r="D359" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E359" s="23" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="360" ht="15" spans="1:5">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360" s="23" t="s">
+        <v>803</v>
+      </c>
+      <c r="C360" s="23"/>
+      <c r="D360" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E360" s="23" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="361" ht="15" spans="1:5">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361" s="23" t="s">
+        <v>805</v>
+      </c>
+      <c r="C361" s="23"/>
+      <c r="D361" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E361" s="23" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="362" ht="15" spans="1:5">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362" s="23" t="s">
+        <v>807</v>
+      </c>
+      <c r="C362" s="23"/>
+      <c r="D362" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E362" s="23" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="363" ht="15" spans="1:5">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363" s="23" t="s">
+        <v>809</v>
+      </c>
+      <c r="C363" s="23"/>
+      <c r="D363" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E363" s="23" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="364" ht="15" spans="1:5">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364" s="23" t="s">
+        <v>811</v>
+      </c>
+      <c r="C364" s="23"/>
+      <c r="D364" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E364" s="23" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="365" ht="15" spans="1:5">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="C365" s="23"/>
+      <c r="D365" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E365" s="23" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="366" ht="15" spans="1:5">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366" s="23" t="s">
+        <v>815</v>
+      </c>
+      <c r="C366" s="23"/>
+      <c r="D366" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E366" s="23" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="367" ht="15" spans="1:5">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367" s="23" t="s">
+        <v>817</v>
+      </c>
+      <c r="C367" s="23"/>
+      <c r="D367" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E367" s="23" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="368" ht="15" spans="1:5">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="C368" s="23"/>
+      <c r="D368" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E368" s="23" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="369" ht="15" spans="1:5">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369" s="23" t="s">
+        <v>821</v>
+      </c>
+      <c r="C369" s="23"/>
+      <c r="D369" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E369" s="23" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="370" ht="15" spans="1:5">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370" s="23" t="s">
+        <v>823</v>
+      </c>
+      <c r="C370" s="23"/>
+      <c r="D370" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E370" s="23" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="371" ht="15" spans="1:5">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371" s="23" t="s">
+        <v>825</v>
+      </c>
+      <c r="C371" s="23"/>
+      <c r="D371" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E371" s="23" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="372" ht="15" spans="1:5">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372" s="23" t="s">
+        <v>827</v>
+      </c>
+      <c r="C372" s="23"/>
+      <c r="D372" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E372" s="23" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="373" ht="15" spans="1:5">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373" s="23" t="s">
+        <v>829</v>
+      </c>
+      <c r="C373" s="23"/>
+      <c r="D373" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E373" s="23" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="374" ht="15" spans="1:5">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374" s="23" t="s">
+        <v>831</v>
+      </c>
+      <c r="C374" s="23"/>
+      <c r="D374" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E374" s="23" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="375" ht="15" spans="1:5">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375" s="23" t="s">
+        <v>833</v>
+      </c>
+      <c r="C375" s="23"/>
+      <c r="D375" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E375" s="23" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="376" ht="15" spans="1:5">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376" s="23" t="s">
+        <v>835</v>
+      </c>
+      <c r="C376" s="23"/>
+      <c r="D376" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E376" s="23" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="377" ht="15" spans="1:5">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377" s="23" t="s">
+        <v>837</v>
+      </c>
+      <c r="C377" s="23"/>
+      <c r="D377" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E377" s="23" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="378" ht="15" spans="1:5">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378" s="23" t="s">
+        <v>839</v>
+      </c>
+      <c r="C378" s="23"/>
+      <c r="D378" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E378" s="23" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="379" ht="15" spans="1:5">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="23" t="s">
+        <v>841</v>
+      </c>
+      <c r="C379" s="23"/>
+      <c r="D379" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E379" s="23" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="380" ht="15" spans="1:5">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380" s="23" t="s">
+        <v>843</v>
+      </c>
+      <c r="C380" s="23"/>
+      <c r="D380" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E380" s="23" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="381" ht="15" spans="1:5">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381" s="23" t="s">
+        <v>845</v>
+      </c>
+      <c r="C381" s="23"/>
+      <c r="D381" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E381" s="23" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="382" ht="15" spans="1:5">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382" s="23" t="s">
+        <v>847</v>
+      </c>
+      <c r="C382" s="23"/>
+      <c r="D382" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E382" s="23" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="383" ht="15" spans="1:5">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383" s="23" t="s">
+        <v>849</v>
+      </c>
+      <c r="C383" s="23"/>
+      <c r="D383" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E383" s="23" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="384" ht="15" spans="1:5">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384" s="23" t="s">
+        <v>851</v>
+      </c>
+      <c r="C384" s="23"/>
+      <c r="D384" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E384" s="23" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="385" ht="15" spans="1:5">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385" s="23" t="s">
+        <v>853</v>
+      </c>
+      <c r="C385" s="23"/>
+      <c r="D385" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E385" s="23" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="386" ht="15" spans="1:5">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="C386" s="23"/>
+      <c r="D386" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E386" s="23" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="387" ht="15" spans="1:5">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387" s="23" t="s">
+        <v>857</v>
+      </c>
+      <c r="C387" s="23"/>
+      <c r="D387" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E387" s="23" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="388" ht="15" spans="1:5">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388" s="23" t="s">
+        <v>859</v>
+      </c>
+      <c r="C388" s="23"/>
+      <c r="D388" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E388" s="23" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="389" ht="15" spans="1:5">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389" s="23" t="s">
+        <v>861</v>
+      </c>
+      <c r="C389" s="23"/>
+      <c r="D389" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E389" s="23" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="390" ht="15" spans="1:5">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="23" t="s">
+        <v>863</v>
+      </c>
+      <c r="C390" s="23"/>
+      <c r="D390" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E390" s="23" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="391" ht="15" spans="1:5">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391" s="23" t="s">
+        <v>865</v>
+      </c>
+      <c r="C391" s="23"/>
+      <c r="D391" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E391" s="23" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="392" ht="15" spans="1:5">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392" s="23" t="s">
+        <v>867</v>
+      </c>
+      <c r="C392" s="23"/>
+      <c r="D392" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E392" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="393" ht="15" spans="1:5">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393" s="23" t="s">
+        <v>869</v>
+      </c>
+      <c r="C393" s="23"/>
+      <c r="D393" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E393" s="23" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="394" ht="15" spans="1:5">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394" s="23" t="s">
+        <v>871</v>
+      </c>
+      <c r="C394" s="23"/>
+      <c r="D394" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E394" s="24" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="395" ht="15" spans="1:5">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395" s="23" t="s">
+        <v>873</v>
+      </c>
+      <c r="C395" s="23"/>
+      <c r="D395" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E395" s="23" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="396" ht="15" spans="1:5">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396" s="23" t="s">
+        <v>875</v>
+      </c>
+      <c r="C396" s="23"/>
+      <c r="D396" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E396" s="23" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="397" ht="15" spans="1:5">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397" s="23" t="s">
+        <v>877</v>
+      </c>
+      <c r="C397" s="23"/>
+      <c r="D397" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E397" s="23" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="398" ht="15" spans="1:5">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398" s="23" t="s">
+        <v>879</v>
+      </c>
+      <c r="C398" s="23"/>
+      <c r="D398" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E398" s="23" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="399" ht="15" spans="1:5">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399" s="23" t="s">
+        <v>881</v>
+      </c>
+      <c r="C399" s="23"/>
+      <c r="D399" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E399" s="23" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="400" ht="15" spans="1:5">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400" s="23" t="s">
+        <v>883</v>
+      </c>
+      <c r="C400" s="23"/>
+      <c r="D400" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E400" s="23" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="401" ht="15" spans="1:5">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401" s="23" t="s">
+        <v>885</v>
+      </c>
+      <c r="C401" s="23"/>
+      <c r="D401" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E401" s="23" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="402" ht="15" spans="1:5">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402" s="23" t="s">
+        <v>887</v>
+      </c>
+      <c r="C402" s="23"/>
+      <c r="D402" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E402" s="23" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="403" ht="15" spans="1:5">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403" s="23" t="s">
+        <v>889</v>
+      </c>
+      <c r="C403" s="23"/>
+      <c r="D403" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E403" s="23" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="404" ht="15" spans="1:5">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404" s="23" t="s">
+        <v>891</v>
+      </c>
+      <c r="C404" s="23"/>
+      <c r="D404" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E404" s="23" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="405" ht="15" spans="1:5">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405" s="23" t="s">
+        <v>893</v>
+      </c>
+      <c r="C405" s="23"/>
+      <c r="D405" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E405" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="406" ht="15" spans="1:5">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406" s="23" t="s">
+        <v>895</v>
+      </c>
+      <c r="C406" s="23"/>
+      <c r="D406" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E406" s="23" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="407" ht="15" spans="1:5">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="23" t="s">
+        <v>897</v>
+      </c>
+      <c r="C407" s="23"/>
+      <c r="D407" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E407" s="23" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="408" ht="15" spans="1:5">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408" s="23" t="s">
+        <v>899</v>
+      </c>
+      <c r="C408" s="23"/>
+      <c r="D408" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E408" s="23" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="409" ht="15" spans="1:5">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409" s="23" t="s">
+        <v>901</v>
+      </c>
+      <c r="C409" s="23"/>
+      <c r="D409" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E409" s="23" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="410" ht="15" spans="1:5">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410" s="23" t="s">
+        <v>903</v>
+      </c>
+      <c r="C410" s="23"/>
+      <c r="D410" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E410" s="23" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="411" ht="15" spans="1:5">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411" s="23" t="s">
+        <v>905</v>
+      </c>
+      <c r="C411" s="23"/>
+      <c r="D411" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E411" s="23" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="412" ht="15" spans="1:5">
+      <c r="A412">
+        <v>411</v>
+      </c>
+      <c r="B412" s="23" t="s">
+        <v>907</v>
+      </c>
+      <c r="C412" s="23"/>
+      <c r="D412" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E412" s="23" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="413" ht="15" spans="1:5">
+      <c r="A413">
+        <v>412</v>
+      </c>
+      <c r="B413" s="23" t="s">
+        <v>909</v>
+      </c>
+      <c r="C413" s="23"/>
+      <c r="D413" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E413" s="23" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="414" ht="15" spans="1:5">
+      <c r="A414">
+        <v>413</v>
+      </c>
+      <c r="B414" s="23" t="s">
+        <v>911</v>
+      </c>
+      <c r="C414" s="23"/>
+      <c r="D414" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E414" s="23" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="415" ht="15" spans="1:5">
+      <c r="A415">
+        <v>414</v>
+      </c>
+      <c r="B415" s="23" t="s">
+        <v>913</v>
+      </c>
+      <c r="C415" s="23"/>
+      <c r="D415" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E415" s="23" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="416" ht="15" spans="1:5">
+      <c r="A416">
+        <v>415</v>
+      </c>
+      <c r="B416" s="23" t="s">
+        <v>915</v>
+      </c>
+      <c r="C416" s="23"/>
+      <c r="D416" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E416" s="23" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="417" ht="15" spans="1:5">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417" s="23" t="s">
+        <v>917</v>
+      </c>
+      <c r="C417" s="23"/>
+      <c r="D417" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E417" s="23" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="418" ht="15" spans="1:5">
+      <c r="A418">
+        <v>417</v>
+      </c>
+      <c r="B418" s="23" t="s">
+        <v>919</v>
+      </c>
+      <c r="C418" s="23"/>
+      <c r="D418" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E418" s="23" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="419" ht="15" spans="1:5">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419" s="23" t="s">
+        <v>921</v>
+      </c>
+      <c r="C419" s="23"/>
+      <c r="D419" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E419" s="23" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="420" ht="15" spans="1:5">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" s="23" t="s">
+        <v>923</v>
+      </c>
+      <c r="C420" s="23"/>
+      <c r="D420" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E420" s="23" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="421" ht="15" spans="1:5">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" s="23" t="s">
+        <v>925</v>
+      </c>
+      <c r="C421" s="23"/>
+      <c r="D421" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E421" s="23" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="422" ht="15" spans="1:5">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422" s="23" t="s">
+        <v>927</v>
+      </c>
+      <c r="C422" s="23"/>
+      <c r="D422" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E422" s="23" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="423" ht="15" spans="1:5">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423" s="23" t="s">
+        <v>929</v>
+      </c>
+      <c r="C423" s="23"/>
+      <c r="D423" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E423" s="23" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="424" ht="15" spans="1:5">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424" s="23" t="s">
+        <v>931</v>
+      </c>
+      <c r="C424" s="23"/>
+      <c r="D424" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E424" s="23" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="425" ht="15" spans="1:5">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425" s="23" t="s">
+        <v>933</v>
+      </c>
+      <c r="C425" s="23"/>
+      <c r="D425" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E425" s="23" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="426" ht="15" spans="1:5">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426" s="23" t="s">
+        <v>935</v>
+      </c>
+      <c r="C426" s="23"/>
+      <c r="D426" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E426" s="23" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="427" ht="15" spans="1:5">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427" s="23" t="s">
+        <v>937</v>
+      </c>
+      <c r="C427" s="23"/>
+      <c r="D427" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E427" s="23" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="428" ht="15" spans="1:5">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428" s="23" t="s">
+        <v>939</v>
+      </c>
+      <c r="C428" s="23"/>
+      <c r="D428" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E428" s="23" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="429" ht="15" spans="1:5">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" s="23" t="s">
+        <v>941</v>
+      </c>
+      <c r="C429" s="23"/>
+      <c r="D429" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E429" s="23" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="430" ht="15" spans="1:5">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" s="23" t="s">
+        <v>943</v>
+      </c>
+      <c r="C430" s="23"/>
+      <c r="D430" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E430" s="23" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="431" ht="15" spans="1:5">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431" s="23" t="s">
+        <v>945</v>
+      </c>
+      <c r="C431" s="23"/>
+      <c r="D431" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E431" s="23" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="432" ht="15" spans="1:5">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432" s="23" t="s">
+        <v>947</v>
+      </c>
+      <c r="C432" s="23"/>
+      <c r="D432" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E432" s="23" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="433" ht="15" spans="1:5">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433" s="23" t="s">
+        <v>949</v>
+      </c>
+      <c r="C433" s="23"/>
+      <c r="D433" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E433" s="23" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="434" ht="15" spans="1:5">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434" s="23" t="s">
+        <v>951</v>
+      </c>
+      <c r="C434" s="23"/>
+      <c r="D434" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E434" s="23" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="435" ht="15" spans="1:5">
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" s="23" t="s">
+        <v>953</v>
+      </c>
+      <c r="C435" s="23"/>
+      <c r="D435" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E435" s="23" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="436" ht="15" spans="1:5">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" s="23" t="s">
+        <v>955</v>
+      </c>
+      <c r="C436" s="23"/>
+      <c r="D436" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E436" s="23" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="437" ht="15" spans="1:5">
+      <c r="A437">
+        <v>436</v>
+      </c>
+      <c r="B437" s="23" t="s">
+        <v>957</v>
+      </c>
+      <c r="C437" s="23"/>
+      <c r="D437" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E437" s="23" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="438" ht="15" spans="1:5">
+      <c r="A438">
+        <v>437</v>
+      </c>
+      <c r="B438" s="23" t="s">
+        <v>959</v>
+      </c>
+      <c r="C438" s="23"/>
+      <c r="D438" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E438" s="23" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="439" ht="15" spans="1:5">
+      <c r="A439">
+        <v>438</v>
+      </c>
+      <c r="B439" s="23" t="s">
+        <v>961</v>
+      </c>
+      <c r="C439" s="23"/>
+      <c r="D439" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E439" s="23" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="440" ht="15" spans="1:5">
+      <c r="A440">
+        <v>439</v>
+      </c>
+      <c r="B440" s="23" t="s">
+        <v>963</v>
+      </c>
+      <c r="C440" s="23"/>
+      <c r="D440" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E440" s="23" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="441" ht="15" spans="1:5">
+      <c r="A441">
+        <v>440</v>
+      </c>
+      <c r="B441" s="23" t="s">
+        <v>965</v>
+      </c>
+      <c r="C441" s="23"/>
+      <c r="D441" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E441" s="23" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="442" ht="15" spans="1:5">
+      <c r="A442">
+        <v>441</v>
+      </c>
+      <c r="B442" s="23" t="s">
+        <v>967</v>
+      </c>
+      <c r="C442" s="23"/>
+      <c r="D442" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E442" s="23" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="443" ht="15" spans="1:5">
+      <c r="A443">
+        <v>442</v>
+      </c>
+      <c r="B443" s="23" t="s">
+        <v>969</v>
+      </c>
+      <c r="C443" s="23"/>
+      <c r="D443" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E443" s="23" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="444" ht="15" spans="1:5">
+      <c r="A444">
+        <v>443</v>
+      </c>
+      <c r="B444" s="23" t="s">
+        <v>971</v>
+      </c>
+      <c r="C444" s="23"/>
+      <c r="D444" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E444" s="23" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="445" ht="15" spans="1:5">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445" s="23" t="s">
+        <v>973</v>
+      </c>
+      <c r="C445" s="23"/>
+      <c r="D445" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E445" s="23" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="446" ht="15" spans="1:5">
+      <c r="A446">
+        <v>445</v>
+      </c>
+      <c r="B446" s="23" t="s">
+        <v>975</v>
+      </c>
+      <c r="C446" s="23"/>
+      <c r="D446" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E446" s="23" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="447" ht="15" spans="1:5">
+      <c r="A447">
+        <v>446</v>
+      </c>
+      <c r="B447" s="23" t="s">
+        <v>977</v>
+      </c>
+      <c r="C447" s="23"/>
+      <c r="D447" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E447" s="23" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="448" ht="15" spans="1:5">
+      <c r="A448">
+        <v>447</v>
+      </c>
+      <c r="B448" s="23" t="s">
+        <v>979</v>
+      </c>
+      <c r="C448" s="23"/>
+      <c r="D448" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E448" s="23" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="449" ht="15" spans="1:5">
+      <c r="A449">
+        <v>448</v>
+      </c>
+      <c r="B449" s="23" t="s">
+        <v>981</v>
+      </c>
+      <c r="C449" s="23"/>
+      <c r="D449" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E449" s="23" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="450" ht="15" spans="1:5">
+      <c r="A450">
+        <v>449</v>
+      </c>
+      <c r="B450" s="23" t="s">
+        <v>983</v>
+      </c>
+      <c r="C450" s="23"/>
+      <c r="D450" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E450" s="23" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="451" ht="15" spans="1:5">
+      <c r="A451">
+        <v>450</v>
+      </c>
+      <c r="B451" s="23" t="s">
+        <v>985</v>
+      </c>
+      <c r="C451" s="23"/>
+      <c r="D451" s="23" t="s">
+        <v>777</v>
+      </c>
+      <c r="E451" s="23" t="s">
+        <v>986</v>
       </c>
     </row>
   </sheetData>
@@ -8733,6 +10943,7 @@
     <hyperlink ref="E289" r:id="rId150" display="https://pan.quark.cn/s/936af0ed13b7"/>
     <hyperlink ref="E296" r:id="rId151" display="https://pan.quark.cn/s/f4ac3e17be93"/>
     <hyperlink ref="E314" r:id="rId152" display="https://pan.quark.cn/s/c928c080711b"/>
+    <hyperlink ref="E394" r:id="rId153" display="https://pan.quark.cn/s/e90ebe569558"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$453</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="1009">
   <si>
     <t>id</t>
   </si>
@@ -1448,7 +1448,7 @@
     <t>雪乡连环杀人事件</t>
   </si>
   <si>
-    <t>雪乡连环杀人事件,雪乡杀人事件</t>
+    <t>雪乡连环杀人事件,雪乡杀人事件,雪乡连环杀人案</t>
   </si>
   <si>
     <t>https://pan.quark.cn/s/cd96eb3e7191</t>
@@ -1647,6 +1647,9 @@
   </si>
   <si>
     <t>望雀</t>
+  </si>
+  <si>
+    <t>望雀,忘雀</t>
   </si>
   <si>
     <t>https://pan.quark.cn/s/1d663430e5d8</t>
@@ -1944,6 +1947,9 @@
     <t>仁馨精神病院</t>
   </si>
   <si>
+    <t>仁馨精神病院,仁馨精神医院</t>
+  </si>
+  <si>
     <t>https://pan.quark.cn/s/7238bd7db544</t>
   </si>
   <si>
@@ -3043,6 +3049,66 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/0c78700a9b55</t>
+  </si>
+  <si>
+    <t>三生三世枕上书</t>
+  </si>
+  <si>
+    <t>三生三世枕上书,枕上书</t>
+  </si>
+  <si>
+    <t>剧集,国剧,电视剧,那些回不去的年少时光,三生三世枕上书</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/fb10f2c52bb1</t>
+  </si>
+  <si>
+    <t>季风吹过橘色的海</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/1344ec35ccd0</t>
+  </si>
+  <si>
+    <t>雪乡连环杀人事件2</t>
+  </si>
+  <si>
+    <t>雪乡连环杀人事件2,雪乡杀人事件2,雪乡连环杀人案2</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/5d694cff834e</t>
+  </si>
+  <si>
+    <t>豆大点事物语</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d3b05e00c02e</t>
+  </si>
+  <si>
+    <t>盒子先生的秘密商店</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/7ffada50549b</t>
+  </si>
+  <si>
+    <t>豺狼的日子</t>
+  </si>
+  <si>
+    <t>剧集,豺狼的日子</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/8f1dba4c0f68</t>
+  </si>
+  <si>
+    <t>孤城</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e7e289b429d1</t>
+  </si>
+  <si>
+    <t>刀鞘</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c00a82990679</t>
   </si>
 </sst>
 </file>
@@ -4097,7 +4163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E451"/>
+  <dimension ref="A1:E459"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="60.75" customWidth="1"/>
@@ -4122,7 +4188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:5">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4234,7 +4300,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" ht="28" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4248,7 +4314,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" ht="28" spans="1:5">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4276,7 +4342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" ht="42" spans="1:5">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4304,7 +4370,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="28" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4360,7 +4426,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" ht="28" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4374,7 +4440,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" ht="28" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4430,7 +4496,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" ht="28" spans="1:5">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4444,7 +4510,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" ht="28" spans="1:5">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4458,7 +4524,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" ht="28" spans="1:5">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4724,7 +4790,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" ht="28" spans="1:5">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4738,7 +4804,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" ht="28" spans="1:5">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4752,7 +4818,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" ht="28" spans="1:5">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4780,7 +4846,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" ht="28" spans="1:5">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4822,7 +4888,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" ht="28" spans="1:5">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4836,7 +4902,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" ht="28" spans="1:5">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4850,7 +4916,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" ht="42" spans="1:5">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4864,7 +4930,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" ht="28" spans="1:5">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4906,7 +4972,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="58" ht="42" spans="1:5">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4934,7 +5000,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" ht="28" spans="1:5">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4962,7 +5028,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" ht="28" spans="1:5">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7507,12 +7573,14 @@
       <c r="B233" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="C233" s="10"/>
+      <c r="C233" t="s">
+        <v>539</v>
+      </c>
       <c r="D233" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E233" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="234" ht="15.5" spans="1:5">
@@ -7520,14 +7588,14 @@
         <v>233</v>
       </c>
       <c r="B234" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C234" s="10"/>
       <c r="D234" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E234" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="235" ht="15.5" spans="1:5">
@@ -7535,14 +7603,14 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="236" ht="15.5" spans="1:5">
@@ -7550,14 +7618,14 @@
         <v>235</v>
       </c>
       <c r="B236" s="16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C236" s="10"/>
       <c r="D236" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E236" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="237" ht="15.5" spans="1:5">
@@ -7565,14 +7633,14 @@
         <v>236</v>
       </c>
       <c r="B237" s="16" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E237" s="12" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="238" ht="15.5" spans="1:5">
@@ -7580,14 +7648,14 @@
         <v>237</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C238" s="10"/>
       <c r="D238" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E238" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="239" ht="15.5" spans="1:5">
@@ -7595,14 +7663,14 @@
         <v>238</v>
       </c>
       <c r="B239" s="16" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E239" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="240" ht="15.5" spans="1:5">
@@ -7610,14 +7678,14 @@
         <v>239</v>
       </c>
       <c r="B240" s="16" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C240" s="10"/>
       <c r="D240" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="241" ht="15.5" spans="1:5">
@@ -7625,14 +7693,14 @@
         <v>240</v>
       </c>
       <c r="B241" s="16" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C241" s="10"/>
       <c r="D241" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E241" s="13" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="242" ht="15.5" spans="1:5">
@@ -7640,14 +7708,14 @@
         <v>241</v>
       </c>
       <c r="B242" s="16" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C242" s="10"/>
       <c r="D242" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E242" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -7655,13 +7723,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D243" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E243" s="13" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -7669,13 +7737,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D244" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E244" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="245" ht="15.5" spans="1:5">
@@ -7683,14 +7751,14 @@
         <v>244</v>
       </c>
       <c r="B245" s="13" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C245" s="10"/>
       <c r="D245" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E245" s="13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="246" ht="15.5" spans="1:5">
@@ -7698,14 +7766,14 @@
         <v>245</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C246" s="10"/>
       <c r="D246" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E246" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="247" ht="15.5" spans="1:5">
@@ -7713,14 +7781,14 @@
         <v>246</v>
       </c>
       <c r="B247" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C247" s="10"/>
       <c r="D247" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E247" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="248" ht="15.5" spans="1:5">
@@ -7728,14 +7796,14 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C248" s="10"/>
       <c r="D248" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E248" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="249" ht="15.5" spans="1:5">
@@ -7743,14 +7811,14 @@
         <v>248</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C249" s="10"/>
       <c r="D249" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E249" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="250" ht="15.5" spans="1:5">
@@ -7758,14 +7826,14 @@
         <v>249</v>
       </c>
       <c r="B250" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C250" s="10"/>
       <c r="D250" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="251" ht="15.5" spans="1:5">
@@ -7773,14 +7841,14 @@
         <v>250</v>
       </c>
       <c r="B251" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C251" s="10"/>
       <c r="D251" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E251" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="252" ht="15.5" spans="1:5">
@@ -7788,14 +7856,14 @@
         <v>251</v>
       </c>
       <c r="B252" s="20" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C252" s="10"/>
       <c r="D252" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E252" s="13" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="253" ht="15.5" spans="1:5">
@@ -7803,14 +7871,14 @@
         <v>252</v>
       </c>
       <c r="B253" s="13" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C253" s="10"/>
       <c r="D253" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E253" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="254" ht="15.5" spans="1:5">
@@ -7818,14 +7886,14 @@
         <v>253</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C254" s="10"/>
       <c r="D254" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E254" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="255" ht="15.5" spans="1:5">
@@ -7833,16 +7901,16 @@
         <v>254</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D255" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E255" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="256" ht="15.5" spans="1:5">
@@ -7850,14 +7918,14 @@
         <v>255</v>
       </c>
       <c r="B256" s="20" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C256" s="10"/>
       <c r="D256" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E256" s="13" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="257" ht="15.5" spans="1:5">
@@ -7865,14 +7933,14 @@
         <v>256</v>
       </c>
       <c r="B257" s="13" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C257" s="10"/>
       <c r="D257" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E257" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="258" ht="15.5" spans="1:5">
@@ -7880,14 +7948,14 @@
         <v>257</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C258" s="10"/>
       <c r="D258" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E258" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="259" ht="15.5" spans="1:5">
@@ -7895,14 +7963,14 @@
         <v>258</v>
       </c>
       <c r="B259" s="13" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C259" s="10"/>
       <c r="D259" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E259" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="260" ht="15.5" spans="1:5">
@@ -7910,14 +7978,14 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C260" s="10"/>
       <c r="D260" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E260" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="261" ht="15.5" spans="1:5">
@@ -7925,14 +7993,14 @@
         <v>260</v>
       </c>
       <c r="B261" s="20" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C261" s="10"/>
       <c r="D261" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E261" s="13" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="262" ht="15.5" spans="1:5">
@@ -7940,14 +8008,14 @@
         <v>261</v>
       </c>
       <c r="B262" s="16" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C262" s="10"/>
       <c r="D262" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E262" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="263" ht="15.5" spans="1:5">
@@ -7955,14 +8023,14 @@
         <v>262</v>
       </c>
       <c r="B263" s="13" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C263" s="10"/>
       <c r="D263" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E263" s="12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="264" ht="15.5" spans="1:5">
@@ -7970,14 +8038,14 @@
         <v>263</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C264" s="10"/>
       <c r="D264" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E264" s="13" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="265" ht="15.5" spans="1:5">
@@ -7985,14 +8053,14 @@
         <v>264</v>
       </c>
       <c r="B265" s="13" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C265" s="10"/>
       <c r="D265" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E265" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="266" ht="15.5" spans="1:5">
@@ -8000,14 +8068,14 @@
         <v>265</v>
       </c>
       <c r="B266" s="17" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C266" s="10"/>
       <c r="D266" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E266" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="267" ht="15.5" spans="1:5">
@@ -8015,16 +8083,16 @@
         <v>266</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D267" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="268" ht="15.5" spans="1:5">
@@ -8032,14 +8100,14 @@
         <v>267</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C268" s="10"/>
       <c r="D268" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E268" s="13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="269" ht="15.5" spans="1:5">
@@ -8047,14 +8115,14 @@
         <v>268</v>
       </c>
       <c r="B269" s="13" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C269" s="10"/>
       <c r="D269" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E269" s="13" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="270" ht="15.5" spans="1:5">
@@ -8062,14 +8130,14 @@
         <v>269</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C270" s="10"/>
       <c r="D270" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E270" s="13" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="271" ht="15.5" spans="1:5">
@@ -8077,29 +8145,31 @@
         <v>270</v>
       </c>
       <c r="B271" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C271" s="10"/>
       <c r="D271" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E271" s="13" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="272" ht="15.5" spans="1:5">
       <c r="A272">
         <v>271</v>
       </c>
-      <c r="B272" s="13" t="s">
-        <v>619</v>
-      </c>
-      <c r="C272" s="10"/>
+      <c r="B272" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="C272" s="10" t="s">
+        <v>621</v>
+      </c>
       <c r="D272" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E272" s="13" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="273" ht="15.5" spans="1:5">
@@ -8107,14 +8177,14 @@
         <v>272</v>
       </c>
       <c r="B273" s="13" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C273" s="10"/>
       <c r="D273" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E273" s="13" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="274" ht="15.5" spans="1:5">
@@ -8122,14 +8192,14 @@
         <v>273</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C274" s="10"/>
       <c r="D274" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E274" s="13" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="275" ht="15.5" spans="1:5">
@@ -8137,14 +8207,14 @@
         <v>274</v>
       </c>
       <c r="B275" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C275" s="10"/>
       <c r="D275" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E275" s="13" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="276" ht="15.5" spans="1:5">
@@ -8152,14 +8222,14 @@
         <v>275</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C276" s="10"/>
       <c r="D276" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E276" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="277" ht="15.5" spans="1:5">
@@ -8167,14 +8237,14 @@
         <v>276</v>
       </c>
       <c r="B277" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C277" s="10"/>
       <c r="D277" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E277" s="13" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="278" ht="15.5" spans="1:5">
@@ -8182,14 +8252,14 @@
         <v>277</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C278" s="10"/>
       <c r="D278" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E278" s="13" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="279" ht="15.5" spans="1:5">
@@ -8197,14 +8267,14 @@
         <v>278</v>
       </c>
       <c r="B279" s="13" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C279" s="10"/>
       <c r="D279" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E279" s="13" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="280" ht="15.5" spans="1:5">
@@ -8212,14 +8282,14 @@
         <v>279</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C280" s="10"/>
       <c r="D280" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E280" s="13" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="281" ht="15.5" spans="1:5">
@@ -8227,14 +8297,14 @@
         <v>280</v>
       </c>
       <c r="B281" s="13" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C281" s="10"/>
       <c r="D281" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E281" s="13" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="282" ht="15.5" spans="1:5">
@@ -8242,14 +8312,14 @@
         <v>281</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C282" s="10"/>
       <c r="D282" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E282" s="13" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="283" ht="15.5" spans="1:5">
@@ -8257,14 +8327,14 @@
         <v>282</v>
       </c>
       <c r="B283" s="13" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C283" s="10"/>
       <c r="D283" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="284" ht="15.5" spans="1:5">
@@ -8272,14 +8342,14 @@
         <v>283</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C284" s="10"/>
       <c r="D284" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E284" s="13" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="285" ht="15.5" spans="1:5">
@@ -8287,14 +8357,14 @@
         <v>284</v>
       </c>
       <c r="B285" s="13" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C285" s="10"/>
       <c r="D285" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="286" ht="15.5" spans="1:5">
@@ -8302,14 +8372,14 @@
         <v>285</v>
       </c>
       <c r="B286" s="17" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C286" s="10"/>
       <c r="D286" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E286" s="13" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="287" ht="15.5" spans="1:5">
@@ -8317,14 +8387,14 @@
         <v>286</v>
       </c>
       <c r="B287" s="13" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C287" s="10"/>
       <c r="D287" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E287" s="13" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="288" ht="15.5" spans="1:5">
@@ -8332,14 +8402,14 @@
         <v>287</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C288" s="10"/>
       <c r="D288" s="10" t="s">
         <v>180</v>
       </c>
       <c r="E288" s="13" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="289" ht="15" spans="1:5">
@@ -8347,14 +8417,14 @@
         <v>288</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C289" s="8"/>
       <c r="D289" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="290" ht="15" spans="1:5">
@@ -8362,14 +8432,14 @@
         <v>289</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C290" s="8"/>
       <c r="D290" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E290" s="8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="291" ht="15" spans="1:5">
@@ -8377,16 +8447,16 @@
         <v>290</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D291" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E291" s="8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="292" ht="15" spans="1:5">
@@ -8394,14 +8464,14 @@
         <v>291</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C292" s="8"/>
       <c r="D292" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E292" s="8" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="293" ht="15" spans="1:5">
@@ -8409,13 +8479,13 @@
         <v>292</v>
       </c>
       <c r="B293" s="13" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D293" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E293" s="13" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="294" ht="15" spans="1:5">
@@ -8423,13 +8493,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D294" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E294" s="13" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="295" ht="15" spans="1:5">
@@ -8437,13 +8507,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="13" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D295" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E295" s="13" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="296" ht="15" spans="1:5">
@@ -8451,13 +8521,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D296" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E296" s="12" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="297" ht="15" spans="1:5">
@@ -8465,14 +8535,14 @@
         <v>296</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C297" s="8"/>
       <c r="D297" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E297" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="298" ht="15" spans="1:5">
@@ -8480,14 +8550,14 @@
         <v>297</v>
       </c>
       <c r="B298" s="8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C298" s="8"/>
       <c r="D298" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E298" s="8" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="299" ht="15" spans="1:5">
@@ -8495,14 +8565,14 @@
         <v>298</v>
       </c>
       <c r="B299" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C299" s="8"/>
       <c r="D299" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E299" s="8" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="300" ht="15" spans="1:5">
@@ -8510,14 +8580,14 @@
         <v>299</v>
       </c>
       <c r="B300" s="8" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C300" s="8"/>
       <c r="D300" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E300" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="301" ht="15" spans="1:5">
@@ -8525,14 +8595,14 @@
         <v>300</v>
       </c>
       <c r="B301" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C301" s="8"/>
       <c r="D301" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E301" s="8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="302" ht="15" spans="1:5">
@@ -8540,14 +8610,14 @@
         <v>301</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C302" s="8"/>
       <c r="D302" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E302" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="303" ht="15" spans="1:5">
@@ -8555,16 +8625,16 @@
         <v>302</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C303" s="8" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D303" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E303" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="304" ht="15" spans="1:5">
@@ -8572,14 +8642,14 @@
         <v>303</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C304" s="8"/>
       <c r="D304" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E304" s="8" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="305" ht="15" spans="1:5">
@@ -8587,14 +8657,14 @@
         <v>304</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C305" s="8"/>
       <c r="D305" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E305" s="8" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="306" ht="15" spans="1:5">
@@ -8602,14 +8672,14 @@
         <v>305</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C306" s="8"/>
       <c r="D306" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E306" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="307" ht="15" spans="1:5">
@@ -8617,14 +8687,14 @@
         <v>306</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C307" s="8"/>
       <c r="D307" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E307" s="8" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="308" ht="15" spans="1:5">
@@ -8632,14 +8702,14 @@
         <v>307</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C308" s="8"/>
       <c r="D308" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E308" s="8" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="309" ht="15" spans="1:5">
@@ -8647,14 +8717,14 @@
         <v>308</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C309" s="8"/>
       <c r="D309" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E309" s="8" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="310" ht="15" spans="1:5">
@@ -8662,14 +8732,14 @@
         <v>309</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C310" s="8"/>
       <c r="D310" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E310" s="8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="311" ht="15" spans="1:5">
@@ -8677,14 +8747,14 @@
         <v>310</v>
       </c>
       <c r="B311" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C311" s="8"/>
       <c r="D311" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E311" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="312" ht="15" spans="1:5">
@@ -8692,14 +8762,14 @@
         <v>311</v>
       </c>
       <c r="B312" s="8" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C312" s="8"/>
       <c r="D312" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E312" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="313" ht="15" spans="1:5">
@@ -8707,13 +8777,13 @@
         <v>312</v>
       </c>
       <c r="B313" s="13" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D313" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E313" s="13" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="314" ht="15" spans="1:5">
@@ -8721,13 +8791,13 @@
         <v>313</v>
       </c>
       <c r="B314" s="17" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D314" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E314" s="12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="315" ht="15" spans="1:5">
@@ -8735,13 +8805,13 @@
         <v>314</v>
       </c>
       <c r="B315" s="17" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D315" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E315" s="13" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="316" ht="15" spans="1:5">
@@ -8749,13 +8819,13 @@
         <v>315</v>
       </c>
       <c r="B316" s="17" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D316" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E316" s="13" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="317" ht="15" spans="1:5">
@@ -8763,14 +8833,14 @@
         <v>316</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C317" s="8"/>
       <c r="D317" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E317" s="8" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="318" ht="15" spans="1:5">
@@ -8778,14 +8848,14 @@
         <v>317</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C318" s="8"/>
       <c r="D318" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="319" ht="15" spans="1:5">
@@ -8793,14 +8863,14 @@
         <v>318</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C319" s="8"/>
       <c r="D319" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E319" s="8" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="320" ht="15" spans="1:5">
@@ -8808,14 +8878,14 @@
         <v>319</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C320" s="8"/>
       <c r="D320" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E320" s="8" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="321" ht="15" spans="1:5">
@@ -8823,14 +8893,14 @@
         <v>320</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C321" s="8"/>
       <c r="D321" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E321" s="8" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="322" ht="15" spans="1:5">
@@ -8838,14 +8908,14 @@
         <v>321</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C322" s="8"/>
       <c r="D322" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E322" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="323" ht="15" spans="1:5">
@@ -8853,14 +8923,14 @@
         <v>322</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C323" s="8"/>
       <c r="D323" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E323" s="8" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="324" ht="15" spans="1:5">
@@ -8868,14 +8938,14 @@
         <v>323</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C324" s="8"/>
       <c r="D324" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E324" s="8" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="325" ht="15" spans="1:5">
@@ -8883,14 +8953,14 @@
         <v>324</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C325" s="8"/>
       <c r="D325" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E325" s="8" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="326" ht="15" spans="1:5">
@@ -8898,14 +8968,14 @@
         <v>325</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C326" s="8"/>
       <c r="D326" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E326" s="8" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="327" ht="15" spans="1:5">
@@ -8913,14 +8983,14 @@
         <v>326</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C327" s="8"/>
       <c r="D327" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E327" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="328" ht="15" spans="1:5">
@@ -8928,14 +8998,14 @@
         <v>327</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C328" s="8"/>
       <c r="D328" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E328" s="8" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="329" ht="15" spans="1:5">
@@ -8943,14 +9013,14 @@
         <v>328</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C329" s="8"/>
       <c r="D329" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E329" s="8" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="330" ht="15" spans="1:5">
@@ -8958,14 +9028,14 @@
         <v>329</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C330" s="8"/>
       <c r="D330" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E330" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="331" ht="15" spans="1:5">
@@ -8973,14 +9043,14 @@
         <v>330</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C331" s="8"/>
       <c r="D331" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E331" s="8" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="332" ht="15" spans="1:5">
@@ -8988,14 +9058,14 @@
         <v>331</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C332" s="8"/>
       <c r="D332" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E332" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="333" ht="15" spans="1:5">
@@ -9003,14 +9073,14 @@
         <v>332</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C333" s="8"/>
       <c r="D333" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E333" s="8" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="334" ht="15" spans="1:5">
@@ -9018,14 +9088,14 @@
         <v>333</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C334" s="8"/>
       <c r="D334" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E334" s="8" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="335" ht="15" spans="1:5">
@@ -9033,14 +9103,14 @@
         <v>334</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C335" s="8"/>
       <c r="D335" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E335" s="8" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="336" ht="15" spans="1:5">
@@ -9048,14 +9118,14 @@
         <v>335</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C336" s="8"/>
       <c r="D336" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E336" s="8" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="337" ht="15" spans="1:5">
@@ -9063,14 +9133,14 @@
         <v>336</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C337" s="8"/>
       <c r="D337" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E337" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="338" ht="15" spans="1:5">
@@ -9078,14 +9148,14 @@
         <v>337</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C338" s="8"/>
       <c r="D338" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E338" s="8" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="339" ht="15" spans="1:5">
@@ -9093,14 +9163,14 @@
         <v>338</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C339" s="8"/>
       <c r="D339" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E339" s="8" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="340" ht="15" spans="1:5">
@@ -9108,14 +9178,14 @@
         <v>339</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C340" s="8"/>
       <c r="D340" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E340" s="8" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="341" ht="15" spans="1:5">
@@ -9123,14 +9193,14 @@
         <v>340</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C341" s="8"/>
       <c r="D341" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E341" s="8" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="342" ht="15" spans="1:5">
@@ -9138,14 +9208,14 @@
         <v>341</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C342" s="8"/>
       <c r="D342" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E342" s="8" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="343" ht="15" spans="1:5">
@@ -9153,14 +9223,14 @@
         <v>342</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C343" s="8"/>
       <c r="D343" s="8" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E343" s="8" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -9168,16 +9238,16 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C344" s="16" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D344" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -9185,13 +9255,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D345" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="346" ht="15" spans="1:5">
@@ -9199,1595 +9269,1714 @@
         <v>345</v>
       </c>
       <c r="B346" s="17" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C346" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D346" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E346" s="22" t="s">
-        <v>775</v>
+      <c r="E346" s="13" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="347" ht="15" spans="1:5">
       <c r="A347">
         <v>346</v>
       </c>
-      <c r="B347" s="23" t="s">
-        <v>776</v>
-      </c>
-      <c r="C347" s="23"/>
-      <c r="D347" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E347" s="23" t="s">
+      <c r="B347" s="8" t="s">
         <v>778</v>
+      </c>
+      <c r="C347" s="8"/>
+      <c r="D347" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E347" s="8" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="348" ht="15" spans="1:5">
       <c r="A348">
         <v>347</v>
       </c>
-      <c r="B348" s="23" t="s">
+      <c r="B348" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="C348" s="8"/>
+      <c r="D348" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="C348" s="23"/>
-      <c r="D348" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E348" s="23" t="s">
-        <v>780</v>
+      <c r="E348" s="8" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="349" ht="15" spans="1:5">
       <c r="A349">
         <v>348</v>
       </c>
-      <c r="B349" s="23" t="s">
-        <v>781</v>
-      </c>
-      <c r="C349" s="23"/>
-      <c r="D349" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E349" s="23" t="s">
-        <v>782</v>
+      <c r="B349" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C349" s="8"/>
+      <c r="D349" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E349" s="8" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="350" ht="15" spans="1:5">
       <c r="A350">
         <v>349</v>
       </c>
-      <c r="B350" s="23" t="s">
-        <v>783</v>
-      </c>
-      <c r="C350" s="23"/>
-      <c r="D350" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E350" s="23" t="s">
-        <v>784</v>
+      <c r="B350" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="C350" s="8"/>
+      <c r="D350" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E350" s="8" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="351" ht="15" spans="1:5">
       <c r="A351">
         <v>350</v>
       </c>
-      <c r="B351" s="23" t="s">
-        <v>785</v>
-      </c>
-      <c r="C351" s="23"/>
-      <c r="D351" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E351" s="23" t="s">
-        <v>786</v>
+      <c r="B351" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="C351" s="8"/>
+      <c r="D351" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E351" s="8" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="352" ht="15" spans="1:5">
       <c r="A352">
         <v>351</v>
       </c>
-      <c r="B352" s="23" t="s">
-        <v>787</v>
-      </c>
-      <c r="C352" s="23"/>
-      <c r="D352" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E352" s="23" t="s">
-        <v>788</v>
+      <c r="B352" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="C352" s="8"/>
+      <c r="D352" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E352" s="8" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="353" ht="15" spans="1:5">
       <c r="A353">
         <v>352</v>
       </c>
-      <c r="B353" s="23" t="s">
-        <v>789</v>
-      </c>
-      <c r="C353" s="23"/>
-      <c r="D353" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E353" s="23" t="s">
-        <v>790</v>
+      <c r="B353" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="C353" s="8"/>
+      <c r="D353" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E353" s="8" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="354" ht="15" spans="1:5">
       <c r="A354">
         <v>353</v>
       </c>
-      <c r="B354" s="23" t="s">
-        <v>791</v>
-      </c>
-      <c r="C354" s="23"/>
-      <c r="D354" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E354" s="23" t="s">
-        <v>792</v>
+      <c r="B354" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C354" s="8"/>
+      <c r="D354" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E354" s="8" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="355" ht="15" spans="1:5">
       <c r="A355">
         <v>354</v>
       </c>
-      <c r="B355" s="23" t="s">
-        <v>793</v>
-      </c>
-      <c r="C355" s="23"/>
-      <c r="D355" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E355" s="23" t="s">
-        <v>794</v>
+      <c r="B355" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="C355" s="8"/>
+      <c r="D355" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E355" s="8" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="356" ht="15" spans="1:5">
       <c r="A356">
         <v>355</v>
       </c>
-      <c r="B356" s="23" t="s">
-        <v>795</v>
-      </c>
-      <c r="C356" s="23"/>
-      <c r="D356" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E356" s="23" t="s">
-        <v>796</v>
+      <c r="B356" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="C356" s="8"/>
+      <c r="D356" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E356" s="8" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="357" ht="15" spans="1:5">
       <c r="A357">
         <v>356</v>
       </c>
-      <c r="B357" s="23" t="s">
-        <v>797</v>
-      </c>
-      <c r="C357" s="23"/>
-      <c r="D357" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E357" s="23" t="s">
-        <v>798</v>
+      <c r="B357" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="C357" s="8"/>
+      <c r="D357" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E357" s="8" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="358" ht="15" spans="1:5">
       <c r="A358">
         <v>357</v>
       </c>
-      <c r="B358" s="23" t="s">
-        <v>799</v>
-      </c>
-      <c r="C358" s="23"/>
-      <c r="D358" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E358" s="23" t="s">
-        <v>800</v>
+      <c r="B358" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="C358" s="8"/>
+      <c r="D358" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E358" s="8" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="359" ht="15" spans="1:5">
       <c r="A359">
         <v>358</v>
       </c>
-      <c r="B359" s="23" t="s">
-        <v>801</v>
-      </c>
-      <c r="C359" s="23"/>
-      <c r="D359" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E359" s="23" t="s">
-        <v>802</v>
+      <c r="B359" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="C359" s="8"/>
+      <c r="D359" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E359" s="8" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="360" ht="15" spans="1:5">
       <c r="A360">
         <v>359</v>
       </c>
-      <c r="B360" s="23" t="s">
-        <v>803</v>
-      </c>
-      <c r="C360" s="23"/>
-      <c r="D360" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E360" s="23" t="s">
-        <v>804</v>
+      <c r="B360" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C360" s="8"/>
+      <c r="D360" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E360" s="8" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="361" ht="15" spans="1:5">
       <c r="A361">
         <v>360</v>
       </c>
-      <c r="B361" s="23" t="s">
-        <v>805</v>
-      </c>
-      <c r="C361" s="23"/>
-      <c r="D361" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E361" s="23" t="s">
-        <v>806</v>
+      <c r="B361" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C361" s="8"/>
+      <c r="D361" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E361" s="8" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="362" ht="15" spans="1:5">
       <c r="A362">
         <v>361</v>
       </c>
-      <c r="B362" s="23" t="s">
-        <v>807</v>
-      </c>
-      <c r="C362" s="23"/>
-      <c r="D362" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E362" s="23" t="s">
-        <v>808</v>
+      <c r="B362" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="C362" s="8"/>
+      <c r="D362" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E362" s="8" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="363" ht="15" spans="1:5">
       <c r="A363">
         <v>362</v>
       </c>
-      <c r="B363" s="23" t="s">
-        <v>809</v>
-      </c>
-      <c r="C363" s="23"/>
-      <c r="D363" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E363" s="23" t="s">
-        <v>810</v>
+      <c r="B363" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="C363" s="8"/>
+      <c r="D363" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E363" s="8" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="364" ht="15" spans="1:5">
       <c r="A364">
         <v>363</v>
       </c>
-      <c r="B364" s="23" t="s">
-        <v>811</v>
-      </c>
-      <c r="C364" s="23"/>
-      <c r="D364" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E364" s="23" t="s">
-        <v>812</v>
+      <c r="B364" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C364" s="8"/>
+      <c r="D364" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E364" s="8" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="365" ht="15" spans="1:5">
       <c r="A365">
         <v>364</v>
       </c>
-      <c r="B365" s="23" t="s">
-        <v>813</v>
-      </c>
-      <c r="C365" s="23"/>
-      <c r="D365" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E365" s="23" t="s">
-        <v>814</v>
+      <c r="B365" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="C365" s="8"/>
+      <c r="D365" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E365" s="8" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="366" ht="15" spans="1:5">
       <c r="A366">
         <v>365</v>
       </c>
-      <c r="B366" s="23" t="s">
-        <v>815</v>
-      </c>
-      <c r="C366" s="23"/>
-      <c r="D366" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E366" s="23" t="s">
-        <v>816</v>
+      <c r="B366" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="C366" s="8"/>
+      <c r="D366" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E366" s="8" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="367" ht="15" spans="1:5">
       <c r="A367">
         <v>366</v>
       </c>
-      <c r="B367" s="23" t="s">
-        <v>817</v>
-      </c>
-      <c r="C367" s="23"/>
-      <c r="D367" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E367" s="23" t="s">
-        <v>818</v>
+      <c r="B367" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="C367" s="8"/>
+      <c r="D367" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E367" s="8" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="368" ht="15" spans="1:5">
       <c r="A368">
         <v>367</v>
       </c>
-      <c r="B368" s="23" t="s">
-        <v>819</v>
-      </c>
-      <c r="C368" s="23"/>
-      <c r="D368" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E368" s="23" t="s">
-        <v>820</v>
+      <c r="B368" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C368" s="8"/>
+      <c r="D368" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E368" s="8" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="369" ht="15" spans="1:5">
       <c r="A369">
         <v>368</v>
       </c>
-      <c r="B369" s="23" t="s">
-        <v>821</v>
-      </c>
-      <c r="C369" s="23"/>
-      <c r="D369" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E369" s="23" t="s">
-        <v>822</v>
+      <c r="B369" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="C369" s="8"/>
+      <c r="D369" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E369" s="8" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="370" ht="15" spans="1:5">
       <c r="A370">
         <v>369</v>
       </c>
-      <c r="B370" s="23" t="s">
-        <v>823</v>
-      </c>
-      <c r="C370" s="23"/>
-      <c r="D370" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E370" s="23" t="s">
-        <v>824</v>
+      <c r="B370" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="C370" s="8"/>
+      <c r="D370" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E370" s="8" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="371" ht="15" spans="1:5">
       <c r="A371">
         <v>370</v>
       </c>
-      <c r="B371" s="23" t="s">
-        <v>825</v>
-      </c>
-      <c r="C371" s="23"/>
-      <c r="D371" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E371" s="23" t="s">
-        <v>826</v>
+      <c r="B371" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="C371" s="8"/>
+      <c r="D371" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E371" s="8" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="372" ht="15" spans="1:5">
       <c r="A372">
         <v>371</v>
       </c>
-      <c r="B372" s="23" t="s">
-        <v>827</v>
-      </c>
-      <c r="C372" s="23"/>
-      <c r="D372" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E372" s="23" t="s">
-        <v>828</v>
+      <c r="B372" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="C372" s="8"/>
+      <c r="D372" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E372" s="8" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="373" ht="15" spans="1:5">
       <c r="A373">
         <v>372</v>
       </c>
-      <c r="B373" s="23" t="s">
-        <v>829</v>
-      </c>
-      <c r="C373" s="23"/>
-      <c r="D373" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E373" s="23" t="s">
-        <v>830</v>
+      <c r="B373" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="C373" s="8"/>
+      <c r="D373" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E373" s="8" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="374" ht="15" spans="1:5">
       <c r="A374">
         <v>373</v>
       </c>
-      <c r="B374" s="23" t="s">
-        <v>831</v>
-      </c>
-      <c r="C374" s="23"/>
-      <c r="D374" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E374" s="23" t="s">
-        <v>832</v>
+      <c r="B374" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C374" s="8"/>
+      <c r="D374" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E374" s="8" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="375" ht="15" spans="1:5">
       <c r="A375">
         <v>374</v>
       </c>
-      <c r="B375" s="23" t="s">
-        <v>833</v>
-      </c>
-      <c r="C375" s="23"/>
-      <c r="D375" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E375" s="23" t="s">
-        <v>834</v>
+      <c r="B375" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C375" s="8"/>
+      <c r="D375" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E375" s="8" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="376" ht="15" spans="1:5">
       <c r="A376">
         <v>375</v>
       </c>
-      <c r="B376" s="23" t="s">
-        <v>835</v>
-      </c>
-      <c r="C376" s="23"/>
-      <c r="D376" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E376" s="23" t="s">
-        <v>836</v>
+      <c r="B376" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C376" s="8"/>
+      <c r="D376" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E376" s="8" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="377" ht="15" spans="1:5">
       <c r="A377">
         <v>376</v>
       </c>
-      <c r="B377" s="23" t="s">
-        <v>837</v>
-      </c>
-      <c r="C377" s="23"/>
-      <c r="D377" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E377" s="23" t="s">
-        <v>838</v>
+      <c r="B377" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="C377" s="8"/>
+      <c r="D377" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E377" s="8" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="378" ht="15" spans="1:5">
       <c r="A378">
         <v>377</v>
       </c>
-      <c r="B378" s="23" t="s">
-        <v>839</v>
-      </c>
-      <c r="C378" s="23"/>
-      <c r="D378" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E378" s="23" t="s">
-        <v>840</v>
+      <c r="B378" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="C378" s="8"/>
+      <c r="D378" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E378" s="8" t="s">
+        <v>842</v>
       </c>
     </row>
     <row r="379" ht="15" spans="1:5">
       <c r="A379">
         <v>378</v>
       </c>
-      <c r="B379" s="23" t="s">
-        <v>841</v>
-      </c>
-      <c r="C379" s="23"/>
-      <c r="D379" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E379" s="23" t="s">
-        <v>842</v>
+      <c r="B379" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="C379" s="8"/>
+      <c r="D379" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E379" s="8" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="380" ht="15" spans="1:5">
       <c r="A380">
         <v>379</v>
       </c>
-      <c r="B380" s="23" t="s">
-        <v>843</v>
-      </c>
-      <c r="C380" s="23"/>
-      <c r="D380" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E380" s="23" t="s">
-        <v>844</v>
+      <c r="B380" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="C380" s="8"/>
+      <c r="D380" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E380" s="8" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="381" ht="15" spans="1:5">
       <c r="A381">
         <v>380</v>
       </c>
-      <c r="B381" s="23" t="s">
-        <v>845</v>
-      </c>
-      <c r="C381" s="23"/>
-      <c r="D381" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E381" s="23" t="s">
-        <v>846</v>
+      <c r="B381" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="C381" s="8"/>
+      <c r="D381" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E381" s="8" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="382" ht="15" spans="1:5">
       <c r="A382">
         <v>381</v>
       </c>
-      <c r="B382" s="23" t="s">
-        <v>847</v>
-      </c>
-      <c r="C382" s="23"/>
-      <c r="D382" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E382" s="23" t="s">
-        <v>848</v>
+      <c r="B382" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="C382" s="8"/>
+      <c r="D382" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E382" s="8" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="383" ht="15" spans="1:5">
       <c r="A383">
         <v>382</v>
       </c>
-      <c r="B383" s="23" t="s">
-        <v>849</v>
-      </c>
-      <c r="C383" s="23"/>
-      <c r="D383" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E383" s="23" t="s">
-        <v>850</v>
+      <c r="B383" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="C383" s="8"/>
+      <c r="D383" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E383" s="8" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="384" ht="15" spans="1:5">
       <c r="A384">
         <v>383</v>
       </c>
-      <c r="B384" s="23" t="s">
-        <v>851</v>
-      </c>
-      <c r="C384" s="23"/>
-      <c r="D384" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E384" s="23" t="s">
-        <v>852</v>
+      <c r="B384" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C384" s="8"/>
+      <c r="D384" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E384" s="8" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="385" ht="15" spans="1:5">
       <c r="A385">
         <v>384</v>
       </c>
-      <c r="B385" s="23" t="s">
-        <v>853</v>
-      </c>
-      <c r="C385" s="23"/>
-      <c r="D385" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E385" s="23" t="s">
-        <v>854</v>
+      <c r="B385" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="C385" s="8"/>
+      <c r="D385" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E385" s="8" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="386" ht="15" spans="1:5">
       <c r="A386">
         <v>385</v>
       </c>
-      <c r="B386" s="23" t="s">
-        <v>855</v>
-      </c>
-      <c r="C386" s="23"/>
-      <c r="D386" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E386" s="23" t="s">
-        <v>856</v>
+      <c r="B386" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="C386" s="8"/>
+      <c r="D386" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E386" s="8" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="387" ht="15" spans="1:5">
       <c r="A387">
         <v>386</v>
       </c>
-      <c r="B387" s="23" t="s">
-        <v>857</v>
-      </c>
-      <c r="C387" s="23"/>
-      <c r="D387" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E387" s="23" t="s">
-        <v>858</v>
+      <c r="B387" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="C387" s="8"/>
+      <c r="D387" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E387" s="8" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="388" ht="15" spans="1:5">
       <c r="A388">
         <v>387</v>
       </c>
-      <c r="B388" s="23" t="s">
-        <v>859</v>
-      </c>
-      <c r="C388" s="23"/>
-      <c r="D388" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E388" s="23" t="s">
-        <v>860</v>
+      <c r="B388" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C388" s="8"/>
+      <c r="D388" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E388" s="8" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="389" ht="15" spans="1:5">
       <c r="A389">
         <v>388</v>
       </c>
-      <c r="B389" s="23" t="s">
-        <v>861</v>
-      </c>
-      <c r="C389" s="23"/>
-      <c r="D389" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E389" s="23" t="s">
-        <v>862</v>
+      <c r="B389" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="C389" s="8"/>
+      <c r="D389" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E389" s="8" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="390" ht="15" spans="1:5">
       <c r="A390">
         <v>389</v>
       </c>
-      <c r="B390" s="23" t="s">
-        <v>863</v>
-      </c>
-      <c r="C390" s="23"/>
-      <c r="D390" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E390" s="23" t="s">
-        <v>864</v>
+      <c r="B390" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="C390" s="8"/>
+      <c r="D390" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E390" s="8" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="391" ht="15" spans="1:5">
       <c r="A391">
         <v>390</v>
       </c>
-      <c r="B391" s="23" t="s">
-        <v>865</v>
-      </c>
-      <c r="C391" s="23"/>
-      <c r="D391" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E391" s="23" t="s">
-        <v>866</v>
+      <c r="B391" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="C391" s="8"/>
+      <c r="D391" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E391" s="8" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="392" ht="15" spans="1:5">
       <c r="A392">
         <v>391</v>
       </c>
-      <c r="B392" s="23" t="s">
-        <v>867</v>
-      </c>
-      <c r="C392" s="23"/>
-      <c r="D392" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E392" s="23" t="s">
-        <v>868</v>
+      <c r="B392" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="C392" s="8"/>
+      <c r="D392" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E392" s="8" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="393" ht="15" spans="1:5">
       <c r="A393">
         <v>392</v>
       </c>
-      <c r="B393" s="23" t="s">
-        <v>869</v>
-      </c>
-      <c r="C393" s="23"/>
-      <c r="D393" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E393" s="23" t="s">
-        <v>870</v>
+      <c r="B393" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C393" s="8"/>
+      <c r="D393" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E393" s="8" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="394" ht="15" spans="1:5">
       <c r="A394">
         <v>393</v>
       </c>
-      <c r="B394" s="23" t="s">
-        <v>871</v>
-      </c>
-      <c r="C394" s="23"/>
-      <c r="D394" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E394" s="24" t="s">
-        <v>872</v>
+      <c r="B394" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="C394" s="8"/>
+      <c r="D394" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E394" s="21" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="395" ht="15" spans="1:5">
       <c r="A395">
         <v>394</v>
       </c>
-      <c r="B395" s="23" t="s">
-        <v>873</v>
-      </c>
-      <c r="C395" s="23"/>
-      <c r="D395" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E395" s="23" t="s">
-        <v>874</v>
+      <c r="B395" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="C395" s="8"/>
+      <c r="D395" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E395" s="8" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="396" ht="15" spans="1:5">
       <c r="A396">
         <v>395</v>
       </c>
-      <c r="B396" s="23" t="s">
-        <v>875</v>
-      </c>
-      <c r="C396" s="23"/>
-      <c r="D396" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E396" s="23" t="s">
-        <v>876</v>
+      <c r="B396" s="8" t="s">
+        <v>877</v>
+      </c>
+      <c r="C396" s="8"/>
+      <c r="D396" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E396" s="8" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="397" ht="15" spans="1:5">
       <c r="A397">
         <v>396</v>
       </c>
-      <c r="B397" s="23" t="s">
-        <v>877</v>
-      </c>
-      <c r="C397" s="23"/>
-      <c r="D397" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E397" s="23" t="s">
-        <v>878</v>
+      <c r="B397" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="C397" s="8"/>
+      <c r="D397" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E397" s="8" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="398" ht="15" spans="1:5">
       <c r="A398">
         <v>397</v>
       </c>
-      <c r="B398" s="23" t="s">
-        <v>879</v>
-      </c>
-      <c r="C398" s="23"/>
-      <c r="D398" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E398" s="23" t="s">
-        <v>880</v>
+      <c r="B398" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="C398" s="8"/>
+      <c r="D398" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E398" s="8" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="399" ht="15" spans="1:5">
       <c r="A399">
         <v>398</v>
       </c>
-      <c r="B399" s="23" t="s">
-        <v>881</v>
-      </c>
-      <c r="C399" s="23"/>
-      <c r="D399" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E399" s="23" t="s">
-        <v>882</v>
+      <c r="B399" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="C399" s="8"/>
+      <c r="D399" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E399" s="8" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="400" ht="15" spans="1:5">
       <c r="A400">
         <v>399</v>
       </c>
-      <c r="B400" s="23" t="s">
-        <v>883</v>
-      </c>
-      <c r="C400" s="23"/>
-      <c r="D400" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E400" s="23" t="s">
-        <v>884</v>
+      <c r="B400" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="C400" s="8"/>
+      <c r="D400" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E400" s="8" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="401" ht="15" spans="1:5">
       <c r="A401">
         <v>400</v>
       </c>
-      <c r="B401" s="23" t="s">
-        <v>885</v>
-      </c>
-      <c r="C401" s="23"/>
-      <c r="D401" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E401" s="23" t="s">
-        <v>886</v>
+      <c r="B401" s="8" t="s">
+        <v>887</v>
+      </c>
+      <c r="C401" s="8"/>
+      <c r="D401" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E401" s="8" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="402" ht="15" spans="1:5">
       <c r="A402">
         <v>401</v>
       </c>
-      <c r="B402" s="23" t="s">
-        <v>887</v>
-      </c>
-      <c r="C402" s="23"/>
-      <c r="D402" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E402" s="23" t="s">
-        <v>888</v>
+      <c r="B402" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="C402" s="8"/>
+      <c r="D402" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E402" s="8" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="403" ht="15" spans="1:5">
       <c r="A403">
         <v>402</v>
       </c>
-      <c r="B403" s="23" t="s">
-        <v>889</v>
-      </c>
-      <c r="C403" s="23"/>
-      <c r="D403" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E403" s="23" t="s">
-        <v>890</v>
+      <c r="B403" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="C403" s="8"/>
+      <c r="D403" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E403" s="8" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="404" ht="15" spans="1:5">
       <c r="A404">
         <v>403</v>
       </c>
-      <c r="B404" s="23" t="s">
-        <v>891</v>
-      </c>
-      <c r="C404" s="23"/>
-      <c r="D404" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E404" s="23" t="s">
-        <v>892</v>
+      <c r="B404" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="C404" s="8"/>
+      <c r="D404" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E404" s="8" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="405" ht="15" spans="1:5">
       <c r="A405">
         <v>404</v>
       </c>
-      <c r="B405" s="23" t="s">
-        <v>893</v>
-      </c>
-      <c r="C405" s="23"/>
-      <c r="D405" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E405" s="23" t="s">
-        <v>894</v>
+      <c r="B405" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="C405" s="8"/>
+      <c r="D405" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E405" s="8" t="s">
+        <v>896</v>
       </c>
     </row>
     <row r="406" ht="15" spans="1:5">
       <c r="A406">
         <v>405</v>
       </c>
-      <c r="B406" s="23" t="s">
-        <v>895</v>
-      </c>
-      <c r="C406" s="23"/>
-      <c r="D406" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E406" s="23" t="s">
-        <v>896</v>
+      <c r="B406" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="C406" s="8"/>
+      <c r="D406" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E406" s="8" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="407" ht="15" spans="1:5">
       <c r="A407">
         <v>406</v>
       </c>
-      <c r="B407" s="23" t="s">
-        <v>897</v>
-      </c>
-      <c r="C407" s="23"/>
-      <c r="D407" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E407" s="23" t="s">
-        <v>898</v>
+      <c r="B407" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="C407" s="8"/>
+      <c r="D407" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E407" s="8" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="408" ht="15" spans="1:5">
       <c r="A408">
         <v>407</v>
       </c>
-      <c r="B408" s="23" t="s">
-        <v>899</v>
-      </c>
-      <c r="C408" s="23"/>
-      <c r="D408" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E408" s="23" t="s">
-        <v>900</v>
+      <c r="B408" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="C408" s="8"/>
+      <c r="D408" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E408" s="8" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="409" ht="15" spans="1:5">
       <c r="A409">
         <v>408</v>
       </c>
-      <c r="B409" s="23" t="s">
-        <v>901</v>
-      </c>
-      <c r="C409" s="23"/>
-      <c r="D409" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E409" s="23" t="s">
-        <v>902</v>
+      <c r="B409" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="C409" s="8"/>
+      <c r="D409" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E409" s="8" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="410" ht="15" spans="1:5">
       <c r="A410">
         <v>409</v>
       </c>
-      <c r="B410" s="23" t="s">
-        <v>903</v>
-      </c>
-      <c r="C410" s="23"/>
-      <c r="D410" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E410" s="23" t="s">
-        <v>904</v>
+      <c r="B410" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="C410" s="8"/>
+      <c r="D410" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E410" s="8" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="411" ht="15" spans="1:5">
       <c r="A411">
         <v>410</v>
       </c>
-      <c r="B411" s="23" t="s">
-        <v>905</v>
-      </c>
-      <c r="C411" s="23"/>
-      <c r="D411" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E411" s="23" t="s">
-        <v>906</v>
+      <c r="B411" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="C411" s="8"/>
+      <c r="D411" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E411" s="8" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="412" ht="15" spans="1:5">
       <c r="A412">
         <v>411</v>
       </c>
-      <c r="B412" s="23" t="s">
-        <v>907</v>
-      </c>
-      <c r="C412" s="23"/>
-      <c r="D412" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E412" s="23" t="s">
-        <v>908</v>
+      <c r="B412" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="C412" s="8"/>
+      <c r="D412" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E412" s="8" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="413" ht="15" spans="1:5">
       <c r="A413">
         <v>412</v>
       </c>
-      <c r="B413" s="23" t="s">
-        <v>909</v>
-      </c>
-      <c r="C413" s="23"/>
-      <c r="D413" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E413" s="23" t="s">
-        <v>910</v>
+      <c r="B413" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="C413" s="8"/>
+      <c r="D413" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E413" s="8" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="414" ht="15" spans="1:5">
       <c r="A414">
         <v>413</v>
       </c>
-      <c r="B414" s="23" t="s">
-        <v>911</v>
-      </c>
-      <c r="C414" s="23"/>
-      <c r="D414" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E414" s="23" t="s">
-        <v>912</v>
+      <c r="B414" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="C414" s="8"/>
+      <c r="D414" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E414" s="8" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="415" ht="15" spans="1:5">
       <c r="A415">
         <v>414</v>
       </c>
-      <c r="B415" s="23" t="s">
-        <v>913</v>
-      </c>
-      <c r="C415" s="23"/>
-      <c r="D415" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E415" s="23" t="s">
-        <v>914</v>
+      <c r="B415" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="C415" s="8"/>
+      <c r="D415" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E415" s="8" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="416" ht="15" spans="1:5">
       <c r="A416">
         <v>415</v>
       </c>
-      <c r="B416" s="23" t="s">
-        <v>915</v>
-      </c>
-      <c r="C416" s="23"/>
-      <c r="D416" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E416" s="23" t="s">
-        <v>916</v>
+      <c r="B416" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="C416" s="8"/>
+      <c r="D416" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E416" s="8" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="417" ht="15" spans="1:5">
       <c r="A417">
         <v>416</v>
       </c>
-      <c r="B417" s="23" t="s">
-        <v>917</v>
-      </c>
-      <c r="C417" s="23"/>
-      <c r="D417" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E417" s="23" t="s">
-        <v>918</v>
+      <c r="B417" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="C417" s="8"/>
+      <c r="D417" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E417" s="8" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="418" ht="15" spans="1:5">
       <c r="A418">
         <v>417</v>
       </c>
-      <c r="B418" s="23" t="s">
-        <v>919</v>
-      </c>
-      <c r="C418" s="23"/>
-      <c r="D418" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E418" s="23" t="s">
-        <v>920</v>
+      <c r="B418" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="C418" s="8"/>
+      <c r="D418" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E418" s="8" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="419" ht="15" spans="1:5">
       <c r="A419">
         <v>418</v>
       </c>
-      <c r="B419" s="23" t="s">
-        <v>921</v>
-      </c>
-      <c r="C419" s="23"/>
-      <c r="D419" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E419" s="23" t="s">
-        <v>922</v>
+      <c r="B419" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="C419" s="8"/>
+      <c r="D419" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E419" s="8" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="420" ht="15" spans="1:5">
       <c r="A420">
         <v>419</v>
       </c>
-      <c r="B420" s="23" t="s">
-        <v>923</v>
-      </c>
-      <c r="C420" s="23"/>
-      <c r="D420" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E420" s="23" t="s">
-        <v>924</v>
+      <c r="B420" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="C420" s="8"/>
+      <c r="D420" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E420" s="8" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="421" ht="15" spans="1:5">
       <c r="A421">
         <v>420</v>
       </c>
-      <c r="B421" s="23" t="s">
-        <v>925</v>
-      </c>
-      <c r="C421" s="23"/>
-      <c r="D421" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E421" s="23" t="s">
-        <v>926</v>
+      <c r="B421" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="C421" s="8"/>
+      <c r="D421" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E421" s="8" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="422" ht="15" spans="1:5">
       <c r="A422">
         <v>421</v>
       </c>
-      <c r="B422" s="23" t="s">
-        <v>927</v>
-      </c>
-      <c r="C422" s="23"/>
-      <c r="D422" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E422" s="23" t="s">
-        <v>928</v>
+      <c r="B422" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="C422" s="8"/>
+      <c r="D422" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E422" s="8" t="s">
+        <v>930</v>
       </c>
     </row>
     <row r="423" ht="15" spans="1:5">
       <c r="A423">
         <v>422</v>
       </c>
-      <c r="B423" s="23" t="s">
-        <v>929</v>
-      </c>
-      <c r="C423" s="23"/>
-      <c r="D423" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E423" s="23" t="s">
-        <v>930</v>
+      <c r="B423" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="C423" s="8"/>
+      <c r="D423" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E423" s="8" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="424" ht="15" spans="1:5">
       <c r="A424">
         <v>423</v>
       </c>
-      <c r="B424" s="23" t="s">
-        <v>931</v>
-      </c>
-      <c r="C424" s="23"/>
-      <c r="D424" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E424" s="23" t="s">
-        <v>932</v>
+      <c r="B424" s="8" t="s">
+        <v>933</v>
+      </c>
+      <c r="C424" s="8"/>
+      <c r="D424" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E424" s="8" t="s">
+        <v>934</v>
       </c>
     </row>
     <row r="425" ht="15" spans="1:5">
       <c r="A425">
         <v>424</v>
       </c>
-      <c r="B425" s="23" t="s">
-        <v>933</v>
-      </c>
-      <c r="C425" s="23"/>
-      <c r="D425" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E425" s="23" t="s">
-        <v>934</v>
+      <c r="B425" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="C425" s="8"/>
+      <c r="D425" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E425" s="8" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="426" ht="15" spans="1:5">
       <c r="A426">
         <v>425</v>
       </c>
-      <c r="B426" s="23" t="s">
-        <v>935</v>
-      </c>
-      <c r="C426" s="23"/>
-      <c r="D426" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E426" s="23" t="s">
-        <v>936</v>
+      <c r="B426" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="C426" s="8"/>
+      <c r="D426" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E426" s="8" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="427" ht="15" spans="1:5">
       <c r="A427">
         <v>426</v>
       </c>
-      <c r="B427" s="23" t="s">
-        <v>937</v>
-      </c>
-      <c r="C427" s="23"/>
-      <c r="D427" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E427" s="23" t="s">
-        <v>938</v>
+      <c r="B427" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="C427" s="8"/>
+      <c r="D427" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E427" s="8" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="428" ht="15" spans="1:5">
       <c r="A428">
         <v>427</v>
       </c>
-      <c r="B428" s="23" t="s">
-        <v>939</v>
-      </c>
-      <c r="C428" s="23"/>
-      <c r="D428" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E428" s="23" t="s">
-        <v>940</v>
+      <c r="B428" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="C428" s="8"/>
+      <c r="D428" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E428" s="8" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="429" ht="15" spans="1:5">
       <c r="A429">
         <v>428</v>
       </c>
-      <c r="B429" s="23" t="s">
-        <v>941</v>
-      </c>
-      <c r="C429" s="23"/>
-      <c r="D429" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E429" s="23" t="s">
-        <v>942</v>
+      <c r="B429" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="C429" s="8"/>
+      <c r="D429" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E429" s="8" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="430" ht="15" spans="1:5">
       <c r="A430">
         <v>429</v>
       </c>
-      <c r="B430" s="23" t="s">
-        <v>943</v>
-      </c>
-      <c r="C430" s="23"/>
-      <c r="D430" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E430" s="23" t="s">
-        <v>944</v>
+      <c r="B430" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="C430" s="8"/>
+      <c r="D430" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E430" s="8" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="431" ht="15" spans="1:5">
       <c r="A431">
         <v>430</v>
       </c>
-      <c r="B431" s="23" t="s">
-        <v>945</v>
-      </c>
-      <c r="C431" s="23"/>
-      <c r="D431" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E431" s="23" t="s">
-        <v>946</v>
+      <c r="B431" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="C431" s="8"/>
+      <c r="D431" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E431" s="8" t="s">
+        <v>948</v>
       </c>
     </row>
     <row r="432" ht="15" spans="1:5">
       <c r="A432">
         <v>431</v>
       </c>
-      <c r="B432" s="23" t="s">
-        <v>947</v>
-      </c>
-      <c r="C432" s="23"/>
-      <c r="D432" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E432" s="23" t="s">
-        <v>948</v>
+      <c r="B432" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="C432" s="8"/>
+      <c r="D432" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E432" s="8" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="433" ht="15" spans="1:5">
       <c r="A433">
         <v>432</v>
       </c>
-      <c r="B433" s="23" t="s">
-        <v>949</v>
-      </c>
-      <c r="C433" s="23"/>
-      <c r="D433" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E433" s="23" t="s">
-        <v>950</v>
+      <c r="B433" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="C433" s="8"/>
+      <c r="D433" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E433" s="8" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="434" ht="15" spans="1:5">
       <c r="A434">
         <v>433</v>
       </c>
-      <c r="B434" s="23" t="s">
-        <v>951</v>
-      </c>
-      <c r="C434" s="23"/>
-      <c r="D434" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E434" s="23" t="s">
-        <v>952</v>
+      <c r="B434" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="C434" s="8"/>
+      <c r="D434" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E434" s="8" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="435" ht="15" spans="1:5">
       <c r="A435">
         <v>434</v>
       </c>
-      <c r="B435" s="23" t="s">
-        <v>953</v>
-      </c>
-      <c r="C435" s="23"/>
-      <c r="D435" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E435" s="23" t="s">
-        <v>954</v>
+      <c r="B435" s="8" t="s">
+        <v>955</v>
+      </c>
+      <c r="C435" s="8"/>
+      <c r="D435" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E435" s="8" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="436" ht="15" spans="1:5">
       <c r="A436">
         <v>435</v>
       </c>
-      <c r="B436" s="23" t="s">
-        <v>955</v>
-      </c>
-      <c r="C436" s="23"/>
-      <c r="D436" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E436" s="23" t="s">
-        <v>956</v>
+      <c r="B436" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="C436" s="8"/>
+      <c r="D436" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E436" s="8" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="437" ht="15" spans="1:5">
       <c r="A437">
         <v>436</v>
       </c>
-      <c r="B437" s="23" t="s">
-        <v>957</v>
-      </c>
-      <c r="C437" s="23"/>
-      <c r="D437" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E437" s="23" t="s">
-        <v>958</v>
+      <c r="B437" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="C437" s="8"/>
+      <c r="D437" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E437" s="8" t="s">
+        <v>960</v>
       </c>
     </row>
     <row r="438" ht="15" spans="1:5">
       <c r="A438">
         <v>437</v>
       </c>
-      <c r="B438" s="23" t="s">
-        <v>959</v>
-      </c>
-      <c r="C438" s="23"/>
-      <c r="D438" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E438" s="23" t="s">
-        <v>960</v>
+      <c r="B438" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="C438" s="8"/>
+      <c r="D438" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E438" s="8" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="439" ht="15" spans="1:5">
       <c r="A439">
         <v>438</v>
       </c>
-      <c r="B439" s="23" t="s">
-        <v>961</v>
-      </c>
-      <c r="C439" s="23"/>
-      <c r="D439" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E439" s="23" t="s">
-        <v>962</v>
+      <c r="B439" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="C439" s="8"/>
+      <c r="D439" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E439" s="8" t="s">
+        <v>964</v>
       </c>
     </row>
     <row r="440" ht="15" spans="1:5">
       <c r="A440">
         <v>439</v>
       </c>
-      <c r="B440" s="23" t="s">
-        <v>963</v>
-      </c>
-      <c r="C440" s="23"/>
-      <c r="D440" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E440" s="23" t="s">
-        <v>964</v>
+      <c r="B440" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="C440" s="8"/>
+      <c r="D440" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E440" s="8" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="441" ht="15" spans="1:5">
       <c r="A441">
         <v>440</v>
       </c>
-      <c r="B441" s="23" t="s">
-        <v>965</v>
-      </c>
-      <c r="C441" s="23"/>
-      <c r="D441" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E441" s="23" t="s">
-        <v>966</v>
+      <c r="B441" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="C441" s="8"/>
+      <c r="D441" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E441" s="8" t="s">
+        <v>968</v>
       </c>
     </row>
     <row r="442" ht="15" spans="1:5">
       <c r="A442">
         <v>441</v>
       </c>
-      <c r="B442" s="23" t="s">
-        <v>967</v>
-      </c>
-      <c r="C442" s="23"/>
-      <c r="D442" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E442" s="23" t="s">
-        <v>968</v>
+      <c r="B442" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="C442" s="8"/>
+      <c r="D442" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E442" s="8" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="443" ht="15" spans="1:5">
       <c r="A443">
         <v>442</v>
       </c>
-      <c r="B443" s="23" t="s">
-        <v>969</v>
-      </c>
-      <c r="C443" s="23"/>
-      <c r="D443" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E443" s="23" t="s">
-        <v>970</v>
+      <c r="B443" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="C443" s="8"/>
+      <c r="D443" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E443" s="8" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="444" ht="15" spans="1:5">
       <c r="A444">
         <v>443</v>
       </c>
-      <c r="B444" s="23" t="s">
-        <v>971</v>
-      </c>
-      <c r="C444" s="23"/>
-      <c r="D444" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E444" s="23" t="s">
-        <v>972</v>
+      <c r="B444" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="C444" s="8"/>
+      <c r="D444" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E444" s="8" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="445" ht="15" spans="1:5">
       <c r="A445">
         <v>444</v>
       </c>
-      <c r="B445" s="23" t="s">
-        <v>973</v>
-      </c>
-      <c r="C445" s="23"/>
-      <c r="D445" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E445" s="23" t="s">
-        <v>974</v>
+      <c r="B445" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="C445" s="8"/>
+      <c r="D445" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E445" s="8" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="446" ht="15" spans="1:5">
       <c r="A446">
         <v>445</v>
       </c>
-      <c r="B446" s="23" t="s">
-        <v>975</v>
-      </c>
-      <c r="C446" s="23"/>
-      <c r="D446" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E446" s="23" t="s">
-        <v>976</v>
+      <c r="B446" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="C446" s="8"/>
+      <c r="D446" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E446" s="8" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="447" ht="15" spans="1:5">
       <c r="A447">
         <v>446</v>
       </c>
-      <c r="B447" s="23" t="s">
-        <v>977</v>
-      </c>
-      <c r="C447" s="23"/>
-      <c r="D447" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E447" s="23" t="s">
-        <v>978</v>
+      <c r="B447" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="C447" s="8"/>
+      <c r="D447" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E447" s="8" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="448" ht="15" spans="1:5">
       <c r="A448">
         <v>447</v>
       </c>
-      <c r="B448" s="23" t="s">
-        <v>979</v>
-      </c>
-      <c r="C448" s="23"/>
-      <c r="D448" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E448" s="23" t="s">
-        <v>980</v>
+      <c r="B448" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="C448" s="8"/>
+      <c r="D448" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E448" s="8" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="449" ht="15" spans="1:5">
       <c r="A449">
         <v>448</v>
       </c>
-      <c r="B449" s="23" t="s">
-        <v>981</v>
-      </c>
-      <c r="C449" s="23"/>
-      <c r="D449" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E449" s="23" t="s">
-        <v>982</v>
+      <c r="B449" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="C449" s="8"/>
+      <c r="D449" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E449" s="8" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="450" ht="15" spans="1:5">
       <c r="A450">
         <v>449</v>
       </c>
-      <c r="B450" s="23" t="s">
-        <v>983</v>
-      </c>
-      <c r="C450" s="23"/>
-      <c r="D450" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E450" s="23" t="s">
-        <v>984</v>
+      <c r="B450" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="C450" s="8"/>
+      <c r="D450" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E450" s="8" t="s">
+        <v>986</v>
       </c>
     </row>
     <row r="451" ht="15" spans="1:5">
       <c r="A451">
         <v>450</v>
       </c>
-      <c r="B451" s="23" t="s">
-        <v>985</v>
-      </c>
-      <c r="C451" s="23"/>
-      <c r="D451" s="23" t="s">
-        <v>777</v>
-      </c>
-      <c r="E451" s="23" t="s">
-        <v>986</v>
+      <c r="B451" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="C451" s="8"/>
+      <c r="D451" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E451" s="8" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452">
+        <v>451</v>
+      </c>
+      <c r="B452" s="17" t="s">
+        <v>989</v>
+      </c>
+      <c r="C452" t="s">
+        <v>990</v>
+      </c>
+      <c r="D452" t="s">
+        <v>991</v>
+      </c>
+      <c r="E452" s="13" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453">
+        <v>452</v>
+      </c>
+      <c r="B453" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="D453" t="s">
+        <v>180</v>
+      </c>
+      <c r="E453" s="13" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454">
+        <v>453</v>
+      </c>
+      <c r="B454" s="22" t="s">
+        <v>995</v>
+      </c>
+      <c r="C454" t="s">
+        <v>996</v>
+      </c>
+      <c r="E454" s="22" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="455" ht="15" spans="1:5">
+      <c r="A455">
+        <v>454</v>
+      </c>
+      <c r="B455" s="23" t="s">
+        <v>998</v>
+      </c>
+      <c r="C455" s="23"/>
+      <c r="D455" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E455" s="24" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="456" ht="15" spans="1:5">
+      <c r="A456">
+        <v>455</v>
+      </c>
+      <c r="B456" s="23" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C456" s="23"/>
+      <c r="D456" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E456" s="23" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457">
+        <v>456</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D457" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E457" s="1" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="458" ht="15" spans="1:5">
+      <c r="A458">
+        <v>457</v>
+      </c>
+      <c r="B458" s="23" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C458" s="23"/>
+      <c r="D458" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E458" s="23" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="459" ht="15" spans="1:5">
+      <c r="A459">
+        <v>458</v>
+      </c>
+      <c r="B459" s="23" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C459" s="23"/>
+      <c r="D459" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E459" s="23" t="s">
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E345" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E453" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -10944,6 +11133,7 @@
     <hyperlink ref="E296" r:id="rId151" display="https://pan.quark.cn/s/f4ac3e17be93"/>
     <hyperlink ref="E314" r:id="rId152" display="https://pan.quark.cn/s/c928c080711b"/>
     <hyperlink ref="E394" r:id="rId153" display="https://pan.quark.cn/s/e90ebe569558"/>
+    <hyperlink ref="E455" r:id="rId154" display="https://pan.quark.cn/s/d3b05e00c02e"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$453</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$459</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1019">
   <si>
     <t>id</t>
   </si>
@@ -3109,6 +3109,36 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/c00a82990679</t>
+  </si>
+  <si>
+    <t>精神病院4</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/19127453dd73</t>
+  </si>
+  <si>
+    <t>最后的晚餐</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ff2903564234</t>
+  </si>
+  <si>
+    <t>青白</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/0a7827db09f3</t>
+  </si>
+  <si>
+    <t>蓝色大丽花</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/75a3b9508b8f</t>
+  </si>
+  <si>
+    <t>此时彼刻之人</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/dd840fcb4e06</t>
   </si>
 </sst>
 </file>
@@ -3784,7 +3814,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3842,8 +3872,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4163,7 +4191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E459"/>
+  <dimension ref="A1:E464"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="60.75" customWidth="1"/>
@@ -10891,13 +10919,13 @@
       <c r="A454">
         <v>453</v>
       </c>
-      <c r="B454" s="22" t="s">
+      <c r="B454" s="13" t="s">
         <v>995</v>
       </c>
       <c r="C454" t="s">
         <v>996</v>
       </c>
-      <c r="E454" s="22" t="s">
+      <c r="E454" s="13" t="s">
         <v>997</v>
       </c>
     </row>
@@ -10905,14 +10933,14 @@
       <c r="A455">
         <v>454</v>
       </c>
-      <c r="B455" s="23" t="s">
+      <c r="B455" s="8" t="s">
         <v>998</v>
       </c>
-      <c r="C455" s="23"/>
-      <c r="D455" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E455" s="24" t="s">
+      <c r="C455" s="8"/>
+      <c r="D455" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E455" s="21" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10920,14 +10948,14 @@
       <c r="A456">
         <v>455</v>
       </c>
-      <c r="B456" s="23" t="s">
+      <c r="B456" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="C456" s="23"/>
-      <c r="D456" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E456" s="23" t="s">
+      <c r="C456" s="8"/>
+      <c r="D456" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E456" s="8" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -10949,14 +10977,14 @@
       <c r="A458">
         <v>457</v>
       </c>
-      <c r="B458" s="23" t="s">
+      <c r="B458" s="8" t="s">
         <v>1005</v>
       </c>
-      <c r="C458" s="23"/>
-      <c r="D458" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E458" s="23" t="s">
+      <c r="C458" s="8"/>
+      <c r="D458" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E458" s="8" t="s">
         <v>1006</v>
       </c>
     </row>
@@ -10964,19 +10992,89 @@
       <c r="A459">
         <v>458</v>
       </c>
-      <c r="B459" s="23" t="s">
+      <c r="B459" s="8" t="s">
         <v>1007</v>
       </c>
-      <c r="C459" s="23"/>
-      <c r="D459" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E459" s="23" t="s">
+      <c r="C459" s="8"/>
+      <c r="D459" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E459" s="8" t="s">
         <v>1008</v>
       </c>
     </row>
+    <row r="460" ht="15" spans="1:5">
+      <c r="A460">
+        <v>459</v>
+      </c>
+      <c r="B460" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D460" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E460" s="22" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="461" ht="15" spans="1:5">
+      <c r="A461">
+        <v>460</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D461" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E461" s="1" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="462" ht="15" spans="1:5">
+      <c r="A462">
+        <v>461</v>
+      </c>
+      <c r="B462" s="22" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D462" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E462" s="22" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="463" ht="15" spans="1:5">
+      <c r="A463">
+        <v>462</v>
+      </c>
+      <c r="B463" s="22" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D463" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E463" s="22" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="464" ht="15" spans="1:5">
+      <c r="A464">
+        <v>463</v>
+      </c>
+      <c r="B464" s="22" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D464" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E464" s="22" t="s">
+        <v>1018</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E453" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E459" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$459</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$464</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="1031">
   <si>
     <t>id</t>
   </si>
@@ -836,10 +836,16 @@
     <t>相府鱼美人1 4人开放</t>
   </si>
   <si>
+    <t>相府鱼美人1,相府美人鱼1</t>
+  </si>
+  <si>
     <t>https://pan.quark.cn/s/d47624bd9832</t>
   </si>
   <si>
     <t>相府鱼美人2 4人开放</t>
+  </si>
+  <si>
+    <t>相府鱼美人2,相府美人鱼2</t>
   </si>
   <si>
     <t>https://pan.quark.cn/s/4e04a07074cd</t>
@@ -3139,6 +3145,36 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/dd840fcb4e06</t>
+  </si>
+  <si>
+    <t>长安秘案录</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/ec0a3f96df64</t>
+  </si>
+  <si>
+    <t>亡瘾</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/c006323e4119</t>
+  </si>
+  <si>
+    <t>我与我诀别</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/d0bd4ce4f9fe</t>
+  </si>
+  <si>
+    <t>红豆</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e7e922931dc7</t>
+  </si>
+  <si>
+    <t>大宴之上</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/931d2b0fe589</t>
   </si>
 </sst>
 </file>
@@ -3814,7 +3850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3841,6 +3877,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
@@ -3868,10 +3905,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4191,11 +4229,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E464"/>
+  <dimension ref="A1:E469"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="60.75" customWidth="1"/>
-    <col min="3" max="4" width="20.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="48.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="33.0833333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5572,12 +5611,14 @@
       <c r="B98" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C98" s="8"/>
+      <c r="C98" s="8" t="s">
+        <v>268</v>
+      </c>
       <c r="D98" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E98" s="8" t="s">
-        <v>268</v>
+      <c r="E98" s="10" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="99" ht="15" spans="1:5">
@@ -5585,14 +5626,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="C99" s="8"/>
+        <v>270</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="D99" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" ht="15" spans="1:5">
@@ -5600,14 +5643,14 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" ht="15" spans="1:5">
@@ -5615,14 +5658,14 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" ht="15" spans="1:5">
@@ -5630,14 +5673,14 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" ht="15" spans="1:5">
@@ -5645,14 +5688,14 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="104" ht="15" spans="1:5">
@@ -5660,14 +5703,14 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="105" ht="15" spans="1:5">
@@ -5675,14 +5718,14 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="106" ht="15" spans="1:5">
@@ -5690,14 +5733,14 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="107" ht="15" spans="1:5">
@@ -5705,14 +5748,14 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108" ht="15" spans="1:5">
@@ -5720,14 +5763,14 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109" ht="15" spans="1:5">
@@ -5735,14 +5778,14 @@
         <v>108</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="110" ht="15" spans="1:5">
@@ -5750,14 +5793,14 @@
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="111" ht="15" spans="1:5">
@@ -5765,14 +5808,14 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="112" ht="15" spans="1:5">
@@ -5780,14 +5823,14 @@
         <v>111</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="113" ht="15" spans="1:5">
@@ -5795,14 +5838,14 @@
         <v>112</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114" ht="15" spans="1:5">
@@ -5810,14 +5853,14 @@
         <v>113</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="115" ht="15" spans="1:5">
@@ -5825,14 +5868,14 @@
         <v>114</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="116" ht="15" spans="1:5">
@@ -5840,14 +5883,14 @@
         <v>115</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="117" ht="15" spans="1:5">
@@ -5855,14 +5898,14 @@
         <v>116</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="118" ht="15" spans="1:5">
@@ -5870,14 +5913,14 @@
         <v>117</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="119" ht="15" spans="1:5">
@@ -5885,14 +5928,14 @@
         <v>118</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C119" s="8"/>
       <c r="D119" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="120" ht="15" spans="1:5">
@@ -5900,14 +5943,14 @@
         <v>119</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C120" s="8"/>
       <c r="D120" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="121" ht="15" spans="1:5">
@@ -5915,14 +5958,14 @@
         <v>120</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="122" ht="15" spans="1:5">
@@ -5930,14 +5973,14 @@
         <v>121</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C122" s="8"/>
       <c r="D122" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="123" ht="15" spans="1:5">
@@ -5945,14 +5988,14 @@
         <v>122</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="124" ht="15" spans="1:5">
@@ -5960,14 +6003,14 @@
         <v>123</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C124" s="8"/>
       <c r="D124" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="125" ht="15" spans="1:5">
@@ -5975,14 +6018,14 @@
         <v>124</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C125" s="8"/>
       <c r="D125" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" ht="15" spans="1:5">
@@ -5990,14 +6033,14 @@
         <v>125</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C126" s="8"/>
       <c r="D126" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="127" ht="15" spans="1:5">
@@ -6005,14 +6048,14 @@
         <v>126</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="128" ht="15" spans="1:5">
@@ -6020,14 +6063,14 @@
         <v>127</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="129" ht="15" spans="1:5">
@@ -6035,14 +6078,14 @@
         <v>128</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="130" ht="15" spans="1:5">
@@ -6050,14 +6093,14 @@
         <v>129</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="131" ht="15" spans="1:5">
@@ -6065,14 +6108,14 @@
         <v>130</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="132" ht="15" spans="1:5">
@@ -6080,14 +6123,14 @@
         <v>131</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C132" s="8"/>
       <c r="D132" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="133" ht="15" spans="1:5">
@@ -6095,14 +6138,14 @@
         <v>132</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C133" s="8"/>
       <c r="D133" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="134" ht="15" spans="1:5">
@@ -6110,14 +6153,14 @@
         <v>133</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C134" s="8"/>
       <c r="D134" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="135" ht="15" spans="1:5">
@@ -6125,14 +6168,14 @@
         <v>134</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C135" s="8"/>
       <c r="D135" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="136" ht="15" spans="1:5">
@@ -6140,14 +6183,14 @@
         <v>135</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="137" ht="15" spans="1:5">
@@ -6155,14 +6198,14 @@
         <v>136</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C137" s="8"/>
       <c r="D137" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="138" ht="15" spans="1:5">
@@ -6170,14 +6213,14 @@
         <v>137</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="139" ht="15" spans="1:5">
@@ -6185,14 +6228,14 @@
         <v>138</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C139" s="8"/>
       <c r="D139" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="140" ht="15" spans="1:5">
@@ -6200,14 +6243,14 @@
         <v>139</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="141" ht="15" spans="1:5">
@@ -6215,14 +6258,14 @@
         <v>140</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="142" ht="15" spans="1:5">
@@ -6230,14 +6273,14 @@
         <v>141</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="143" ht="15" spans="1:5">
@@ -6245,14 +6288,14 @@
         <v>142</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C143" s="8"/>
       <c r="D143" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="144" ht="15" spans="1:5">
@@ -6260,14 +6303,14 @@
         <v>143</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="145" ht="15" spans="1:5">
@@ -6275,14 +6318,14 @@
         <v>144</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C145" s="8"/>
       <c r="D145" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="146" ht="15" spans="1:5">
@@ -6290,14 +6333,14 @@
         <v>145</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C146" s="8"/>
       <c r="D146" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="147" ht="15" spans="1:5">
@@ -6305,14 +6348,14 @@
         <v>146</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C147" s="8"/>
       <c r="D147" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="148" ht="15" spans="1:5">
@@ -6320,14 +6363,14 @@
         <v>147</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="149" ht="15" spans="1:5">
@@ -6335,14 +6378,14 @@
         <v>148</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C149" s="8"/>
       <c r="D149" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="150" ht="15" spans="1:5">
@@ -6350,14 +6393,14 @@
         <v>149</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="151" ht="15" spans="1:5">
@@ -6365,14 +6408,14 @@
         <v>150</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C151" s="8"/>
       <c r="D151" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="152" ht="15" spans="1:5">
@@ -6380,14 +6423,14 @@
         <v>151</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="153" ht="15" spans="1:5">
@@ -6395,14 +6438,14 @@
         <v>152</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C153" s="8"/>
       <c r="D153" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" ht="15" spans="1:5">
@@ -6410,14 +6453,14 @@
         <v>153</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C154" s="8"/>
       <c r="D154" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="155" ht="15" spans="1:5">
@@ -6425,14 +6468,14 @@
         <v>154</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C155" s="8"/>
       <c r="D155" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" ht="15" spans="1:5">
@@ -6440,14 +6483,14 @@
         <v>155</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C156" s="8"/>
       <c r="D156" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" ht="15" spans="1:5">
@@ -6455,14 +6498,14 @@
         <v>156</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="158" ht="15" spans="1:5">
@@ -6470,14 +6513,14 @@
         <v>157</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C158" s="8"/>
       <c r="D158" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="159" ht="15" spans="1:5">
@@ -6485,14 +6528,14 @@
         <v>158</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" ht="15" spans="1:5">
@@ -6500,14 +6543,14 @@
         <v>159</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C160" s="8"/>
       <c r="D160" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="161" ht="15" spans="1:5">
@@ -6515,14 +6558,14 @@
         <v>160</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C161" s="8"/>
       <c r="D161" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="162" ht="15" spans="1:5">
@@ -6530,14 +6573,14 @@
         <v>161</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C162" s="8"/>
       <c r="D162" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" ht="15" spans="1:5">
@@ -6545,14 +6588,14 @@
         <v>162</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C163" s="8"/>
       <c r="D163" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" ht="15" spans="1:5">
@@ -6560,14 +6603,14 @@
         <v>163</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C164" s="8"/>
       <c r="D164" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="165" ht="15" spans="1:5">
@@ -6575,14 +6618,14 @@
         <v>164</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C165" s="8"/>
       <c r="D165" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" ht="15" spans="1:5">
@@ -6590,14 +6633,14 @@
         <v>165</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C166" s="8"/>
       <c r="D166" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="167" ht="15" spans="1:5">
@@ -6605,14 +6648,14 @@
         <v>166</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C167" s="8"/>
       <c r="D167" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="168" ht="15" spans="1:5">
@@ -6620,14 +6663,14 @@
         <v>167</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C168" s="8"/>
       <c r="D168" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="169" ht="15" spans="1:5">
@@ -6635,14 +6678,14 @@
         <v>168</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C169" s="8"/>
       <c r="D169" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" ht="15" spans="1:5">
@@ -6650,14 +6693,14 @@
         <v>169</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C170" s="8"/>
       <c r="D170" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" ht="15" spans="1:5">
@@ -6665,14 +6708,14 @@
         <v>170</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C171" s="8"/>
       <c r="D171" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="172" ht="15" spans="1:5">
@@ -6680,14 +6723,14 @@
         <v>171</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C172" s="8"/>
       <c r="D172" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="173" ht="15" spans="1:5">
@@ -6695,14 +6738,14 @@
         <v>172</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C173" s="8"/>
       <c r="D173" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" ht="15" spans="1:5">
@@ -6710,14 +6753,14 @@
         <v>173</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C174" s="8"/>
       <c r="D174" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="175" ht="15" spans="1:5">
@@ -6725,14 +6768,14 @@
         <v>174</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C175" s="8"/>
       <c r="D175" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="176" ht="15" spans="1:5">
@@ -6740,14 +6783,14 @@
         <v>175</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C176" s="8"/>
       <c r="D176" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="177" ht="15" spans="1:5">
@@ -6755,14 +6798,14 @@
         <v>176</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C177" s="8"/>
       <c r="D177" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" ht="15" spans="1:5">
@@ -6770,14 +6813,14 @@
         <v>177</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C178" s="8"/>
       <c r="D178" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="179" ht="15" spans="1:5">
@@ -6785,14 +6828,14 @@
         <v>178</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C179" s="8"/>
       <c r="D179" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="180" ht="15" spans="1:5">
@@ -6800,14 +6843,14 @@
         <v>179</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C180" s="8"/>
       <c r="D180" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="181" ht="15" spans="1:5">
@@ -6815,14 +6858,14 @@
         <v>180</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C181" s="8"/>
       <c r="D181" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="182" ht="15" spans="1:5">
@@ -6830,14 +6873,14 @@
         <v>181</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C182" s="8"/>
       <c r="D182" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="183" ht="15" spans="1:5">
@@ -6845,14 +6888,14 @@
         <v>182</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C183" s="8"/>
       <c r="D183" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="184" ht="15" spans="1:5">
@@ -6860,14 +6903,14 @@
         <v>183</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C184" s="8"/>
       <c r="D184" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="185" ht="15" spans="1:5">
@@ -6875,14 +6918,14 @@
         <v>184</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C185" s="8"/>
       <c r="D185" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="186" ht="15" spans="1:5">
@@ -6890,14 +6933,14 @@
         <v>185</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C186" s="8"/>
       <c r="D186" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="187" ht="15" spans="1:5">
@@ -6905,14 +6948,14 @@
         <v>186</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C187" s="8"/>
       <c r="D187" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" ht="15" spans="1:5">
@@ -6920,14 +6963,14 @@
         <v>187</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C188" s="8"/>
       <c r="D188" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" ht="15" spans="1:5">
@@ -6935,149 +6978,149 @@
         <v>188</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C189" s="8"/>
       <c r="D189" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" ht="15.5" spans="1:5">
       <c r="A190">
         <v>189</v>
       </c>
-      <c r="B190" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="C190" s="10"/>
-      <c r="D190" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E190" s="11" t="s">
-        <v>452</v>
+      <c r="B190" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C190" s="11"/>
+      <c r="D190" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="191" ht="15.5" spans="1:5">
       <c r="A191">
         <v>190</v>
       </c>
-      <c r="B191" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="C191" s="10"/>
-      <c r="D191" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E191" s="10" t="s">
-        <v>454</v>
+      <c r="B191" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="C191" s="11"/>
+      <c r="D191" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E191" s="11" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="192" ht="15.5" spans="1:5">
       <c r="A192">
         <v>191</v>
       </c>
-      <c r="B192" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="C192" s="10"/>
-      <c r="D192" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E192" s="10" t="s">
-        <v>456</v>
+      <c r="B192" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="C192" s="11"/>
+      <c r="D192" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E192" s="11" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="193" ht="15.5" spans="1:5">
       <c r="A193">
         <v>192</v>
       </c>
-      <c r="B193" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="C193" s="10"/>
-      <c r="D193" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E193" s="11" t="s">
-        <v>458</v>
+      <c r="B193" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="C193" s="11"/>
+      <c r="D193" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="194" ht="15.5" spans="1:5">
       <c r="A194">
         <v>193</v>
       </c>
-      <c r="B194" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="C194" s="10"/>
-      <c r="D194" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E194" s="11" t="s">
-        <v>460</v>
+      <c r="B194" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="C194" s="11"/>
+      <c r="D194" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E194" s="12" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="195" ht="15.5" spans="1:5">
       <c r="A195">
         <v>194</v>
       </c>
-      <c r="B195" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="C195" s="10"/>
-      <c r="D195" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E195" s="11" t="s">
-        <v>462</v>
+      <c r="B195" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="C195" s="11"/>
+      <c r="D195" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E195" s="12" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="196" ht="15.5" spans="1:5">
       <c r="A196">
         <v>195</v>
       </c>
-      <c r="B196" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="C196" s="10"/>
-      <c r="D196" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E196" s="11" t="s">
-        <v>464</v>
+      <c r="B196" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="C196" s="11"/>
+      <c r="D196" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="197" ht="15.5" spans="1:5">
       <c r="A197">
         <v>196</v>
       </c>
-      <c r="B197" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="C197" s="10"/>
-      <c r="D197" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E197" s="11" t="s">
-        <v>466</v>
+      <c r="B197" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="C197" s="11"/>
+      <c r="D197" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="198" ht="15.5" spans="1:5">
       <c r="A198">
         <v>197</v>
       </c>
-      <c r="B198" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C198" s="10"/>
-      <c r="D198" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E198" s="11" t="s">
-        <v>468</v>
+      <c r="B198" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="C198" s="11"/>
+      <c r="D198" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="199" ht="15.5" spans="1:5">
@@ -7085,14 +7128,14 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>469</v>
-      </c>
-      <c r="C199" s="10"/>
-      <c r="D199" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="C199" s="11"/>
+      <c r="D199" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="200" ht="15.5" spans="1:5">
@@ -7100,16 +7143,16 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>471</v>
-      </c>
-      <c r="C200" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="D200" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="C200" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="D200" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="201" ht="15.5" spans="1:5">
@@ -7117,14 +7160,14 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>474</v>
-      </c>
-      <c r="C201" s="10"/>
-      <c r="D201" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="C201" s="11"/>
+      <c r="D201" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="202" ht="15.5" spans="1:5">
@@ -7132,14 +7175,14 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>476</v>
-      </c>
-      <c r="C202" s="10"/>
-      <c r="D202" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C202" s="11"/>
+      <c r="D202" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="203" ht="15.5" spans="1:5">
@@ -7147,14 +7190,14 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>478</v>
-      </c>
-      <c r="C203" s="10"/>
-      <c r="D203" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C203" s="11"/>
+      <c r="D203" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="204" ht="15.5" spans="1:5">
@@ -7162,14 +7205,14 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>480</v>
-      </c>
-      <c r="C204" s="10"/>
-      <c r="D204" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E204" s="12" t="s">
-        <v>481</v>
+        <v>482</v>
+      </c>
+      <c r="C204" s="11"/>
+      <c r="D204" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E204" s="13" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="205" ht="15.5" spans="1:5">
@@ -7177,14 +7220,14 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>482</v>
-      </c>
-      <c r="C205" s="10"/>
-      <c r="D205" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="C205" s="11"/>
+      <c r="D205" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" ht="15.5" spans="1:5">
@@ -7192,14 +7235,14 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>484</v>
-      </c>
-      <c r="C206" s="10"/>
-      <c r="D206" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="C206" s="11"/>
+      <c r="D206" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="207" ht="15.5" spans="1:5">
@@ -7207,14 +7250,14 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>486</v>
-      </c>
-      <c r="C207" s="10"/>
-      <c r="D207" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="C207" s="11"/>
+      <c r="D207" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="208" ht="15.5" spans="1:5">
@@ -7222,14 +7265,14 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>488</v>
-      </c>
-      <c r="C208" s="10"/>
-      <c r="D208" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="C208" s="11"/>
+      <c r="D208" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="209" ht="15.5" spans="1:5">
@@ -7237,16 +7280,16 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>490</v>
-      </c>
-      <c r="C209" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="D209" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C209" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="D209" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="210" ht="15.5" spans="1:5">
@@ -7254,14 +7297,14 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>493</v>
-      </c>
-      <c r="C210" s="10"/>
-      <c r="D210" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="C210" s="11"/>
+      <c r="D210" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="211" ht="15.5" spans="1:5">
@@ -7269,14 +7312,14 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>495</v>
-      </c>
-      <c r="C211" s="10"/>
-      <c r="D211" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C211" s="11"/>
+      <c r="D211" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="212" ht="15.5" spans="1:5">
@@ -7284,149 +7327,149 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>497</v>
-      </c>
-      <c r="C212" s="10"/>
-      <c r="D212" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="C212" s="11"/>
+      <c r="D212" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="213" ht="15.5" spans="1:5">
       <c r="A213">
         <v>212</v>
       </c>
-      <c r="B213" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="C213" s="10"/>
-      <c r="D213" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E213" s="11" t="s">
-        <v>500</v>
+      <c r="B213" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="C213" s="11"/>
+      <c r="D213" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="214" ht="15.5" spans="1:5">
       <c r="A214">
         <v>213</v>
       </c>
-      <c r="B214" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="C214" s="10"/>
-      <c r="D214" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E214" s="11" t="s">
-        <v>502</v>
+      <c r="B214" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="C214" s="11"/>
+      <c r="D214" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="215" ht="15.5" spans="1:5">
       <c r="A215">
         <v>214</v>
       </c>
-      <c r="B215" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="C215" s="10"/>
-      <c r="D215" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E215" s="13" t="s">
-        <v>504</v>
+      <c r="B215" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="C215" s="11"/>
+      <c r="D215" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E215" s="14" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="216" ht="15.5" spans="1:5">
       <c r="A216">
         <v>215</v>
       </c>
-      <c r="B216" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="C216" s="10"/>
-      <c r="D216" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E216" s="11" t="s">
-        <v>506</v>
+      <c r="B216" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="C216" s="11"/>
+      <c r="D216" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="217" ht="15.5" spans="1:5">
       <c r="A217">
         <v>216</v>
       </c>
-      <c r="B217" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="C217" s="10"/>
-      <c r="D217" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E217" s="14" t="s">
-        <v>508</v>
+      <c r="B217" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E217" s="15" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="218" ht="15.5" spans="1:5">
       <c r="A218">
         <v>217</v>
       </c>
-      <c r="B218" s="10" t="s">
-        <v>509</v>
-      </c>
-      <c r="C218" s="10"/>
-      <c r="D218" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E218" s="11" t="s">
-        <v>510</v>
+      <c r="B218" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="C218" s="11"/>
+      <c r="D218" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="219" ht="15.5" spans="1:5">
       <c r="A219">
         <v>218</v>
       </c>
-      <c r="B219" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="C219" s="10"/>
-      <c r="D219" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E219" s="11" t="s">
-        <v>512</v>
+      <c r="B219" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="C219" s="11"/>
+      <c r="D219" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E219" s="12" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="220" ht="15.5" spans="1:5">
       <c r="A220">
         <v>219</v>
       </c>
-      <c r="B220" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="C220" s="10"/>
-      <c r="D220" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E220" s="11" t="s">
-        <v>514</v>
+      <c r="B220" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="C220" s="11"/>
+      <c r="D220" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E220" s="12" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="221" ht="15.5" spans="1:5">
       <c r="A221">
         <v>220</v>
       </c>
-      <c r="B221" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="C221" s="10"/>
-      <c r="D221" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E221" s="14" t="s">
-        <v>516</v>
+      <c r="B221" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="C221" s="11"/>
+      <c r="D221" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E221" s="15" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="222" ht="15.5" spans="1:5">
@@ -7434,14 +7477,14 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>517</v>
-      </c>
-      <c r="C222" s="10"/>
-      <c r="D222" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C222" s="11"/>
+      <c r="D222" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" ht="15.5" spans="1:5">
@@ -7451,12 +7494,12 @@
       <c r="B223" t="s">
         <v>265</v>
       </c>
-      <c r="C223" s="10"/>
-      <c r="D223" s="10" t="s">
+      <c r="C223" s="11"/>
+      <c r="D223" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="224" ht="15.5" spans="1:5">
@@ -7464,14 +7507,14 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>520</v>
-      </c>
-      <c r="C224" s="10"/>
-      <c r="D224" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C224" s="11"/>
+      <c r="D224" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="225" ht="15.5" spans="1:5">
@@ -7479,29 +7522,29 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>522</v>
-      </c>
-      <c r="C225" s="10"/>
-      <c r="D225" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="C225" s="11"/>
+      <c r="D225" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="226" ht="15.5" spans="1:5">
       <c r="A226">
         <v>225</v>
       </c>
-      <c r="B226" s="15" t="s">
-        <v>524</v>
-      </c>
-      <c r="C226" s="10"/>
-      <c r="D226" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E226" s="13" t="s">
-        <v>525</v>
+      <c r="B226" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="C226" s="11"/>
+      <c r="D226" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E226" s="14" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="227" ht="15.5" spans="1:5">
@@ -7509,121 +7552,121 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>526</v>
-      </c>
-      <c r="C227" s="10"/>
-      <c r="D227" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="C227" s="11"/>
+      <c r="D227" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="228" ht="15.5" spans="1:5">
       <c r="A228">
         <v>227</v>
       </c>
-      <c r="B228" s="16" t="s">
-        <v>528</v>
-      </c>
-      <c r="C228" s="10"/>
-      <c r="D228" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E228" s="13" t="s">
-        <v>529</v>
+      <c r="B228" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="C228" s="11"/>
+      <c r="D228" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E228" s="14" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="229" ht="15.5" spans="1:5">
       <c r="A229">
         <v>228</v>
       </c>
-      <c r="B229" s="16" t="s">
-        <v>530</v>
-      </c>
-      <c r="C229" s="10"/>
-      <c r="D229" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E229" s="12" t="s">
-        <v>531</v>
+      <c r="B229" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="C229" s="11"/>
+      <c r="D229" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E229" s="13" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="230" ht="15.5" spans="1:5">
       <c r="A230">
         <v>229</v>
       </c>
-      <c r="B230" s="13" t="s">
-        <v>532</v>
-      </c>
-      <c r="C230" s="10"/>
-      <c r="D230" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E230" s="12" t="s">
-        <v>533</v>
+      <c r="B230" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="C230" s="11"/>
+      <c r="D230" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E230" s="13" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="231" ht="15.5" spans="1:5">
       <c r="A231">
         <v>230</v>
       </c>
-      <c r="B231" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="C231" s="10"/>
-      <c r="D231" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E231" s="12" t="s">
-        <v>535</v>
+      <c r="B231" s="14" t="s">
+        <v>536</v>
+      </c>
+      <c r="C231" s="11"/>
+      <c r="D231" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E231" s="13" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="232" ht="15.5" spans="1:5">
       <c r="A232">
         <v>231</v>
       </c>
-      <c r="B232" s="16" t="s">
-        <v>536</v>
-      </c>
-      <c r="C232" s="10"/>
-      <c r="D232" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E232" s="12" t="s">
-        <v>537</v>
+      <c r="B232" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="C232" s="11"/>
+      <c r="D232" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E232" s="13" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="233" ht="15.5" spans="1:5">
       <c r="A233">
         <v>232</v>
       </c>
-      <c r="B233" s="16" t="s">
-        <v>538</v>
+      <c r="B233" s="17" t="s">
+        <v>540</v>
       </c>
       <c r="C233" t="s">
-        <v>539</v>
-      </c>
-      <c r="D233" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E233" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
+      </c>
+      <c r="D233" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E233" s="13" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="234" ht="15.5" spans="1:5">
       <c r="A234">
         <v>233</v>
       </c>
-      <c r="B234" s="17" t="s">
-        <v>541</v>
-      </c>
-      <c r="C234" s="10"/>
-      <c r="D234" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E234" s="12" t="s">
-        <v>542</v>
+      <c r="B234" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C234" s="11"/>
+      <c r="D234" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E234" s="13" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="235" ht="15.5" spans="1:5">
@@ -7631,119 +7674,119 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>543</v>
-      </c>
-      <c r="C235" s="10"/>
-      <c r="D235" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="C235" s="11"/>
+      <c r="D235" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="236" ht="15.5" spans="1:5">
       <c r="A236">
         <v>235</v>
       </c>
-      <c r="B236" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="C236" s="10"/>
-      <c r="D236" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E236" s="12" t="s">
-        <v>546</v>
+      <c r="B236" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="C236" s="11"/>
+      <c r="D236" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E236" s="13" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="237" ht="15.5" spans="1:5">
       <c r="A237">
         <v>236</v>
       </c>
-      <c r="B237" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="C237" s="10"/>
-      <c r="D237" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E237" s="12" t="s">
-        <v>548</v>
+      <c r="B237" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="C237" s="11"/>
+      <c r="D237" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E237" s="13" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="238" ht="15.5" spans="1:5">
       <c r="A238">
         <v>237</v>
       </c>
-      <c r="B238" s="13" t="s">
-        <v>549</v>
-      </c>
-      <c r="C238" s="10"/>
-      <c r="D238" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E238" s="12" t="s">
-        <v>550</v>
+      <c r="B238" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="C238" s="11"/>
+      <c r="D238" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E238" s="13" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="239" ht="15.5" spans="1:5">
       <c r="A239">
         <v>238</v>
       </c>
-      <c r="B239" s="16" t="s">
-        <v>551</v>
-      </c>
-      <c r="C239" s="10"/>
-      <c r="D239" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E239" s="12" t="s">
-        <v>552</v>
+      <c r="B239" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="C239" s="11"/>
+      <c r="D239" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E239" s="13" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="240" ht="15.5" spans="1:5">
       <c r="A240">
         <v>239</v>
       </c>
-      <c r="B240" s="16" t="s">
-        <v>553</v>
-      </c>
-      <c r="C240" s="10"/>
-      <c r="D240" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E240" s="12" t="s">
-        <v>554</v>
+      <c r="B240" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="C240" s="11"/>
+      <c r="D240" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E240" s="13" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="241" ht="15.5" spans="1:5">
       <c r="A241">
         <v>240</v>
       </c>
-      <c r="B241" s="16" t="s">
-        <v>555</v>
-      </c>
-      <c r="C241" s="10"/>
-      <c r="D241" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E241" s="13" t="s">
-        <v>556</v>
+      <c r="B241" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="C241" s="11"/>
+      <c r="D241" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E241" s="14" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="242" ht="15.5" spans="1:5">
       <c r="A242">
         <v>241</v>
       </c>
-      <c r="B242" s="16" t="s">
-        <v>557</v>
-      </c>
-      <c r="C242" s="10"/>
-      <c r="D242" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E242" s="12" t="s">
-        <v>558</v>
+      <c r="B242" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="C242" s="11"/>
+      <c r="D242" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E242" s="13" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -7751,13 +7794,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D243" t="s">
-        <v>560</v>
-      </c>
-      <c r="E243" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
+      </c>
+      <c r="E243" s="14" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -7765,58 +7808,58 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D244" t="s">
-        <v>562</v>
-      </c>
-      <c r="E244" s="13" t="s">
-        <v>563</v>
+        <v>564</v>
+      </c>
+      <c r="E244" s="14" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="245" ht="15.5" spans="1:5">
       <c r="A245">
         <v>244</v>
       </c>
-      <c r="B245" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="C245" s="10"/>
-      <c r="D245" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E245" s="13" t="s">
-        <v>565</v>
+      <c r="B245" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="C245" s="11"/>
+      <c r="D245" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E245" s="14" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="246" ht="15.5" spans="1:5">
       <c r="A246">
         <v>245</v>
       </c>
-      <c r="B246" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="C246" s="10"/>
-      <c r="D246" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E246" s="12" t="s">
-        <v>567</v>
+      <c r="B246" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="C246" s="11"/>
+      <c r="D246" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E246" s="13" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="247" ht="15.5" spans="1:5">
       <c r="A247">
         <v>246</v>
       </c>
-      <c r="B247" s="16" t="s">
-        <v>568</v>
-      </c>
-      <c r="C247" s="10"/>
-      <c r="D247" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E247" s="12" t="s">
-        <v>569</v>
+      <c r="B247" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="C247" s="11"/>
+      <c r="D247" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E247" s="13" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="248" ht="15.5" spans="1:5">
@@ -7824,181 +7867,181 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>570</v>
-      </c>
-      <c r="C248" s="10"/>
-      <c r="D248" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E248" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
+      </c>
+      <c r="C248" s="11"/>
+      <c r="D248" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E248" s="13" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="249" ht="15.5" spans="1:5">
       <c r="A249">
         <v>248</v>
       </c>
-      <c r="B249" s="18" t="s">
-        <v>572</v>
-      </c>
-      <c r="C249" s="10"/>
-      <c r="D249" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E249" s="12" t="s">
-        <v>573</v>
+      <c r="B249" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="C249" s="11"/>
+      <c r="D249" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E249" s="13" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="250" ht="15.5" spans="1:5">
       <c r="A250">
         <v>249</v>
       </c>
-      <c r="B250" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="C250" s="10"/>
-      <c r="D250" s="10" t="s">
+      <c r="B250" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="C250" s="11"/>
+      <c r="D250" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="251" ht="15.5" spans="1:5">
       <c r="A251">
         <v>250</v>
       </c>
-      <c r="B251" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="C251" s="10"/>
-      <c r="D251" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E251" s="12" t="s">
-        <v>577</v>
+      <c r="B251" s="14" t="s">
+        <v>578</v>
+      </c>
+      <c r="C251" s="11"/>
+      <c r="D251" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E251" s="13" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="252" ht="15.5" spans="1:5">
       <c r="A252">
         <v>251</v>
       </c>
-      <c r="B252" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="C252" s="10"/>
-      <c r="D252" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E252" s="13" t="s">
-        <v>579</v>
+      <c r="B252" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="C252" s="11"/>
+      <c r="D252" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E252" s="14" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="253" ht="15.5" spans="1:5">
       <c r="A253">
         <v>252</v>
       </c>
-      <c r="B253" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="C253" s="10"/>
-      <c r="D253" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E253" s="12" t="s">
-        <v>581</v>
+      <c r="B253" s="14" t="s">
+        <v>582</v>
+      </c>
+      <c r="C253" s="11"/>
+      <c r="D253" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E253" s="13" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="254" ht="15.5" spans="1:5">
       <c r="A254">
         <v>253</v>
       </c>
-      <c r="B254" s="13" t="s">
-        <v>582</v>
-      </c>
-      <c r="C254" s="10"/>
-      <c r="D254" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E254" s="12" t="s">
-        <v>583</v>
+      <c r="B254" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="C254" s="11"/>
+      <c r="D254" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E254" s="13" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="255" ht="15.5" spans="1:5">
       <c r="A255">
         <v>254</v>
       </c>
-      <c r="B255" s="17" t="s">
-        <v>584</v>
-      </c>
-      <c r="C255" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="D255" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E255" s="12" t="s">
+      <c r="B255" s="18" t="s">
         <v>586</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="D255" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E255" s="13" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="256" ht="15.5" spans="1:5">
       <c r="A256">
         <v>255</v>
       </c>
-      <c r="B256" s="20" t="s">
-        <v>587</v>
-      </c>
-      <c r="C256" s="10"/>
-      <c r="D256" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E256" s="13" t="s">
-        <v>588</v>
+      <c r="B256" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="C256" s="11"/>
+      <c r="D256" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E256" s="14" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="257" ht="15.5" spans="1:5">
       <c r="A257">
         <v>256</v>
       </c>
-      <c r="B257" s="13" t="s">
-        <v>589</v>
-      </c>
-      <c r="C257" s="10"/>
-      <c r="D257" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E257" s="12" t="s">
-        <v>590</v>
+      <c r="B257" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="C257" s="11"/>
+      <c r="D257" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E257" s="13" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="258" ht="15.5" spans="1:5">
       <c r="A258">
         <v>257</v>
       </c>
-      <c r="B258" s="13" t="s">
-        <v>591</v>
-      </c>
-      <c r="C258" s="10"/>
-      <c r="D258" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E258" s="12" t="s">
-        <v>592</v>
+      <c r="B258" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="C258" s="11"/>
+      <c r="D258" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E258" s="13" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="259" ht="15.5" spans="1:5">
       <c r="A259">
         <v>258</v>
       </c>
-      <c r="B259" s="13" t="s">
-        <v>593</v>
-      </c>
-      <c r="C259" s="10"/>
-      <c r="D259" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E259" s="12" t="s">
-        <v>594</v>
+      <c r="B259" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="C259" s="11"/>
+      <c r="D259" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E259" s="13" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="260" ht="15.5" spans="1:5">
@@ -8006,438 +8049,438 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>595</v>
-      </c>
-      <c r="C260" s="10"/>
-      <c r="D260" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E260" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
+      </c>
+      <c r="C260" s="11"/>
+      <c r="D260" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E260" s="13" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="261" ht="15.5" spans="1:5">
       <c r="A261">
         <v>260</v>
       </c>
-      <c r="B261" s="20" t="s">
-        <v>597</v>
-      </c>
-      <c r="C261" s="10"/>
-      <c r="D261" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E261" s="13" t="s">
-        <v>598</v>
+      <c r="B261" s="21" t="s">
+        <v>599</v>
+      </c>
+      <c r="C261" s="11"/>
+      <c r="D261" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E261" s="14" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="262" ht="15.5" spans="1:5">
       <c r="A262">
         <v>261</v>
       </c>
-      <c r="B262" s="16" t="s">
-        <v>599</v>
-      </c>
-      <c r="C262" s="10"/>
-      <c r="D262" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E262" s="12" t="s">
-        <v>600</v>
+      <c r="B262" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="C262" s="11"/>
+      <c r="D262" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E262" s="13" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="263" ht="15.5" spans="1:5">
       <c r="A263">
         <v>262</v>
       </c>
-      <c r="B263" s="13" t="s">
-        <v>601</v>
-      </c>
-      <c r="C263" s="10"/>
-      <c r="D263" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E263" s="12" t="s">
-        <v>602</v>
+      <c r="B263" s="14" t="s">
+        <v>603</v>
+      </c>
+      <c r="C263" s="11"/>
+      <c r="D263" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E263" s="13" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="264" ht="15.5" spans="1:5">
       <c r="A264">
         <v>263</v>
       </c>
-      <c r="B264" s="13" t="s">
-        <v>603</v>
-      </c>
-      <c r="C264" s="10"/>
-      <c r="D264" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E264" s="13" t="s">
-        <v>604</v>
+      <c r="B264" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="C264" s="11"/>
+      <c r="D264" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E264" s="14" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="265" ht="15.5" spans="1:5">
       <c r="A265">
         <v>264</v>
       </c>
-      <c r="B265" s="13" t="s">
-        <v>605</v>
-      </c>
-      <c r="C265" s="10"/>
-      <c r="D265" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E265" s="13" t="s">
-        <v>606</v>
+      <c r="B265" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="C265" s="11"/>
+      <c r="D265" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E265" s="14" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="266" ht="15.5" spans="1:5">
       <c r="A266">
         <v>265</v>
       </c>
-      <c r="B266" s="17" t="s">
-        <v>607</v>
-      </c>
-      <c r="C266" s="10"/>
-      <c r="D266" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E266" s="13" t="s">
-        <v>608</v>
+      <c r="B266" s="18" t="s">
+        <v>609</v>
+      </c>
+      <c r="C266" s="11"/>
+      <c r="D266" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E266" s="14" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="267" ht="15.5" spans="1:5">
       <c r="A267">
         <v>266</v>
       </c>
-      <c r="B267" s="17" t="s">
-        <v>609</v>
-      </c>
-      <c r="C267" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="D267" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E267" s="13" t="s">
+      <c r="B267" s="18" t="s">
         <v>611</v>
+      </c>
+      <c r="C267" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="D267" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E267" s="14" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="268" ht="15.5" spans="1:5">
       <c r="A268">
         <v>267</v>
       </c>
-      <c r="B268" s="13" t="s">
-        <v>612</v>
-      </c>
-      <c r="C268" s="10"/>
-      <c r="D268" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E268" s="13" t="s">
-        <v>613</v>
+      <c r="B268" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="C268" s="11"/>
+      <c r="D268" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E268" s="14" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="269" ht="15.5" spans="1:5">
       <c r="A269">
         <v>268</v>
       </c>
-      <c r="B269" s="13" t="s">
-        <v>614</v>
-      </c>
-      <c r="C269" s="10"/>
-      <c r="D269" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E269" s="13" t="s">
-        <v>615</v>
+      <c r="B269" s="14" t="s">
+        <v>616</v>
+      </c>
+      <c r="C269" s="11"/>
+      <c r="D269" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E269" s="14" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="270" ht="15.5" spans="1:5">
       <c r="A270">
         <v>269</v>
       </c>
-      <c r="B270" s="13" t="s">
-        <v>616</v>
-      </c>
-      <c r="C270" s="10"/>
-      <c r="D270" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E270" s="13" t="s">
-        <v>617</v>
+      <c r="B270" s="14" t="s">
+        <v>618</v>
+      </c>
+      <c r="C270" s="11"/>
+      <c r="D270" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E270" s="14" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="271" ht="15.5" spans="1:5">
       <c r="A271">
         <v>270</v>
       </c>
-      <c r="B271" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="C271" s="10"/>
-      <c r="D271" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E271" s="13" t="s">
-        <v>619</v>
+      <c r="B271" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="C271" s="11"/>
+      <c r="D271" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E271" s="14" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="272" ht="15.5" spans="1:5">
       <c r="A272">
         <v>271</v>
       </c>
-      <c r="B272" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="C272" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="D272" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E272" s="13" t="s">
+      <c r="B272" s="18" t="s">
         <v>622</v>
+      </c>
+      <c r="C272" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="D272" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E272" s="14" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="273" ht="15.5" spans="1:5">
       <c r="A273">
         <v>272</v>
       </c>
-      <c r="B273" s="13" t="s">
-        <v>623</v>
-      </c>
-      <c r="C273" s="10"/>
-      <c r="D273" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E273" s="13" t="s">
-        <v>624</v>
+      <c r="B273" s="14" t="s">
+        <v>625</v>
+      </c>
+      <c r="C273" s="11"/>
+      <c r="D273" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E273" s="14" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="274" ht="15.5" spans="1:5">
       <c r="A274">
         <v>273</v>
       </c>
-      <c r="B274" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="C274" s="10"/>
-      <c r="D274" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E274" s="13" t="s">
-        <v>626</v>
+      <c r="B274" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="C274" s="11"/>
+      <c r="D274" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E274" s="14" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="275" ht="15.5" spans="1:5">
       <c r="A275">
         <v>274</v>
       </c>
-      <c r="B275" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="C275" s="10"/>
-      <c r="D275" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E275" s="13" t="s">
-        <v>628</v>
+      <c r="B275" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="C275" s="11"/>
+      <c r="D275" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E275" s="14" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="276" ht="15.5" spans="1:5">
       <c r="A276">
         <v>275</v>
       </c>
-      <c r="B276" s="13" t="s">
-        <v>629</v>
-      </c>
-      <c r="C276" s="10"/>
-      <c r="D276" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E276" s="13" t="s">
-        <v>630</v>
+      <c r="B276" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="C276" s="11"/>
+      <c r="D276" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E276" s="14" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="277" ht="15.5" spans="1:5">
       <c r="A277">
         <v>276</v>
       </c>
-      <c r="B277" s="13" t="s">
-        <v>631</v>
-      </c>
-      <c r="C277" s="10"/>
-      <c r="D277" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E277" s="13" t="s">
-        <v>632</v>
+      <c r="B277" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C277" s="11"/>
+      <c r="D277" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E277" s="14" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="278" ht="15.5" spans="1:5">
       <c r="A278">
         <v>277</v>
       </c>
-      <c r="B278" s="13" t="s">
-        <v>633</v>
-      </c>
-      <c r="C278" s="10"/>
-      <c r="D278" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E278" s="13" t="s">
-        <v>634</v>
+      <c r="B278" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C278" s="11"/>
+      <c r="D278" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E278" s="14" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="279" ht="15.5" spans="1:5">
       <c r="A279">
         <v>278</v>
       </c>
-      <c r="B279" s="13" t="s">
-        <v>635</v>
-      </c>
-      <c r="C279" s="10"/>
-      <c r="D279" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E279" s="13" t="s">
-        <v>636</v>
+      <c r="B279" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="C279" s="11"/>
+      <c r="D279" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E279" s="14" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="280" ht="15.5" spans="1:5">
       <c r="A280">
         <v>279</v>
       </c>
-      <c r="B280" s="13" t="s">
-        <v>637</v>
-      </c>
-      <c r="C280" s="10"/>
-      <c r="D280" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E280" s="13" t="s">
-        <v>638</v>
+      <c r="B280" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="C280" s="11"/>
+      <c r="D280" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E280" s="14" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="281" ht="15.5" spans="1:5">
       <c r="A281">
         <v>280</v>
       </c>
-      <c r="B281" s="13" t="s">
-        <v>639</v>
-      </c>
-      <c r="C281" s="10"/>
-      <c r="D281" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E281" s="13" t="s">
-        <v>640</v>
+      <c r="B281" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="C281" s="11"/>
+      <c r="D281" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E281" s="14" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="282" ht="15.5" spans="1:5">
       <c r="A282">
         <v>281</v>
       </c>
-      <c r="B282" s="13" t="s">
-        <v>641</v>
-      </c>
-      <c r="C282" s="10"/>
-      <c r="D282" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E282" s="13" t="s">
-        <v>642</v>
+      <c r="B282" s="14" t="s">
+        <v>643</v>
+      </c>
+      <c r="C282" s="11"/>
+      <c r="D282" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E282" s="14" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="283" ht="15.5" spans="1:5">
       <c r="A283">
         <v>282</v>
       </c>
-      <c r="B283" s="13" t="s">
-        <v>643</v>
-      </c>
-      <c r="C283" s="10"/>
-      <c r="D283" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E283" s="13" t="s">
-        <v>644</v>
+      <c r="B283" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="C283" s="11"/>
+      <c r="D283" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E283" s="14" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="284" ht="15.5" spans="1:5">
       <c r="A284">
         <v>283</v>
       </c>
-      <c r="B284" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="C284" s="10"/>
-      <c r="D284" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E284" s="13" t="s">
-        <v>646</v>
+      <c r="B284" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="C284" s="11"/>
+      <c r="D284" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E284" s="14" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="285" ht="15.5" spans="1:5">
       <c r="A285">
         <v>284</v>
       </c>
-      <c r="B285" s="13" t="s">
-        <v>647</v>
-      </c>
-      <c r="C285" s="10"/>
-      <c r="D285" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E285" s="13" t="s">
-        <v>648</v>
+      <c r="B285" s="14" t="s">
+        <v>649</v>
+      </c>
+      <c r="C285" s="11"/>
+      <c r="D285" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E285" s="14" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="286" ht="15.5" spans="1:5">
       <c r="A286">
         <v>285</v>
       </c>
-      <c r="B286" s="17" t="s">
-        <v>649</v>
-      </c>
-      <c r="C286" s="10"/>
-      <c r="D286" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E286" s="13" t="s">
-        <v>650</v>
+      <c r="B286" s="18" t="s">
+        <v>651</v>
+      </c>
+      <c r="C286" s="11"/>
+      <c r="D286" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E286" s="14" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="287" ht="15.5" spans="1:5">
       <c r="A287">
         <v>286</v>
       </c>
-      <c r="B287" s="13" t="s">
-        <v>651</v>
-      </c>
-      <c r="C287" s="10"/>
-      <c r="D287" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E287" s="13" t="s">
-        <v>652</v>
+      <c r="B287" s="14" t="s">
+        <v>653</v>
+      </c>
+      <c r="C287" s="11"/>
+      <c r="D287" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E287" s="14" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="288" ht="15.5" spans="1:5">
       <c r="A288">
         <v>287</v>
       </c>
-      <c r="B288" s="13" t="s">
-        <v>653</v>
-      </c>
-      <c r="C288" s="10"/>
-      <c r="D288" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E288" s="13" t="s">
-        <v>654</v>
+      <c r="B288" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="C288" s="11"/>
+      <c r="D288" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E288" s="14" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="289" ht="15" spans="1:5">
@@ -8445,14 +8488,14 @@
         <v>288</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C289" s="8"/>
       <c r="D289" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E289" s="21" t="s">
-        <v>656</v>
+      <c r="E289" s="10" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="290" ht="15" spans="1:5">
@@ -8460,14 +8503,14 @@
         <v>289</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C290" s="8"/>
       <c r="D290" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E290" s="8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="291" ht="15" spans="1:5">
@@ -8475,16 +8518,16 @@
         <v>290</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D291" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E291" s="8" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="292" ht="15" spans="1:5">
@@ -8492,70 +8535,70 @@
         <v>291</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C292" s="8"/>
       <c r="D292" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E292" s="8" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="293" ht="15" spans="1:5">
       <c r="A293">
         <v>292</v>
       </c>
-      <c r="B293" s="13" t="s">
-        <v>664</v>
+      <c r="B293" s="14" t="s">
+        <v>666</v>
       </c>
       <c r="D293" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E293" s="13" t="s">
-        <v>665</v>
+      <c r="E293" s="14" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="294" ht="15" spans="1:5">
       <c r="A294">
         <v>293</v>
       </c>
-      <c r="B294" s="13" t="s">
-        <v>666</v>
+      <c r="B294" s="14" t="s">
+        <v>668</v>
       </c>
       <c r="D294" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E294" s="13" t="s">
-        <v>667</v>
+      <c r="E294" s="14" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="295" ht="15" spans="1:5">
       <c r="A295">
         <v>294</v>
       </c>
-      <c r="B295" s="13" t="s">
-        <v>668</v>
+      <c r="B295" s="14" t="s">
+        <v>670</v>
       </c>
       <c r="D295" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E295" s="13" t="s">
-        <v>669</v>
+      <c r="E295" s="14" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="296" ht="15" spans="1:5">
       <c r="A296">
         <v>295</v>
       </c>
-      <c r="B296" s="13" t="s">
-        <v>670</v>
+      <c r="B296" s="14" t="s">
+        <v>672</v>
       </c>
       <c r="D296" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E296" s="12" t="s">
-        <v>671</v>
+      <c r="E296" s="13" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="297" ht="15" spans="1:5">
@@ -8563,14 +8606,14 @@
         <v>296</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C297" s="8"/>
       <c r="D297" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E297" s="8" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="298" ht="15" spans="1:5">
@@ -8578,14 +8621,14 @@
         <v>297</v>
       </c>
       <c r="B298" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C298" s="8"/>
       <c r="D298" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E298" s="8" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="299" ht="15" spans="1:5">
@@ -8593,14 +8636,14 @@
         <v>298</v>
       </c>
       <c r="B299" s="8" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C299" s="8"/>
       <c r="D299" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E299" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="300" ht="15" spans="1:5">
@@ -8608,14 +8651,14 @@
         <v>299</v>
       </c>
       <c r="B300" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C300" s="8"/>
       <c r="D300" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E300" s="8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="301" ht="15" spans="1:5">
@@ -8623,14 +8666,14 @@
         <v>300</v>
       </c>
       <c r="B301" s="8" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C301" s="8"/>
       <c r="D301" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E301" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="302" ht="15" spans="1:5">
@@ -8638,14 +8681,14 @@
         <v>301</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C302" s="8"/>
       <c r="D302" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E302" s="8" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="303" ht="15" spans="1:5">
@@ -8653,16 +8696,16 @@
         <v>302</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C303" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D303" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E303" s="8" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="304" ht="15" spans="1:5">
@@ -8670,14 +8713,14 @@
         <v>303</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C304" s="8"/>
       <c r="D304" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E304" s="8" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="305" ht="15" spans="1:5">
@@ -8685,14 +8728,14 @@
         <v>304</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C305" s="8"/>
       <c r="D305" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E305" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="306" ht="15" spans="1:5">
@@ -8700,14 +8743,14 @@
         <v>305</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C306" s="8"/>
       <c r="D306" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E306" s="8" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="307" ht="15" spans="1:5">
@@ -8715,14 +8758,14 @@
         <v>306</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C307" s="8"/>
       <c r="D307" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E307" s="8" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="308" ht="15" spans="1:5">
@@ -8730,14 +8773,14 @@
         <v>307</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C308" s="8"/>
       <c r="D308" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E308" s="8" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="309" ht="15" spans="1:5">
@@ -8745,14 +8788,14 @@
         <v>308</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C309" s="8"/>
       <c r="D309" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E309" s="8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="310" ht="15" spans="1:5">
@@ -8760,14 +8803,14 @@
         <v>309</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C310" s="8"/>
       <c r="D310" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E310" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="311" ht="15" spans="1:5">
@@ -8775,14 +8818,14 @@
         <v>310</v>
       </c>
       <c r="B311" s="8" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C311" s="8"/>
       <c r="D311" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E311" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="312" ht="15" spans="1:5">
@@ -8790,70 +8833,70 @@
         <v>311</v>
       </c>
       <c r="B312" s="8" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C312" s="8"/>
       <c r="D312" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E312" s="8" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="313" ht="15" spans="1:5">
       <c r="A313">
         <v>312</v>
       </c>
-      <c r="B313" s="13" t="s">
-        <v>705</v>
+      <c r="B313" s="14" t="s">
+        <v>707</v>
       </c>
       <c r="D313" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E313" s="13" t="s">
-        <v>706</v>
+      <c r="E313" s="14" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="314" ht="15" spans="1:5">
       <c r="A314">
         <v>313</v>
       </c>
-      <c r="B314" s="17" t="s">
-        <v>707</v>
+      <c r="B314" s="18" t="s">
+        <v>709</v>
       </c>
       <c r="D314" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E314" s="12" t="s">
-        <v>708</v>
+      <c r="E314" s="13" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="315" ht="15" spans="1:5">
       <c r="A315">
         <v>314</v>
       </c>
-      <c r="B315" s="17" t="s">
-        <v>709</v>
+      <c r="B315" s="18" t="s">
+        <v>711</v>
       </c>
       <c r="D315" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E315" s="13" t="s">
-        <v>710</v>
+      <c r="E315" s="14" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="316" ht="15" spans="1:5">
       <c r="A316">
         <v>315</v>
       </c>
-      <c r="B316" s="17" t="s">
-        <v>711</v>
+      <c r="B316" s="18" t="s">
+        <v>713</v>
       </c>
       <c r="D316" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E316" s="13" t="s">
-        <v>712</v>
+      <c r="E316" s="14" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="317" ht="15" spans="1:5">
@@ -8861,14 +8904,14 @@
         <v>316</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C317" s="8"/>
       <c r="D317" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E317" s="8" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="318" ht="15" spans="1:5">
@@ -8876,14 +8919,14 @@
         <v>317</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C318" s="8"/>
       <c r="D318" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="319" ht="15" spans="1:5">
@@ -8891,14 +8934,14 @@
         <v>318</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C319" s="8"/>
       <c r="D319" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E319" s="8" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="320" ht="15" spans="1:5">
@@ -8906,14 +8949,14 @@
         <v>319</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C320" s="8"/>
       <c r="D320" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E320" s="8" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="321" ht="15" spans="1:5">
@@ -8921,14 +8964,14 @@
         <v>320</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C321" s="8"/>
       <c r="D321" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E321" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="322" ht="15" spans="1:5">
@@ -8936,14 +8979,14 @@
         <v>321</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C322" s="8"/>
       <c r="D322" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E322" s="8" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="323" ht="15" spans="1:5">
@@ -8951,14 +8994,14 @@
         <v>322</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C323" s="8"/>
       <c r="D323" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E323" s="8" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="324" ht="15" spans="1:5">
@@ -8966,14 +9009,14 @@
         <v>323</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C324" s="8"/>
       <c r="D324" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E324" s="8" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="325" ht="15" spans="1:5">
@@ -8981,14 +9024,14 @@
         <v>324</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C325" s="8"/>
       <c r="D325" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E325" s="8" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="326" ht="15" spans="1:5">
@@ -8996,14 +9039,14 @@
         <v>325</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C326" s="8"/>
       <c r="D326" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E326" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="327" ht="15" spans="1:5">
@@ -9011,14 +9054,14 @@
         <v>326</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C327" s="8"/>
       <c r="D327" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E327" s="8" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="328" ht="15" spans="1:5">
@@ -9026,14 +9069,14 @@
         <v>327</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C328" s="8"/>
       <c r="D328" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E328" s="8" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="329" ht="15" spans="1:5">
@@ -9041,14 +9084,14 @@
         <v>328</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C329" s="8"/>
       <c r="D329" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E329" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="330" ht="15" spans="1:5">
@@ -9056,14 +9099,14 @@
         <v>329</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C330" s="8"/>
       <c r="D330" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E330" s="8" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="331" ht="15" spans="1:5">
@@ -9071,14 +9114,14 @@
         <v>330</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C331" s="8"/>
       <c r="D331" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E331" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="332" ht="15" spans="1:5">
@@ -9086,14 +9129,14 @@
         <v>331</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C332" s="8"/>
       <c r="D332" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E332" s="8" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="333" ht="15" spans="1:5">
@@ -9101,14 +9144,14 @@
         <v>332</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C333" s="8"/>
       <c r="D333" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E333" s="8" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="334" ht="15" spans="1:5">
@@ -9116,14 +9159,14 @@
         <v>333</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C334" s="8"/>
       <c r="D334" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E334" s="8" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="335" ht="15" spans="1:5">
@@ -9131,14 +9174,14 @@
         <v>334</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C335" s="8"/>
       <c r="D335" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E335" s="8" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="336" ht="15" spans="1:5">
@@ -9146,14 +9189,14 @@
         <v>335</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C336" s="8"/>
       <c r="D336" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E336" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="337" ht="15" spans="1:5">
@@ -9161,14 +9204,14 @@
         <v>336</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C337" s="8"/>
       <c r="D337" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E337" s="8" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="338" ht="15" spans="1:5">
@@ -9176,14 +9219,14 @@
         <v>337</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C338" s="8"/>
       <c r="D338" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E338" s="8" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="339" ht="15" spans="1:5">
@@ -9191,14 +9234,14 @@
         <v>338</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C339" s="8"/>
       <c r="D339" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E339" s="8" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="340" ht="15" spans="1:5">
@@ -9206,14 +9249,14 @@
         <v>339</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C340" s="8"/>
       <c r="D340" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E340" s="8" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="341" ht="15" spans="1:5">
@@ -9221,14 +9264,14 @@
         <v>340</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C341" s="8"/>
       <c r="D341" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E341" s="8" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="342" ht="15" spans="1:5">
@@ -9236,14 +9279,14 @@
         <v>341</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C342" s="8"/>
       <c r="D342" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E342" s="8" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="343" ht="15" spans="1:5">
@@ -9251,14 +9294,14 @@
         <v>342</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C343" s="8"/>
       <c r="D343" s="8" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E343" s="8" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -9266,16 +9309,16 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>768</v>
-      </c>
-      <c r="C344" s="16" t="s">
-        <v>769</v>
+        <v>770</v>
+      </c>
+      <c r="C344" s="17" t="s">
+        <v>771</v>
       </c>
       <c r="D344" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -9283,30 +9326,30 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D345" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="346" ht="15" spans="1:5">
       <c r="A346">
         <v>345</v>
       </c>
-      <c r="B346" s="17" t="s">
-        <v>775</v>
+      <c r="B346" s="18" t="s">
+        <v>777</v>
       </c>
       <c r="C346" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D346" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E346" s="13" t="s">
-        <v>777</v>
+      <c r="E346" s="14" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="347" ht="15" spans="1:5">
@@ -9314,14 +9357,14 @@
         <v>346</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C347" s="8"/>
       <c r="D347" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E347" s="8" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="348" ht="15" spans="1:5">
@@ -9329,14 +9372,14 @@
         <v>347</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C348" s="8"/>
       <c r="D348" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E348" s="8" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="349" ht="15" spans="1:5">
@@ -9344,14 +9387,14 @@
         <v>348</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C349" s="8"/>
       <c r="D349" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="350" ht="15" spans="1:5">
@@ -9359,14 +9402,14 @@
         <v>349</v>
       </c>
       <c r="B350" s="8" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C350" s="8"/>
       <c r="D350" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E350" s="8" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="351" ht="15" spans="1:5">
@@ -9374,14 +9417,14 @@
         <v>350</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C351" s="8"/>
       <c r="D351" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E351" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="352" ht="15" spans="1:5">
@@ -9389,14 +9432,14 @@
         <v>351</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C352" s="8"/>
       <c r="D352" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E352" s="8" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="353" ht="15" spans="1:5">
@@ -9404,14 +9447,14 @@
         <v>352</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C353" s="8"/>
       <c r="D353" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E353" s="8" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="354" ht="15" spans="1:5">
@@ -9419,14 +9462,14 @@
         <v>353</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C354" s="8"/>
       <c r="D354" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E354" s="8" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="355" ht="15" spans="1:5">
@@ -9434,14 +9477,14 @@
         <v>354</v>
       </c>
       <c r="B355" s="8" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C355" s="8"/>
       <c r="D355" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E355" s="8" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="356" ht="15" spans="1:5">
@@ -9449,14 +9492,14 @@
         <v>355</v>
       </c>
       <c r="B356" s="8" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C356" s="8"/>
       <c r="D356" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E356" s="8" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="357" ht="15" spans="1:5">
@@ -9464,14 +9507,14 @@
         <v>356</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C357" s="8"/>
       <c r="D357" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E357" s="8" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="358" ht="15" spans="1:5">
@@ -9479,14 +9522,14 @@
         <v>357</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C358" s="8"/>
       <c r="D358" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E358" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="359" ht="15" spans="1:5">
@@ -9494,14 +9537,14 @@
         <v>358</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C359" s="8"/>
       <c r="D359" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E359" s="8" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="360" ht="15" spans="1:5">
@@ -9509,14 +9552,14 @@
         <v>359</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C360" s="8"/>
       <c r="D360" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E360" s="8" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="361" ht="15" spans="1:5">
@@ -9524,14 +9567,14 @@
         <v>360</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C361" s="8"/>
       <c r="D361" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E361" s="8" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="362" ht="15" spans="1:5">
@@ -9539,14 +9582,14 @@
         <v>361</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C362" s="8"/>
       <c r="D362" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E362" s="8" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="363" ht="15" spans="1:5">
@@ -9554,14 +9597,14 @@
         <v>362</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C363" s="8"/>
       <c r="D363" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E363" s="8" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="364" ht="15" spans="1:5">
@@ -9569,14 +9612,14 @@
         <v>363</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C364" s="8"/>
       <c r="D364" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E364" s="8" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="365" ht="15" spans="1:5">
@@ -9584,14 +9627,14 @@
         <v>364</v>
       </c>
       <c r="B365" s="8" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C365" s="8"/>
       <c r="D365" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E365" s="8" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="366" ht="15" spans="1:5">
@@ -9599,14 +9642,14 @@
         <v>365</v>
       </c>
       <c r="B366" s="8" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C366" s="8"/>
       <c r="D366" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E366" s="8" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="367" ht="15" spans="1:5">
@@ -9614,14 +9657,14 @@
         <v>366</v>
       </c>
       <c r="B367" s="8" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C367" s="8"/>
       <c r="D367" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E367" s="8" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="368" ht="15" spans="1:5">
@@ -9629,14 +9672,14 @@
         <v>367</v>
       </c>
       <c r="B368" s="8" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C368" s="8"/>
       <c r="D368" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E368" s="8" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="369" ht="15" spans="1:5">
@@ -9644,14 +9687,14 @@
         <v>368</v>
       </c>
       <c r="B369" s="8" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C369" s="8"/>
       <c r="D369" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E369" s="8" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="370" ht="15" spans="1:5">
@@ -9659,14 +9702,14 @@
         <v>369</v>
       </c>
       <c r="B370" s="8" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C370" s="8"/>
       <c r="D370" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E370" s="8" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="371" ht="15" spans="1:5">
@@ -9674,14 +9717,14 @@
         <v>370</v>
       </c>
       <c r="B371" s="8" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C371" s="8"/>
       <c r="D371" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E371" s="8" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="372" ht="15" spans="1:5">
@@ -9689,14 +9732,14 @@
         <v>371</v>
       </c>
       <c r="B372" s="8" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C372" s="8"/>
       <c r="D372" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E372" s="8" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="373" ht="15" spans="1:5">
@@ -9704,14 +9747,14 @@
         <v>372</v>
       </c>
       <c r="B373" s="8" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C373" s="8"/>
       <c r="D373" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E373" s="8" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="374" ht="15" spans="1:5">
@@ -9719,14 +9762,14 @@
         <v>373</v>
       </c>
       <c r="B374" s="8" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C374" s="8"/>
       <c r="D374" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E374" s="8" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="375" ht="15" spans="1:5">
@@ -9734,14 +9777,14 @@
         <v>374</v>
       </c>
       <c r="B375" s="8" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C375" s="8"/>
       <c r="D375" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E375" s="8" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="376" ht="15" spans="1:5">
@@ -9749,14 +9792,14 @@
         <v>375</v>
       </c>
       <c r="B376" s="8" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C376" s="8"/>
       <c r="D376" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E376" s="8" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="377" ht="15" spans="1:5">
@@ -9764,14 +9807,14 @@
         <v>376</v>
       </c>
       <c r="B377" s="8" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C377" s="8"/>
       <c r="D377" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E377" s="8" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="378" ht="15" spans="1:5">
@@ -9779,14 +9822,14 @@
         <v>377</v>
       </c>
       <c r="B378" s="8" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C378" s="8"/>
       <c r="D378" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E378" s="8" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="379" ht="15" spans="1:5">
@@ -9794,14 +9837,14 @@
         <v>378</v>
       </c>
       <c r="B379" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C379" s="8"/>
       <c r="D379" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E379" s="8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="380" ht="15" spans="1:5">
@@ -9809,14 +9852,14 @@
         <v>379</v>
       </c>
       <c r="B380" s="8" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C380" s="8"/>
       <c r="D380" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E380" s="8" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="381" ht="15" spans="1:5">
@@ -9824,14 +9867,14 @@
         <v>380</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C381" s="8"/>
       <c r="D381" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E381" s="8" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="382" ht="15" spans="1:5">
@@ -9839,14 +9882,14 @@
         <v>381</v>
       </c>
       <c r="B382" s="8" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C382" s="8"/>
       <c r="D382" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E382" s="8" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="383" ht="15" spans="1:5">
@@ -9854,14 +9897,14 @@
         <v>382</v>
       </c>
       <c r="B383" s="8" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C383" s="8"/>
       <c r="D383" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E383" s="8" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="384" ht="15" spans="1:5">
@@ -9869,14 +9912,14 @@
         <v>383</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C384" s="8"/>
       <c r="D384" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E384" s="8" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="385" ht="15" spans="1:5">
@@ -9884,14 +9927,14 @@
         <v>384</v>
       </c>
       <c r="B385" s="8" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C385" s="8"/>
       <c r="D385" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E385" s="8" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="386" ht="15" spans="1:5">
@@ -9899,14 +9942,14 @@
         <v>385</v>
       </c>
       <c r="B386" s="8" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C386" s="8"/>
       <c r="D386" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E386" s="8" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="387" ht="15" spans="1:5">
@@ -9914,14 +9957,14 @@
         <v>386</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C387" s="8"/>
       <c r="D387" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E387" s="8" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="388" ht="15" spans="1:5">
@@ -9929,14 +9972,14 @@
         <v>387</v>
       </c>
       <c r="B388" s="8" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C388" s="8"/>
       <c r="D388" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E388" s="8" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="389" ht="15" spans="1:5">
@@ -9944,14 +9987,14 @@
         <v>388</v>
       </c>
       <c r="B389" s="8" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C389" s="8"/>
       <c r="D389" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E389" s="8" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="390" ht="15" spans="1:5">
@@ -9959,14 +10002,14 @@
         <v>389</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C390" s="8"/>
       <c r="D390" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E390" s="8" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="391" ht="15" spans="1:5">
@@ -9974,14 +10017,14 @@
         <v>390</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C391" s="8"/>
       <c r="D391" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E391" s="8" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="392" ht="15" spans="1:5">
@@ -9989,14 +10032,14 @@
         <v>391</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C392" s="8"/>
       <c r="D392" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E392" s="8" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="393" ht="15" spans="1:5">
@@ -10004,14 +10047,14 @@
         <v>392</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C393" s="8"/>
       <c r="D393" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E393" s="8" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="394" ht="15" spans="1:5">
@@ -10019,14 +10062,14 @@
         <v>393</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C394" s="8"/>
       <c r="D394" s="8" t="s">
-        <v>779</v>
-      </c>
-      <c r="E394" s="21" t="s">
-        <v>874</v>
+        <v>781</v>
+      </c>
+      <c r="E394" s="10" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="395" ht="15" spans="1:5">
@@ -10034,14 +10077,14 @@
         <v>394</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C395" s="8"/>
       <c r="D395" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E395" s="8" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="396" ht="15" spans="1:5">
@@ -10049,14 +10092,14 @@
         <v>395</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C396" s="8"/>
       <c r="D396" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E396" s="8" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="397" ht="15" spans="1:5">
@@ -10064,14 +10107,14 @@
         <v>396</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C397" s="8"/>
       <c r="D397" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E397" s="8" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="398" ht="15" spans="1:5">
@@ -10079,14 +10122,14 @@
         <v>397</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C398" s="8"/>
       <c r="D398" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E398" s="8" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="399" ht="15" spans="1:5">
@@ -10094,14 +10137,14 @@
         <v>398</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C399" s="8"/>
       <c r="D399" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E399" s="8" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="400" ht="15" spans="1:5">
@@ -10109,14 +10152,14 @@
         <v>399</v>
       </c>
       <c r="B400" s="8" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C400" s="8"/>
       <c r="D400" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E400" s="8" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="401" ht="15" spans="1:5">
@@ -10124,14 +10167,14 @@
         <v>400</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C401" s="8"/>
       <c r="D401" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E401" s="8" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="402" ht="15" spans="1:5">
@@ -10139,14 +10182,14 @@
         <v>401</v>
       </c>
       <c r="B402" s="8" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C402" s="8"/>
       <c r="D402" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E402" s="8" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="403" ht="15" spans="1:5">
@@ -10154,14 +10197,14 @@
         <v>402</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C403" s="8"/>
       <c r="D403" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E403" s="8" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="404" ht="15" spans="1:5">
@@ -10169,14 +10212,14 @@
         <v>403</v>
       </c>
       <c r="B404" s="8" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C404" s="8"/>
       <c r="D404" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E404" s="8" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="405" ht="15" spans="1:5">
@@ -10184,14 +10227,14 @@
         <v>404</v>
       </c>
       <c r="B405" s="8" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C405" s="8"/>
       <c r="D405" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E405" s="8" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="406" ht="15" spans="1:5">
@@ -10199,14 +10242,14 @@
         <v>405</v>
       </c>
       <c r="B406" s="8" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C406" s="8"/>
       <c r="D406" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E406" s="8" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="407" ht="15" spans="1:5">
@@ -10214,14 +10257,14 @@
         <v>406</v>
       </c>
       <c r="B407" s="8" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C407" s="8"/>
       <c r="D407" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E407" s="8" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="408" ht="15" spans="1:5">
@@ -10229,14 +10272,14 @@
         <v>407</v>
       </c>
       <c r="B408" s="8" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C408" s="8"/>
       <c r="D408" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E408" s="8" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="409" ht="15" spans="1:5">
@@ -10244,14 +10287,14 @@
         <v>408</v>
       </c>
       <c r="B409" s="8" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C409" s="8"/>
       <c r="D409" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E409" s="8" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="410" ht="15" spans="1:5">
@@ -10259,14 +10302,14 @@
         <v>409</v>
       </c>
       <c r="B410" s="8" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C410" s="8"/>
       <c r="D410" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E410" s="8" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="411" ht="15" spans="1:5">
@@ -10274,14 +10317,14 @@
         <v>410</v>
       </c>
       <c r="B411" s="8" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C411" s="8"/>
       <c r="D411" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E411" s="8" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="412" ht="15" spans="1:5">
@@ -10289,14 +10332,14 @@
         <v>411</v>
       </c>
       <c r="B412" s="8" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C412" s="8"/>
       <c r="D412" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E412" s="8" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="413" ht="15" spans="1:5">
@@ -10304,14 +10347,14 @@
         <v>412</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C413" s="8"/>
       <c r="D413" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E413" s="8" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="414" ht="15" spans="1:5">
@@ -10319,14 +10362,14 @@
         <v>413</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C414" s="8"/>
       <c r="D414" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E414" s="8" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="415" ht="15" spans="1:5">
@@ -10334,14 +10377,14 @@
         <v>414</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C415" s="8"/>
       <c r="D415" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E415" s="8" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="416" ht="15" spans="1:5">
@@ -10349,14 +10392,14 @@
         <v>415</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C416" s="8"/>
       <c r="D416" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E416" s="8" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="417" ht="15" spans="1:5">
@@ -10364,14 +10407,14 @@
         <v>416</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C417" s="8"/>
       <c r="D417" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E417" s="8" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="418" ht="15" spans="1:5">
@@ -10379,14 +10422,14 @@
         <v>417</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C418" s="8"/>
       <c r="D418" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E418" s="8" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="419" ht="15" spans="1:5">
@@ -10394,14 +10437,14 @@
         <v>418</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C419" s="8"/>
       <c r="D419" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E419" s="8" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="420" ht="15" spans="1:5">
@@ -10409,14 +10452,14 @@
         <v>419</v>
       </c>
       <c r="B420" s="8" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C420" s="8"/>
       <c r="D420" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E420" s="8" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="421" ht="15" spans="1:5">
@@ -10424,14 +10467,14 @@
         <v>420</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C421" s="8"/>
       <c r="D421" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E421" s="8" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="422" ht="15" spans="1:5">
@@ -10439,14 +10482,14 @@
         <v>421</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C422" s="8"/>
       <c r="D422" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E422" s="8" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="423" ht="15" spans="1:5">
@@ -10454,14 +10497,14 @@
         <v>422</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C423" s="8"/>
       <c r="D423" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E423" s="8" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="424" ht="15" spans="1:5">
@@ -10469,14 +10512,14 @@
         <v>423</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C424" s="8"/>
       <c r="D424" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E424" s="8" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="425" ht="15" spans="1:5">
@@ -10484,14 +10527,14 @@
         <v>424</v>
       </c>
       <c r="B425" s="8" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C425" s="8"/>
       <c r="D425" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E425" s="8" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="426" ht="15" spans="1:5">
@@ -10499,14 +10542,14 @@
         <v>425</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C426" s="8"/>
       <c r="D426" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E426" s="8" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="427" ht="15" spans="1:5">
@@ -10514,14 +10557,14 @@
         <v>426</v>
       </c>
       <c r="B427" s="8" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C427" s="8"/>
       <c r="D427" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E427" s="8" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="428" ht="15" spans="1:5">
@@ -10529,14 +10572,14 @@
         <v>427</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C428" s="8"/>
       <c r="D428" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E428" s="8" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="429" ht="15" spans="1:5">
@@ -10544,14 +10587,14 @@
         <v>428</v>
       </c>
       <c r="B429" s="8" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C429" s="8"/>
       <c r="D429" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E429" s="8" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="430" ht="15" spans="1:5">
@@ -10559,14 +10602,14 @@
         <v>429</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C430" s="8"/>
       <c r="D430" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E430" s="8" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="431" ht="15" spans="1:5">
@@ -10574,14 +10617,14 @@
         <v>430</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C431" s="8"/>
       <c r="D431" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E431" s="8" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="432" ht="15" spans="1:5">
@@ -10589,14 +10632,14 @@
         <v>431</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C432" s="8"/>
       <c r="D432" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E432" s="8" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="433" ht="15" spans="1:5">
@@ -10604,14 +10647,14 @@
         <v>432</v>
       </c>
       <c r="B433" s="8" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C433" s="8"/>
       <c r="D433" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E433" s="8" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="434" ht="15" spans="1:5">
@@ -10619,14 +10662,14 @@
         <v>433</v>
       </c>
       <c r="B434" s="8" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C434" s="8"/>
       <c r="D434" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E434" s="8" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="435" ht="15" spans="1:5">
@@ -10634,14 +10677,14 @@
         <v>434</v>
       </c>
       <c r="B435" s="8" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C435" s="8"/>
       <c r="D435" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E435" s="8" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="436" ht="15" spans="1:5">
@@ -10649,14 +10692,14 @@
         <v>435</v>
       </c>
       <c r="B436" s="8" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C436" s="8"/>
       <c r="D436" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E436" s="8" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="437" ht="15" spans="1:5">
@@ -10664,14 +10707,14 @@
         <v>436</v>
       </c>
       <c r="B437" s="8" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C437" s="8"/>
       <c r="D437" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E437" s="8" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="438" ht="15" spans="1:5">
@@ -10679,14 +10722,14 @@
         <v>437</v>
       </c>
       <c r="B438" s="8" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C438" s="8"/>
       <c r="D438" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E438" s="8" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="439" ht="15" spans="1:5">
@@ -10694,14 +10737,14 @@
         <v>438</v>
       </c>
       <c r="B439" s="8" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C439" s="8"/>
       <c r="D439" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E439" s="8" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="440" ht="15" spans="1:5">
@@ -10709,14 +10752,14 @@
         <v>439</v>
       </c>
       <c r="B440" s="8" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C440" s="8"/>
       <c r="D440" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E440" s="8" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="441" ht="15" spans="1:5">
@@ -10724,14 +10767,14 @@
         <v>440</v>
       </c>
       <c r="B441" s="8" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C441" s="8"/>
       <c r="D441" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E441" s="8" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="442" ht="15" spans="1:5">
@@ -10739,14 +10782,14 @@
         <v>441</v>
       </c>
       <c r="B442" s="8" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C442" s="8"/>
       <c r="D442" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E442" s="8" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="443" ht="15" spans="1:5">
@@ -10754,14 +10797,14 @@
         <v>442</v>
       </c>
       <c r="B443" s="8" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C443" s="8"/>
       <c r="D443" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E443" s="8" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="444" ht="15" spans="1:5">
@@ -10769,14 +10812,14 @@
         <v>443</v>
       </c>
       <c r="B444" s="8" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C444" s="8"/>
       <c r="D444" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E444" s="8" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="445" ht="15" spans="1:5">
@@ -10784,14 +10827,14 @@
         <v>444</v>
       </c>
       <c r="B445" s="8" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C445" s="8"/>
       <c r="D445" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E445" s="8" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="446" ht="15" spans="1:5">
@@ -10799,14 +10842,14 @@
         <v>445</v>
       </c>
       <c r="B446" s="8" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C446" s="8"/>
       <c r="D446" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E446" s="8" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="447" ht="15" spans="1:5">
@@ -10814,14 +10857,14 @@
         <v>446</v>
       </c>
       <c r="B447" s="8" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C447" s="8"/>
       <c r="D447" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E447" s="8" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="448" ht="15" spans="1:5">
@@ -10829,14 +10872,14 @@
         <v>447</v>
       </c>
       <c r="B448" s="8" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C448" s="8"/>
       <c r="D448" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E448" s="8" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="449" ht="15" spans="1:5">
@@ -10844,14 +10887,14 @@
         <v>448</v>
       </c>
       <c r="B449" s="8" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C449" s="8"/>
       <c r="D449" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E449" s="8" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="450" ht="15" spans="1:5">
@@ -10859,14 +10902,14 @@
         <v>449</v>
       </c>
       <c r="B450" s="8" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C450" s="8"/>
       <c r="D450" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E450" s="8" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="451" ht="15" spans="1:5">
@@ -10874,59 +10917,59 @@
         <v>450</v>
       </c>
       <c r="B451" s="8" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C451" s="8"/>
       <c r="D451" s="8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E451" s="8" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="452" spans="1:5">
       <c r="A452">
         <v>451</v>
       </c>
-      <c r="B452" s="17" t="s">
-        <v>989</v>
+      <c r="B452" s="18" t="s">
+        <v>991</v>
       </c>
       <c r="C452" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D452" t="s">
-        <v>991</v>
-      </c>
-      <c r="E452" s="13" t="s">
-        <v>992</v>
+        <v>993</v>
+      </c>
+      <c r="E452" s="14" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="453" spans="1:5">
       <c r="A453">
         <v>452</v>
       </c>
-      <c r="B453" s="13" t="s">
-        <v>993</v>
+      <c r="B453" s="14" t="s">
+        <v>995</v>
       </c>
       <c r="D453" t="s">
         <v>180</v>
       </c>
-      <c r="E453" s="13" t="s">
-        <v>994</v>
+      <c r="E453" s="14" t="s">
+        <v>996</v>
       </c>
     </row>
     <row r="454" spans="1:5">
       <c r="A454">
         <v>453</v>
       </c>
-      <c r="B454" s="13" t="s">
-        <v>995</v>
+      <c r="B454" s="14" t="s">
+        <v>997</v>
       </c>
       <c r="C454" t="s">
-        <v>996</v>
-      </c>
-      <c r="E454" s="13" t="s">
-        <v>997</v>
+        <v>998</v>
+      </c>
+      <c r="E454" s="14" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="455" ht="15" spans="1:5">
@@ -10934,14 +10977,14 @@
         <v>454</v>
       </c>
       <c r="B455" s="8" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C455" s="8"/>
       <c r="D455" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E455" s="21" t="s">
-        <v>999</v>
+      <c r="E455" s="10" t="s">
+        <v>1001</v>
       </c>
     </row>
     <row r="456" ht="15" spans="1:5">
@@ -10949,14 +10992,14 @@
         <v>455</v>
       </c>
       <c r="B456" s="8" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C456" s="8"/>
       <c r="D456" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E456" s="8" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -10964,13 +11007,13 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D457" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="458" ht="15" spans="1:5">
@@ -10978,14 +11021,14 @@
         <v>457</v>
       </c>
       <c r="B458" s="8" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C458" s="8"/>
       <c r="D458" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E458" s="8" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="459" ht="15" spans="1:5">
@@ -10993,28 +11036,28 @@
         <v>458</v>
       </c>
       <c r="B459" s="8" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C459" s="8"/>
       <c r="D459" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E459" s="8" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="460" ht="15" spans="1:5">
       <c r="A460">
         <v>459</v>
       </c>
-      <c r="B460" s="22" t="s">
-        <v>1009</v>
+      <c r="B460" s="14" t="s">
+        <v>1011</v>
       </c>
       <c r="D460" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E460" s="22" t="s">
-        <v>1010</v>
+      <c r="E460" s="14" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="461" ht="15" spans="1:5">
@@ -11022,59 +11065,131 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D461" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="462" ht="15" spans="1:5">
       <c r="A462">
         <v>461</v>
       </c>
-      <c r="B462" s="22" t="s">
-        <v>1013</v>
+      <c r="B462" s="14" t="s">
+        <v>1015</v>
       </c>
       <c r="D462" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E462" s="22" t="s">
-        <v>1014</v>
+      <c r="E462" s="14" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="463" ht="15" spans="1:5">
       <c r="A463">
         <v>462</v>
       </c>
-      <c r="B463" s="22" t="s">
-        <v>1015</v>
+      <c r="B463" s="14" t="s">
+        <v>1017</v>
       </c>
       <c r="D463" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E463" s="22" t="s">
-        <v>1016</v>
+      <c r="E463" s="14" t="s">
+        <v>1018</v>
       </c>
     </row>
     <row r="464" ht="15" spans="1:5">
       <c r="A464">
         <v>463</v>
       </c>
-      <c r="B464" s="22" t="s">
-        <v>1017</v>
+      <c r="B464" s="14" t="s">
+        <v>1019</v>
       </c>
       <c r="D464" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E464" s="22" t="s">
-        <v>1018</v>
+      <c r="E464" s="14" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465">
+        <v>464</v>
+      </c>
+      <c r="B465" s="22" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D465" t="s">
+        <v>781</v>
+      </c>
+      <c r="E465" s="22" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466">
+        <v>465</v>
+      </c>
+      <c r="B466" s="22" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D466" t="s">
+        <v>781</v>
+      </c>
+      <c r="E466" s="22" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="467" ht="15" spans="1:5">
+      <c r="A467">
+        <v>466</v>
+      </c>
+      <c r="B467" s="23" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C467" s="23"/>
+      <c r="D467" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E467" s="24" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="468" ht="15" spans="1:5">
+      <c r="A468">
+        <v>467</v>
+      </c>
+      <c r="B468" s="23" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C468" s="23"/>
+      <c r="D468" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E468" s="23" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="469" ht="15" spans="1:5">
+      <c r="A469">
+        <v>468</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D469" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E469" t="s">
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E459" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E464" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -11232,6 +11347,8 @@
     <hyperlink ref="E314" r:id="rId152" display="https://pan.quark.cn/s/c928c080711b"/>
     <hyperlink ref="E394" r:id="rId153" display="https://pan.quark.cn/s/e90ebe569558"/>
     <hyperlink ref="E455" r:id="rId154" display="https://pan.quark.cn/s/d3b05e00c02e"/>
+    <hyperlink ref="E98" r:id="rId155" display="https://pan.quark.cn/s/d47624bd9832"/>
+    <hyperlink ref="E467" r:id="rId156" display="https://pan.quark.cn/s/d0bd4ce4f9fe"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$464</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$469</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1033">
   <si>
     <t>id</t>
   </si>
@@ -3175,6 +3175,12 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/931d2b0fe589</t>
+  </si>
+  <si>
+    <t>家宴</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/302f10500dff</t>
   </si>
 </sst>
 </file>
@@ -3850,7 +3856,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3908,8 +3914,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4229,7 +4233,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E469"/>
+  <dimension ref="A1:E470"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="60.75" customWidth="1"/>
@@ -8018,14 +8022,14 @@
       <c r="A258">
         <v>257</v>
       </c>
-      <c r="B258" s="14" t="s">
+      <c r="B258" s="18" t="s">
         <v>593</v>
       </c>
       <c r="C258" s="11"/>
       <c r="D258" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E258" s="13" t="s">
+      <c r="E258" s="6" t="s">
         <v>594</v>
       </c>
     </row>
@@ -11120,13 +11124,13 @@
       <c r="A465">
         <v>464</v>
       </c>
-      <c r="B465" s="22" t="s">
+      <c r="B465" s="14" t="s">
         <v>1021</v>
       </c>
       <c r="D465" t="s">
         <v>781</v>
       </c>
-      <c r="E465" s="22" t="s">
+      <c r="E465" s="14" t="s">
         <v>1022</v>
       </c>
     </row>
@@ -11134,13 +11138,13 @@
       <c r="A466">
         <v>465</v>
       </c>
-      <c r="B466" s="22" t="s">
+      <c r="B466" s="14" t="s">
         <v>1023</v>
       </c>
       <c r="D466" t="s">
         <v>781</v>
       </c>
-      <c r="E466" s="22" t="s">
+      <c r="E466" s="14" t="s">
         <v>1024</v>
       </c>
     </row>
@@ -11148,14 +11152,14 @@
       <c r="A467">
         <v>466</v>
       </c>
-      <c r="B467" s="23" t="s">
+      <c r="B467" s="8" t="s">
         <v>1025</v>
       </c>
-      <c r="C467" s="23"/>
-      <c r="D467" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E467" s="24" t="s">
+      <c r="C467" s="8"/>
+      <c r="D467" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E467" s="10" t="s">
         <v>1026</v>
       </c>
     </row>
@@ -11163,14 +11167,14 @@
       <c r="A468">
         <v>467</v>
       </c>
-      <c r="B468" s="23" t="s">
+      <c r="B468" s="8" t="s">
         <v>1027</v>
       </c>
-      <c r="C468" s="23"/>
-      <c r="D468" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E468" s="23" t="s">
+      <c r="C468" s="8"/>
+      <c r="D468" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E468" s="8" t="s">
         <v>1028</v>
       </c>
     </row>
@@ -11181,15 +11185,29 @@
       <c r="B469" t="s">
         <v>1029</v>
       </c>
-      <c r="D469" s="23" t="s">
+      <c r="D469" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E469" t="s">
         <v>1030</v>
       </c>
     </row>
+    <row r="470" ht="15" spans="1:5">
+      <c r="A470">
+        <v>469</v>
+      </c>
+      <c r="B470" s="22" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D470" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E470" s="22" t="s">
+        <v>1032</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E464" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E469" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="1033">
   <si>
     <t>id</t>
   </si>
@@ -10972,6 +10972,9 @@
       <c r="C454" t="s">
         <v>998</v>
       </c>
+      <c r="D454" t="s">
+        <v>180</v>
+      </c>
       <c r="E454" s="14" t="s">
         <v>999</v>
       </c>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$469</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$470</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1057">
   <si>
     <t>id</t>
   </si>
@@ -3181,6 +3181,78 @@
   </si>
   <si>
     <t>https://pan.quark.cn/s/302f10500dff</t>
+  </si>
+  <si>
+    <t>阴明寺</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/96b934ac748c</t>
+  </si>
+  <si>
+    <t>死者在幻夜中醒来</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/bce6ef2d3d90</t>
+  </si>
+  <si>
+    <t>刑侦现场雪夜追凶</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/666771fc225b</t>
+  </si>
+  <si>
+    <t>生还之日</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e322eb23918a</t>
+  </si>
+  <si>
+    <t>一个死去的朋友</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/a91f8b159631</t>
+  </si>
+  <si>
+    <t>生门</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/37808472b217</t>
+  </si>
+  <si>
+    <t>东京恐怖故事：加藤病院</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/98d108d70517</t>
+  </si>
+  <si>
+    <t>三界之下</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/dc3d2d0575ae</t>
+  </si>
+  <si>
+    <t>猫岛2犬山谋杀循环</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/767d5570cd79</t>
+  </si>
+  <si>
+    <t>声声慢</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/e847a78fec93</t>
+  </si>
+  <si>
+    <t>声声慢2</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/7cc871fd1e13</t>
+  </si>
+  <si>
+    <t>我滴家在东北</t>
+  </si>
+  <si>
+    <t>https://pan.quark.cn/s/74291074815b</t>
   </si>
 </sst>
 </file>
@@ -4233,7 +4305,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E470"/>
+  <dimension ref="A1:E482"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="60.75" customWidth="1"/>
@@ -6088,7 +6160,7 @@
       <c r="D129" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E129" s="8" t="s">
+      <c r="E129" s="10" t="s">
         <v>332</v>
       </c>
     </row>
@@ -7984,7 +8056,7 @@
       <c r="D255" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E255" s="13" t="s">
+      <c r="E255" s="6" t="s">
         <v>588</v>
       </c>
     </row>
@@ -11199,18 +11271,186 @@
       <c r="A470">
         <v>469</v>
       </c>
-      <c r="B470" s="22" t="s">
+      <c r="B470" s="14" t="s">
         <v>1031</v>
       </c>
       <c r="D470" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E470" s="22" t="s">
+      <c r="E470" s="14" t="s">
         <v>1032</v>
       </c>
     </row>
+    <row r="471" ht="15" spans="1:5">
+      <c r="A471">
+        <v>470</v>
+      </c>
+      <c r="B471" s="18" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D471" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E471" s="22" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="472" ht="15" spans="1:5">
+      <c r="A472">
+        <v>471</v>
+      </c>
+      <c r="B472" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D472" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E472" s="22" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="473" ht="15" spans="1:5">
+      <c r="A473">
+        <v>472</v>
+      </c>
+      <c r="B473" s="22" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D473" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E473" s="22" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="474" ht="15" spans="1:5">
+      <c r="A474">
+        <v>473</v>
+      </c>
+      <c r="B474" s="22" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D474" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E474" s="22" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="475" ht="15" spans="1:5">
+      <c r="A475">
+        <v>474</v>
+      </c>
+      <c r="B475" s="22" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D475" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E475" s="22" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="476" ht="15" spans="1:5">
+      <c r="A476">
+        <v>475</v>
+      </c>
+      <c r="B476" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D476" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E476" s="22" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="477" ht="15" spans="1:5">
+      <c r="A477">
+        <v>476</v>
+      </c>
+      <c r="B477" s="22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D477" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E477" s="22" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="478" ht="15" spans="1:5">
+      <c r="A478">
+        <v>477</v>
+      </c>
+      <c r="B478" s="22" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D478" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E478" s="22" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="479" ht="15" spans="1:5">
+      <c r="A479">
+        <v>478</v>
+      </c>
+      <c r="B479" s="22" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D479" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E479" s="22" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="480" ht="15" spans="1:5">
+      <c r="A480">
+        <v>479</v>
+      </c>
+      <c r="B480" s="22" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D480" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E480" s="22" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="481" ht="15" spans="1:5">
+      <c r="A481">
+        <v>480</v>
+      </c>
+      <c r="B481" s="22" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D481" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E481" s="22" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="482" ht="15" spans="1:5">
+      <c r="A482">
+        <v>481</v>
+      </c>
+      <c r="B482" s="22" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D482" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E482" s="22" t="s">
+        <v>1056</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E469" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E470" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -11370,6 +11610,7 @@
     <hyperlink ref="E455" r:id="rId154" display="https://pan.quark.cn/s/d3b05e00c02e"/>
     <hyperlink ref="E98" r:id="rId155" display="https://pan.quark.cn/s/d47624bd9832"/>
     <hyperlink ref="E467" r:id="rId156" display="https://pan.quark.cn/s/d0bd4ce4f9fe"/>
+    <hyperlink ref="E129" r:id="rId157" display="https://pan.quark.cn/s/d57753b80c6b"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
